--- a/output/diagnostics/Bayesian_parameter(results).xlsx
+++ b/output/diagnostics/Bayesian_parameter(results).xlsx
@@ -482,31 +482,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.847</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.195</v>
+        <v>0.179</v>
       </c>
       <c r="D2" t="n">
-        <v>0.487</v>
+        <v>0.62</v>
       </c>
       <c r="E2" t="n">
-        <v>1.192</v>
+        <v>1.299</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="H2" t="n">
-        <v>804</v>
+        <v>680</v>
       </c>
       <c r="I2" t="n">
-        <v>531</v>
+        <v>507</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="3">
@@ -516,31 +516,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.498</v>
+        <v>0.501</v>
       </c>
       <c r="C3" t="n">
-        <v>0.163</v>
+        <v>0.147</v>
       </c>
       <c r="D3" t="n">
-        <v>0.212</v>
+        <v>0.218</v>
       </c>
       <c r="E3" t="n">
-        <v>0.802</v>
+        <v>0.769</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004</v>
+        <v>0.017</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003</v>
+        <v>0.012</v>
       </c>
       <c r="H3" t="n">
-        <v>1580</v>
+        <v>69</v>
       </c>
       <c r="I3" t="n">
-        <v>749</v>
+        <v>487</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="4">
@@ -550,31 +550,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.497</v>
+        <v>0.474</v>
       </c>
       <c r="C4" t="n">
-        <v>0.147</v>
+        <v>0.146</v>
       </c>
       <c r="D4" t="n">
-        <v>0.282</v>
+        <v>0.219</v>
       </c>
       <c r="E4" t="n">
-        <v>0.778</v>
+        <v>0.663</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005</v>
+        <v>0.031</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004</v>
+        <v>0.022</v>
       </c>
       <c r="H4" t="n">
-        <v>846</v>
+        <v>20</v>
       </c>
       <c r="I4" t="n">
-        <v>647</v>
+        <v>553</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="5">
@@ -584,31 +584,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.142</v>
+        <v>0.117</v>
       </c>
       <c r="C5" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
       <c r="D5" t="n">
-        <v>0.112</v>
+        <v>0.099</v>
       </c>
       <c r="E5" t="n">
-        <v>0.172</v>
+        <v>0.148</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="H5" t="n">
-        <v>430</v>
+        <v>18</v>
       </c>
       <c r="I5" t="n">
-        <v>604</v>
+        <v>449</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="6">
@@ -618,16 +618,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.082</v>
+        <v>0.083</v>
       </c>
       <c r="C6" t="n">
-        <v>0.034</v>
+        <v>0.032</v>
       </c>
       <c r="D6" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="E6" t="n">
-        <v>0.143</v>
+        <v>0.147</v>
       </c>
       <c r="F6" t="n">
         <v>0.001</v>
@@ -636,13 +636,13 @@
         <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>1068</v>
+        <v>1767</v>
       </c>
       <c r="I6" t="n">
-        <v>819</v>
+        <v>329</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="7">
@@ -652,31 +652,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.002</v>
+        <v>1.124</v>
       </c>
       <c r="C7" t="n">
-        <v>0.355</v>
+        <v>0.506</v>
       </c>
       <c r="D7" t="n">
-        <v>0.455</v>
+        <v>0.59</v>
       </c>
       <c r="E7" t="n">
-        <v>1.664</v>
+        <v>2.106</v>
       </c>
       <c r="F7" t="n">
-        <v>0.012</v>
+        <v>0.14</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.101</v>
       </c>
       <c r="H7" t="n">
-        <v>936</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>710</v>
+        <v>187</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="8">
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.033</v>
+        <v>0.039</v>
       </c>
       <c r="C8" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.017</v>
+        <v>0.025</v>
       </c>
       <c r="E8" t="n">
-        <v>0.049</v>
+        <v>0.057</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H8" t="n">
-        <v>874</v>
+        <v>602</v>
       </c>
       <c r="I8" t="n">
-        <v>650</v>
+        <v>622</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="9">
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.252</v>
+        <v>0.262</v>
       </c>
       <c r="C9" t="n">
-        <v>0.054</v>
+        <v>0.052</v>
       </c>
       <c r="D9" t="n">
-        <v>0.154</v>
+        <v>0.153</v>
       </c>
       <c r="E9" t="n">
-        <v>0.348</v>
+        <v>0.355</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H9" t="n">
-        <v>1348</v>
+        <v>160</v>
       </c>
       <c r="I9" t="n">
-        <v>827</v>
+        <v>461</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="10">
@@ -754,31 +754,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.357</v>
+        <v>0.326</v>
       </c>
       <c r="C10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.232</v>
+        <v>0.231</v>
       </c>
       <c r="E10" t="n">
-        <v>0.498</v>
+        <v>0.493</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002</v>
+        <v>0.027</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001</v>
+        <v>0.019</v>
       </c>
       <c r="H10" t="n">
-        <v>1614</v>
+        <v>11</v>
       </c>
       <c r="I10" t="n">
-        <v>672</v>
+        <v>292</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="11">
@@ -791,13 +791,13 @@
         <v>0.017</v>
       </c>
       <c r="C11" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="D11" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.026</v>
+        <v>0.025</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -806,13 +806,13 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>397</v>
+        <v>467</v>
       </c>
       <c r="I11" t="n">
-        <v>563</v>
+        <v>547</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="12">
@@ -822,31 +822,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.713</v>
+        <v>0.767</v>
       </c>
       <c r="C12" t="n">
-        <v>0.252</v>
+        <v>0.225</v>
       </c>
       <c r="D12" t="n">
-        <v>0.273</v>
+        <v>0.358</v>
       </c>
       <c r="E12" t="n">
-        <v>1.142</v>
+        <v>1.229</v>
       </c>
       <c r="F12" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="G12" t="n">
         <v>0.005</v>
       </c>
       <c r="H12" t="n">
-        <v>1268</v>
+        <v>1075</v>
       </c>
       <c r="I12" t="n">
-        <v>842</v>
+        <v>525</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="13">
@@ -856,31 +856,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.176</v>
+        <v>0.185</v>
       </c>
       <c r="C13" t="n">
-        <v>0.089</v>
+        <v>0.079</v>
       </c>
       <c r="D13" t="n">
-        <v>0.019</v>
+        <v>0.038</v>
       </c>
       <c r="E13" t="n">
-        <v>0.336</v>
+        <v>0.319</v>
       </c>
       <c r="F13" t="n">
-        <v>0.002</v>
+        <v>0.012</v>
       </c>
       <c r="G13" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="H13" t="n">
-        <v>1692</v>
+        <v>45</v>
       </c>
       <c r="I13" t="n">
-        <v>630</v>
+        <v>609</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="14">
@@ -890,31 +890,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.619</v>
+        <v>1.75</v>
       </c>
       <c r="C14" t="n">
-        <v>0.652</v>
+        <v>0.74</v>
       </c>
       <c r="D14" t="n">
-        <v>0.555</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>2.895</v>
+        <v>2.633</v>
       </c>
       <c r="F14" t="n">
-        <v>0.023</v>
+        <v>0.253</v>
       </c>
       <c r="G14" t="n">
-        <v>0.016</v>
+        <v>0.188</v>
       </c>
       <c r="H14" t="n">
-        <v>805</v>
+        <v>11</v>
       </c>
       <c r="I14" t="n">
-        <v>674</v>
+        <v>375</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="15">
@@ -924,31 +924,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.434</v>
+        <v>2.529</v>
       </c>
       <c r="C15" t="n">
-        <v>0.517</v>
+        <v>0.458</v>
       </c>
       <c r="D15" t="n">
-        <v>1.505</v>
+        <v>1.514</v>
       </c>
       <c r="E15" t="n">
-        <v>3.416</v>
+        <v>3.304</v>
       </c>
       <c r="F15" t="n">
-        <v>0.015</v>
+        <v>0.059</v>
       </c>
       <c r="G15" t="n">
-        <v>0.011</v>
+        <v>0.042</v>
       </c>
       <c r="H15" t="n">
-        <v>1175</v>
+        <v>68</v>
       </c>
       <c r="I15" t="n">
-        <v>745</v>
+        <v>525</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="16">
@@ -958,31 +958,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.404</v>
+        <v>3.218</v>
       </c>
       <c r="C16" t="n">
-        <v>1.211</v>
+        <v>1.054</v>
       </c>
       <c r="D16" t="n">
-        <v>1.501</v>
+        <v>1.513</v>
       </c>
       <c r="E16" t="n">
-        <v>5.55</v>
+        <v>5.239</v>
       </c>
       <c r="F16" t="n">
-        <v>0.044</v>
+        <v>0.039</v>
       </c>
       <c r="G16" t="n">
-        <v>0.031</v>
+        <v>0.027</v>
       </c>
       <c r="H16" t="n">
-        <v>645</v>
+        <v>679</v>
       </c>
       <c r="I16" t="n">
-        <v>340</v>
+        <v>677</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="17">
@@ -992,31 +992,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.473</v>
+        <v>0.511</v>
       </c>
       <c r="C17" t="n">
-        <v>0.275</v>
+        <v>0.286</v>
       </c>
       <c r="D17" t="n">
-        <v>0.068</v>
+        <v>0.057</v>
       </c>
       <c r="E17" t="n">
-        <v>0.958</v>
+        <v>1.044</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G17" t="n">
-        <v>0.007</v>
+        <v>0.015</v>
       </c>
       <c r="H17" t="n">
-        <v>726</v>
+        <v>570</v>
       </c>
       <c r="I17" t="n">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="18">
@@ -1026,31 +1026,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.575</v>
+        <v>0.47</v>
       </c>
       <c r="C18" t="n">
-        <v>0.283</v>
+        <v>0.319</v>
       </c>
       <c r="D18" t="n">
-        <v>0.125</v>
+        <v>0.119</v>
       </c>
       <c r="E18" t="n">
-        <v>1.096</v>
+        <v>1.027</v>
       </c>
       <c r="F18" t="n">
-        <v>0.008</v>
+        <v>0.099</v>
       </c>
       <c r="G18" t="n">
-        <v>0.005</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>1085</v>
+        <v>7</v>
       </c>
       <c r="I18" t="n">
-        <v>594</v>
+        <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="19">
@@ -1060,31 +1060,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23.109</v>
+        <v>22.187</v>
       </c>
       <c r="C19" t="n">
-        <v>1.788</v>
+        <v>1.71</v>
       </c>
       <c r="D19" t="n">
-        <v>20.349</v>
+        <v>20.02</v>
       </c>
       <c r="E19" t="n">
-        <v>25.986</v>
+        <v>25.417</v>
       </c>
       <c r="F19" t="n">
-        <v>0.051</v>
+        <v>0.368</v>
       </c>
       <c r="G19" t="n">
-        <v>0.036</v>
+        <v>0.264</v>
       </c>
       <c r="H19" t="n">
-        <v>1225</v>
+        <v>37</v>
       </c>
       <c r="I19" t="n">
-        <v>620</v>
+        <v>531</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="20">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.67</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>0.204</v>
+        <v>0.168</v>
       </c>
       <c r="D20" t="n">
-        <v>0.317</v>
+        <v>0.375</v>
       </c>
       <c r="E20" t="n">
-        <v>1.048</v>
+        <v>1.005</v>
       </c>
       <c r="F20" t="n">
-        <v>0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="H20" t="n">
-        <v>1276</v>
+        <v>180</v>
       </c>
       <c r="I20" t="n">
-        <v>847</v>
+        <v>703</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="21">
@@ -1128,31 +1128,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.298</v>
+        <v>0.19</v>
       </c>
       <c r="C21" t="n">
-        <v>0.082</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>0.159</v>
+        <v>0.116</v>
       </c>
       <c r="E21" t="n">
-        <v>0.439</v>
+        <v>0.323</v>
       </c>
       <c r="F21" t="n">
-        <v>0.003</v>
+        <v>0.022</v>
       </c>
       <c r="G21" t="n">
-        <v>0.002</v>
+        <v>0.016</v>
       </c>
       <c r="H21" t="n">
-        <v>788</v>
+        <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>866</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="22">
@@ -1162,16 +1162,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="C22" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="D22" t="n">
-        <v>0.041</v>
+        <v>0.043</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1180,13 +1180,13 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>393</v>
+        <v>453</v>
       </c>
       <c r="I22" t="n">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="J22" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="23">
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.735</v>
       </c>
       <c r="C23" t="n">
-        <v>0.13</v>
+        <v>0.134</v>
       </c>
       <c r="D23" t="n">
-        <v>0.437</v>
+        <v>0.469</v>
       </c>
       <c r="E23" t="n">
-        <v>0.908</v>
+        <v>0.913</v>
       </c>
       <c r="F23" t="n">
-        <v>0.004</v>
+        <v>0.036</v>
       </c>
       <c r="G23" t="n">
-        <v>0.002</v>
+        <v>0.028</v>
       </c>
       <c r="H23" t="n">
-        <v>1390</v>
+        <v>14</v>
       </c>
       <c r="I23" t="n">
-        <v>843</v>
+        <v>703</v>
       </c>
       <c r="J23" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="24">
@@ -1230,31 +1230,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
       <c r="C24" t="n">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
       <c r="D24" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1599</v>
+        <v>754</v>
       </c>
       <c r="I24" t="n">
-        <v>634</v>
+        <v>323</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="25">
@@ -1264,31 +1264,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.034</v>
+        <v>0.041</v>
       </c>
       <c r="C25" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="D25" t="n">
-        <v>0.019</v>
+        <v>0.022</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05</v>
+        <v>0.053</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="H25" t="n">
-        <v>953</v>
+        <v>13</v>
       </c>
       <c r="I25" t="n">
-        <v>766</v>
+        <v>549</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="26">
@@ -1298,31 +1298,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="C26" t="n">
         <v>0.005</v>
       </c>
       <c r="D26" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="E26" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1096</v>
+        <v>267</v>
       </c>
       <c r="I26" t="n">
-        <v>642</v>
+        <v>748</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="27">
@@ -1332,31 +1332,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.193</v>
+        <v>2.961</v>
       </c>
       <c r="C27" t="n">
-        <v>0.665</v>
+        <v>0.707</v>
       </c>
       <c r="D27" t="n">
-        <v>2.049</v>
+        <v>2.039</v>
       </c>
       <c r="E27" t="n">
-        <v>4.469</v>
+        <v>4.332</v>
       </c>
       <c r="F27" t="n">
-        <v>0.019</v>
+        <v>0.198</v>
       </c>
       <c r="G27" t="n">
-        <v>0.014</v>
+        <v>0.143</v>
       </c>
       <c r="H27" t="n">
-        <v>1158</v>
+        <v>13</v>
       </c>
       <c r="I27" t="n">
-        <v>657</v>
+        <v>598</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="28">
@@ -1366,31 +1366,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.077</v>
+        <v>0.075</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="D28" t="n">
-        <v>0.038</v>
+        <v>0.041</v>
       </c>
       <c r="E28" t="n">
-        <v>0.112</v>
+        <v>0.109</v>
       </c>
       <c r="F28" t="n">
         <v>0.001</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>1150</v>
+        <v>376</v>
       </c>
       <c r="I28" t="n">
-        <v>657</v>
+        <v>443</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="29">
@@ -1400,31 +1400,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.22</v>
+        <v>0.221</v>
       </c>
       <c r="C29" t="n">
-        <v>0.062</v>
+        <v>0.055</v>
       </c>
       <c r="D29" t="n">
-        <v>0.102</v>
+        <v>0.113</v>
       </c>
       <c r="E29" t="n">
-        <v>0.323</v>
+        <v>0.332</v>
       </c>
       <c r="F29" t="n">
         <v>0.002</v>
       </c>
       <c r="G29" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H29" t="n">
-        <v>1300</v>
+        <v>1252</v>
       </c>
       <c r="I29" t="n">
-        <v>589</v>
+        <v>633</v>
       </c>
       <c r="J29" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="30">
@@ -1434,31 +1434,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.063</v>
+        <v>1.012</v>
       </c>
       <c r="C30" t="n">
-        <v>0.211</v>
+        <v>0.202</v>
       </c>
       <c r="D30" t="n">
-        <v>0.702</v>
+        <v>0.712</v>
       </c>
       <c r="E30" t="n">
-        <v>1.458</v>
+        <v>1.427</v>
       </c>
       <c r="F30" t="n">
-        <v>0.007</v>
+        <v>0.032</v>
       </c>
       <c r="G30" t="n">
-        <v>0.005</v>
+        <v>0.023</v>
       </c>
       <c r="H30" t="n">
-        <v>884</v>
+        <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>790</v>
+        <v>706</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="31">
@@ -1486,13 +1486,13 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>807</v>
+        <v>7</v>
       </c>
       <c r="I31" t="n">
-        <v>456</v>
+        <v>11</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="32">
@@ -1502,31 +1502,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>23918.437</v>
+        <v>1950229700.775</v>
       </c>
       <c r="C32" t="n">
-        <v>121358.759</v>
+        <v>3379534531.369</v>
       </c>
       <c r="D32" t="n">
-        <v>582.2380000000001</v>
+        <v>1643.001</v>
       </c>
       <c r="E32" t="n">
-        <v>54231.796</v>
+        <v>7800827984.613</v>
       </c>
       <c r="F32" t="n">
-        <v>6984.97</v>
+        <v>1669366912.208</v>
       </c>
       <c r="G32" t="n">
-        <v>4943.899</v>
+        <v>1276393665.527</v>
       </c>
       <c r="H32" t="n">
-        <v>807</v>
+        <v>7</v>
       </c>
       <c r="I32" t="n">
-        <v>456</v>
+        <v>11</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>

--- a/output/diagnostics/Bayesian_parameter(results).xlsx
+++ b/output/diagnostics/Bayesian_parameter(results).xlsx
@@ -482,31 +482,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.958</v>
       </c>
       <c r="C2" t="n">
-        <v>0.179</v>
+        <v>0.197</v>
       </c>
       <c r="D2" t="n">
-        <v>0.62</v>
+        <v>0.611</v>
       </c>
       <c r="E2" t="n">
-        <v>1.299</v>
+        <v>1.347</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="H2" t="n">
-        <v>680</v>
+        <v>1008</v>
       </c>
       <c r="I2" t="n">
-        <v>507</v>
+        <v>846</v>
       </c>
       <c r="J2" t="n">
-        <v>1.58</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -516,31 +516,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.501</v>
+        <v>0.477</v>
       </c>
       <c r="C3" t="n">
-        <v>0.147</v>
+        <v>0.168</v>
       </c>
       <c r="D3" t="n">
-        <v>0.218</v>
+        <v>0.18</v>
       </c>
       <c r="E3" t="n">
-        <v>0.769</v>
+        <v>0.79</v>
       </c>
       <c r="F3" t="n">
-        <v>0.017</v>
+        <v>0.005</v>
       </c>
       <c r="G3" t="n">
-        <v>0.012</v>
+        <v>0.004</v>
       </c>
       <c r="H3" t="n">
-        <v>69</v>
+        <v>1191</v>
       </c>
       <c r="I3" t="n">
-        <v>487</v>
+        <v>733</v>
       </c>
       <c r="J3" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -550,31 +550,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.474</v>
+        <v>0.449</v>
       </c>
       <c r="C4" t="n">
-        <v>0.146</v>
+        <v>0.137</v>
       </c>
       <c r="D4" t="n">
-        <v>0.219</v>
+        <v>0.223</v>
       </c>
       <c r="E4" t="n">
-        <v>0.663</v>
+        <v>0.703</v>
       </c>
       <c r="F4" t="n">
-        <v>0.031</v>
+        <v>0.005</v>
       </c>
       <c r="G4" t="n">
-        <v>0.022</v>
+        <v>0.003</v>
       </c>
       <c r="H4" t="n">
-        <v>20</v>
+        <v>889</v>
       </c>
       <c r="I4" t="n">
-        <v>553</v>
+        <v>824</v>
       </c>
       <c r="J4" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -584,31 +584,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.117</v>
+        <v>0.123</v>
       </c>
       <c r="C5" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="D5" t="n">
-        <v>0.099</v>
+        <v>0.097</v>
       </c>
       <c r="E5" t="n">
-        <v>0.148</v>
+        <v>0.15</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>18</v>
+        <v>575</v>
       </c>
       <c r="I5" t="n">
-        <v>449</v>
+        <v>671</v>
       </c>
       <c r="J5" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="6">
@@ -621,13 +621,13 @@
         <v>0.083</v>
       </c>
       <c r="C6" t="n">
-        <v>0.032</v>
+        <v>0.035</v>
       </c>
       <c r="D6" t="n">
-        <v>0.024</v>
+        <v>0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>0.147</v>
+        <v>0.143</v>
       </c>
       <c r="F6" t="n">
         <v>0.001</v>
@@ -636,13 +636,13 @@
         <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>1767</v>
+        <v>1174</v>
       </c>
       <c r="I6" t="n">
-        <v>329</v>
+        <v>656</v>
       </c>
       <c r="J6" t="n">
-        <v>1.54</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -652,31 +652,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.124</v>
+        <v>1.247</v>
       </c>
       <c r="C7" t="n">
-        <v>0.506</v>
+        <v>0.447</v>
       </c>
       <c r="D7" t="n">
-        <v>0.59</v>
+        <v>0.537</v>
       </c>
       <c r="E7" t="n">
-        <v>2.106</v>
+        <v>2.041</v>
       </c>
       <c r="F7" t="n">
-        <v>0.14</v>
+        <v>0.015</v>
       </c>
       <c r="G7" t="n">
-        <v>0.101</v>
+        <v>0.011</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>912</v>
       </c>
       <c r="I7" t="n">
-        <v>187</v>
+        <v>724</v>
       </c>
       <c r="J7" t="n">
-        <v>1.32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
       <c r="C8" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.025</v>
+        <v>0.022</v>
       </c>
       <c r="E8" t="n">
         <v>0.057</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>602</v>
+        <v>922</v>
       </c>
       <c r="I8" t="n">
-        <v>622</v>
+        <v>757</v>
       </c>
       <c r="J8" t="n">
-        <v>1.55</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.262</v>
+        <v>0.256</v>
       </c>
       <c r="C9" t="n">
-        <v>0.052</v>
+        <v>0.055</v>
       </c>
       <c r="D9" t="n">
-        <v>0.153</v>
+        <v>0.158</v>
       </c>
       <c r="E9" t="n">
         <v>0.355</v>
@@ -735,16 +735,16 @@
         <v>0.002</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H9" t="n">
-        <v>160</v>
+        <v>1067</v>
       </c>
       <c r="I9" t="n">
-        <v>461</v>
+        <v>812</v>
       </c>
       <c r="J9" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="10">
@@ -754,31 +754,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.326</v>
+        <v>0.357</v>
       </c>
       <c r="C10" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.074</v>
       </c>
       <c r="D10" t="n">
-        <v>0.231</v>
+        <v>0.214</v>
       </c>
       <c r="E10" t="n">
-        <v>0.493</v>
+        <v>0.489</v>
       </c>
       <c r="F10" t="n">
-        <v>0.027</v>
+        <v>0.002</v>
       </c>
       <c r="G10" t="n">
-        <v>0.019</v>
+        <v>0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>1526</v>
       </c>
       <c r="I10" t="n">
-        <v>292</v>
+        <v>794</v>
       </c>
       <c r="J10" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -791,13 +791,13 @@
         <v>0.017</v>
       </c>
       <c r="C11" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="D11" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -806,13 +806,13 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>467</v>
+        <v>587</v>
       </c>
       <c r="I11" t="n">
-        <v>547</v>
+        <v>732</v>
       </c>
       <c r="J11" t="n">
-        <v>1.53</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -822,31 +822,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.767</v>
+        <v>0.758</v>
       </c>
       <c r="C12" t="n">
-        <v>0.225</v>
+        <v>0.265</v>
       </c>
       <c r="D12" t="n">
-        <v>0.358</v>
+        <v>0.321</v>
       </c>
       <c r="E12" t="n">
-        <v>1.229</v>
+        <v>1.262</v>
       </c>
       <c r="F12" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="G12" t="n">
         <v>0.006</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.005</v>
-      </c>
       <c r="H12" t="n">
-        <v>1075</v>
+        <v>808</v>
       </c>
       <c r="I12" t="n">
-        <v>525</v>
+        <v>547</v>
       </c>
       <c r="J12" t="n">
-        <v>1.57</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -856,31 +856,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.185</v>
+        <v>0.172</v>
       </c>
       <c r="C13" t="n">
-        <v>0.079</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.038</v>
+        <v>0.03</v>
       </c>
       <c r="E13" t="n">
-        <v>0.319</v>
+        <v>0.329</v>
       </c>
       <c r="F13" t="n">
-        <v>0.012</v>
+        <v>0.003</v>
       </c>
       <c r="G13" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="H13" t="n">
-        <v>45</v>
+        <v>1100</v>
       </c>
       <c r="I13" t="n">
-        <v>609</v>
+        <v>706</v>
       </c>
       <c r="J13" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -890,31 +890,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="C14" t="n">
-        <v>0.74</v>
+        <v>0.593</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.527</v>
       </c>
       <c r="E14" t="n">
-        <v>2.633</v>
+        <v>2.588</v>
       </c>
       <c r="F14" t="n">
-        <v>0.253</v>
+        <v>0.02</v>
       </c>
       <c r="G14" t="n">
-        <v>0.188</v>
+        <v>0.014</v>
       </c>
       <c r="H14" t="n">
-        <v>11</v>
+        <v>802</v>
       </c>
       <c r="I14" t="n">
-        <v>375</v>
+        <v>755</v>
       </c>
       <c r="J14" t="n">
-        <v>1.28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -924,31 +924,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.529</v>
+        <v>2.422</v>
       </c>
       <c r="C15" t="n">
-        <v>0.458</v>
+        <v>0.533</v>
       </c>
       <c r="D15" t="n">
-        <v>1.514</v>
+        <v>1.462</v>
       </c>
       <c r="E15" t="n">
-        <v>3.304</v>
+        <v>3.456</v>
       </c>
       <c r="F15" t="n">
-        <v>0.059</v>
+        <v>0.014</v>
       </c>
       <c r="G15" t="n">
-        <v>0.042</v>
+        <v>0.01</v>
       </c>
       <c r="H15" t="n">
-        <v>68</v>
+        <v>1413</v>
       </c>
       <c r="I15" t="n">
-        <v>525</v>
+        <v>591</v>
       </c>
       <c r="J15" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="16">
@@ -958,31 +958,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.218</v>
+        <v>3.097</v>
       </c>
       <c r="C16" t="n">
-        <v>1.054</v>
+        <v>1.141</v>
       </c>
       <c r="D16" t="n">
-        <v>1.513</v>
+        <v>1.505</v>
       </c>
       <c r="E16" t="n">
-        <v>5.239</v>
+        <v>5.117</v>
       </c>
       <c r="F16" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
       <c r="G16" t="n">
-        <v>0.027</v>
+        <v>0.03</v>
       </c>
       <c r="H16" t="n">
-        <v>679</v>
+        <v>806</v>
       </c>
       <c r="I16" t="n">
-        <v>677</v>
+        <v>575</v>
       </c>
       <c r="J16" t="n">
-        <v>1.54</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -992,31 +992,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.511</v>
+        <v>0.539</v>
       </c>
       <c r="C17" t="n">
-        <v>0.286</v>
+        <v>0.307</v>
       </c>
       <c r="D17" t="n">
-        <v>0.057</v>
+        <v>0.074</v>
       </c>
       <c r="E17" t="n">
-        <v>1.044</v>
+        <v>1.094</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G17" t="n">
-        <v>0.015</v>
+        <v>0.007</v>
       </c>
       <c r="H17" t="n">
-        <v>570</v>
+        <v>865</v>
       </c>
       <c r="I17" t="n">
-        <v>626</v>
+        <v>737</v>
       </c>
       <c r="J17" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="18">
@@ -1026,31 +1026,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.47</v>
+        <v>0.576</v>
       </c>
       <c r="C18" t="n">
-        <v>0.319</v>
+        <v>0.264</v>
       </c>
       <c r="D18" t="n">
-        <v>0.119</v>
+        <v>0.155</v>
       </c>
       <c r="E18" t="n">
-        <v>1.027</v>
+        <v>1.1</v>
       </c>
       <c r="F18" t="n">
-        <v>0.099</v>
+        <v>0.008</v>
       </c>
       <c r="G18" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="H18" t="n">
-        <v>7</v>
+        <v>1061</v>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>588</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1060,31 +1060,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22.187</v>
+        <v>22.687</v>
       </c>
       <c r="C19" t="n">
-        <v>1.71</v>
+        <v>1.769</v>
       </c>
       <c r="D19" t="n">
         <v>20.02</v>
       </c>
       <c r="E19" t="n">
-        <v>25.417</v>
+        <v>25.532</v>
       </c>
       <c r="F19" t="n">
-        <v>0.368</v>
+        <v>0.049</v>
       </c>
       <c r="G19" t="n">
-        <v>0.264</v>
+        <v>0.035</v>
       </c>
       <c r="H19" t="n">
-        <v>37</v>
+        <v>1251</v>
       </c>
       <c r="I19" t="n">
-        <v>531</v>
+        <v>693</v>
       </c>
       <c r="J19" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.666</v>
       </c>
       <c r="C20" t="n">
-        <v>0.168</v>
+        <v>0.194</v>
       </c>
       <c r="D20" t="n">
-        <v>0.375</v>
+        <v>0.349</v>
       </c>
       <c r="E20" t="n">
-        <v>1.005</v>
+        <v>1.045</v>
       </c>
       <c r="F20" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="G20" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="H20" t="n">
-        <v>180</v>
+        <v>1010</v>
       </c>
       <c r="I20" t="n">
-        <v>703</v>
+        <v>671</v>
       </c>
       <c r="J20" t="n">
-        <v>1.46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1128,31 +1128,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.19</v>
+        <v>0.208</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.059</v>
       </c>
       <c r="D21" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="E21" t="n">
-        <v>0.323</v>
+        <v>0.32</v>
       </c>
       <c r="F21" t="n">
-        <v>0.022</v>
+        <v>0.002</v>
       </c>
       <c r="G21" t="n">
-        <v>0.016</v>
+        <v>0.002</v>
       </c>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>707</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>793</v>
       </c>
       <c r="J21" t="n">
-        <v>1.47</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1162,16 +1162,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="C22" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="D22" t="n">
         <v>0.043</v>
       </c>
       <c r="E22" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1180,13 +1180,13 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>453</v>
+        <v>577</v>
       </c>
       <c r="I22" t="n">
-        <v>503</v>
+        <v>712</v>
       </c>
       <c r="J22" t="n">
-        <v>1.58</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.735</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.134</v>
+        <v>0.128</v>
       </c>
       <c r="D23" t="n">
-        <v>0.469</v>
+        <v>0.436</v>
       </c>
       <c r="E23" t="n">
-        <v>0.913</v>
+        <v>0.903</v>
       </c>
       <c r="F23" t="n">
-        <v>0.036</v>
+        <v>0.004</v>
       </c>
       <c r="G23" t="n">
-        <v>0.028</v>
+        <v>0.003</v>
       </c>
       <c r="H23" t="n">
-        <v>14</v>
+        <v>1188</v>
       </c>
       <c r="I23" t="n">
-        <v>703</v>
+        <v>686</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1230,16 +1230,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
       <c r="C24" t="n">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
       <c r="D24" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="E24" t="n">
-        <v>0.082</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F24" t="n">
         <v>0.001</v>
@@ -1248,13 +1248,13 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>754</v>
+        <v>1377</v>
       </c>
       <c r="I24" t="n">
-        <v>323</v>
+        <v>479</v>
       </c>
       <c r="J24" t="n">
-        <v>1.57</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="25">
@@ -1264,31 +1264,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.041</v>
+        <v>0.038</v>
       </c>
       <c r="C25" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="E25" t="n">
-        <v>0.053</v>
+        <v>0.055</v>
       </c>
       <c r="F25" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>13</v>
+        <v>1151</v>
       </c>
       <c r="I25" t="n">
-        <v>549</v>
+        <v>757</v>
       </c>
       <c r="J25" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1298,31 +1298,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="C26" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="D26" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
       <c r="E26" t="n">
-        <v>0.031</v>
+        <v>0.033</v>
       </c>
       <c r="F26" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>267</v>
+        <v>1075</v>
       </c>
       <c r="I26" t="n">
-        <v>748</v>
+        <v>647</v>
       </c>
       <c r="J26" t="n">
-        <v>1.54</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="27">
@@ -1332,31 +1332,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.961</v>
+        <v>3.183</v>
       </c>
       <c r="C27" t="n">
-        <v>0.707</v>
+        <v>0.657</v>
       </c>
       <c r="D27" t="n">
-        <v>2.039</v>
+        <v>2.044</v>
       </c>
       <c r="E27" t="n">
-        <v>4.332</v>
+        <v>4.485</v>
       </c>
       <c r="F27" t="n">
-        <v>0.198</v>
+        <v>0.018</v>
       </c>
       <c r="G27" t="n">
-        <v>0.143</v>
+        <v>0.013</v>
       </c>
       <c r="H27" t="n">
-        <v>13</v>
+        <v>1489</v>
       </c>
       <c r="I27" t="n">
-        <v>598</v>
+        <v>691</v>
       </c>
       <c r="J27" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="28">
@@ -1366,31 +1366,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="C28" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
       <c r="D28" t="n">
         <v>0.041</v>
       </c>
       <c r="E28" t="n">
-        <v>0.109</v>
+        <v>0.113</v>
       </c>
       <c r="F28" t="n">
         <v>0.001</v>
       </c>
       <c r="G28" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>376</v>
+        <v>1376</v>
       </c>
       <c r="I28" t="n">
-        <v>443</v>
+        <v>712</v>
       </c>
       <c r="J28" t="n">
-        <v>1.59</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1400,31 +1400,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.221</v>
+        <v>0.223</v>
       </c>
       <c r="C29" t="n">
-        <v>0.055</v>
+        <v>0.063</v>
       </c>
       <c r="D29" t="n">
-        <v>0.113</v>
+        <v>0.123</v>
       </c>
       <c r="E29" t="n">
-        <v>0.332</v>
+        <v>0.358</v>
       </c>
       <c r="F29" t="n">
         <v>0.002</v>
       </c>
       <c r="G29" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>1252</v>
+        <v>1409</v>
       </c>
       <c r="I29" t="n">
-        <v>633</v>
+        <v>647</v>
       </c>
       <c r="J29" t="n">
-        <v>1.55</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1434,31 +1434,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.012</v>
+        <v>1.062</v>
       </c>
       <c r="C30" t="n">
-        <v>0.202</v>
+        <v>0.209</v>
       </c>
       <c r="D30" t="n">
-        <v>0.712</v>
+        <v>0.711</v>
       </c>
       <c r="E30" t="n">
-        <v>1.427</v>
+        <v>1.453</v>
       </c>
       <c r="F30" t="n">
-        <v>0.032</v>
+        <v>0.006</v>
       </c>
       <c r="G30" t="n">
-        <v>0.023</v>
+        <v>0.005</v>
       </c>
       <c r="H30" t="n">
-        <v>48</v>
+        <v>1192</v>
       </c>
       <c r="I30" t="n">
-        <v>706</v>
+        <v>791</v>
       </c>
       <c r="J30" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1486,13 +1486,13 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>993</v>
       </c>
       <c r="I31" t="n">
-        <v>11</v>
+        <v>589</v>
       </c>
       <c r="J31" t="n">
-        <v>1.56</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1502,31 +1502,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1950229700.775</v>
+        <v>19567.849</v>
       </c>
       <c r="C32" t="n">
-        <v>3379534531.369</v>
+        <v>48793.661</v>
       </c>
       <c r="D32" t="n">
-        <v>1643.001</v>
+        <v>640.046</v>
       </c>
       <c r="E32" t="n">
-        <v>7800827984.613</v>
+        <v>65003.745</v>
       </c>
       <c r="F32" t="n">
-        <v>1669366912.208</v>
+        <v>2111.952</v>
       </c>
       <c r="G32" t="n">
-        <v>1276393665.527</v>
+        <v>1494.192</v>
       </c>
       <c r="H32" t="n">
-        <v>7</v>
+        <v>993</v>
       </c>
       <c r="I32" t="n">
-        <v>11</v>
+        <v>589</v>
       </c>
       <c r="J32" t="n">
-        <v>1.57</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/diagnostics/Bayesian_parameter(results).xlsx
+++ b/output/diagnostics/Bayesian_parameter(results).xlsx
@@ -482,28 +482,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.958</v>
+        <v>0.956</v>
       </c>
       <c r="C2" t="n">
-        <v>0.197</v>
+        <v>0.194</v>
       </c>
       <c r="D2" t="n">
-        <v>0.611</v>
+        <v>0.593</v>
       </c>
       <c r="E2" t="n">
-        <v>1.347</v>
+        <v>1.291</v>
       </c>
       <c r="F2" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.006</v>
       </c>
-      <c r="G2" t="n">
-        <v>0.004</v>
-      </c>
       <c r="H2" t="n">
-        <v>1008</v>
+        <v>780</v>
       </c>
       <c r="I2" t="n">
-        <v>846</v>
+        <v>672</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -516,31 +516,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.477</v>
+        <v>0.483</v>
       </c>
       <c r="C3" t="n">
-        <v>0.168</v>
+        <v>0.166</v>
       </c>
       <c r="D3" t="n">
-        <v>0.18</v>
+        <v>0.197</v>
       </c>
       <c r="E3" t="n">
-        <v>0.79</v>
+        <v>0.782</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="H3" t="n">
-        <v>1191</v>
+        <v>1629</v>
       </c>
       <c r="I3" t="n">
-        <v>733</v>
+        <v>577</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="4">
@@ -550,28 +550,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.449</v>
+        <v>0.442</v>
       </c>
       <c r="C4" t="n">
-        <v>0.137</v>
+        <v>0.143</v>
       </c>
       <c r="D4" t="n">
-        <v>0.223</v>
+        <v>0.219</v>
       </c>
       <c r="E4" t="n">
-        <v>0.703</v>
+        <v>0.705</v>
       </c>
       <c r="F4" t="n">
         <v>0.005</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="H4" t="n">
-        <v>889</v>
+        <v>855</v>
       </c>
       <c r="I4" t="n">
-        <v>824</v>
+        <v>660</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -584,16 +584,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.123</v>
+        <v>0.124</v>
       </c>
       <c r="C5" t="n">
         <v>0.014</v>
       </c>
       <c r="D5" t="n">
-        <v>0.097</v>
+        <v>0.1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.15</v>
+        <v>0.154</v>
       </c>
       <c r="F5" t="n">
         <v>0.001</v>
@@ -602,13 +602,13 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>575</v>
+        <v>493</v>
       </c>
       <c r="I5" t="n">
-        <v>671</v>
+        <v>477</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -618,16 +618,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.083</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C6" t="n">
         <v>0.035</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02</v>
+        <v>0.028</v>
       </c>
       <c r="E6" t="n">
-        <v>0.143</v>
+        <v>0.153</v>
       </c>
       <c r="F6" t="n">
         <v>0.001</v>
@@ -636,10 +636,10 @@
         <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>1174</v>
+        <v>1153</v>
       </c>
       <c r="I6" t="n">
-        <v>656</v>
+        <v>670</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -652,28 +652,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.247</v>
+        <v>1.258</v>
       </c>
       <c r="C7" t="n">
-        <v>0.447</v>
+        <v>0.401</v>
       </c>
       <c r="D7" t="n">
-        <v>0.537</v>
+        <v>0.554</v>
       </c>
       <c r="E7" t="n">
-        <v>2.041</v>
+        <v>2.024</v>
       </c>
       <c r="F7" t="n">
-        <v>0.015</v>
+        <v>0.013</v>
       </c>
       <c r="G7" t="n">
-        <v>0.011</v>
+        <v>0.013</v>
       </c>
       <c r="H7" t="n">
-        <v>912</v>
+        <v>876</v>
       </c>
       <c r="I7" t="n">
-        <v>724</v>
+        <v>669</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="C8" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.022</v>
+        <v>0.024</v>
       </c>
       <c r="E8" t="n">
         <v>0.057</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>922</v>
+        <v>854</v>
       </c>
       <c r="I8" t="n">
-        <v>757</v>
+        <v>746</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.256</v>
+        <v>0.259</v>
       </c>
       <c r="C9" t="n">
         <v>0.055</v>
       </c>
       <c r="D9" t="n">
-        <v>0.158</v>
+        <v>0.148</v>
       </c>
       <c r="E9" t="n">
-        <v>0.355</v>
+        <v>0.354</v>
       </c>
       <c r="F9" t="n">
         <v>0.002</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H9" t="n">
-        <v>1067</v>
+        <v>1151</v>
       </c>
       <c r="I9" t="n">
-        <v>812</v>
+        <v>740</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -754,31 +754,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="C10" t="n">
-        <v>0.074</v>
+        <v>0.075</v>
       </c>
       <c r="D10" t="n">
-        <v>0.214</v>
+        <v>0.225</v>
       </c>
       <c r="E10" t="n">
-        <v>0.489</v>
+        <v>0.498</v>
       </c>
       <c r="F10" t="n">
         <v>0.002</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="H10" t="n">
-        <v>1526</v>
+        <v>1356</v>
       </c>
       <c r="I10" t="n">
-        <v>794</v>
+        <v>606</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="11">
@@ -806,13 +806,13 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>587</v>
+        <v>503</v>
       </c>
       <c r="I11" t="n">
-        <v>732</v>
+        <v>626</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="12">
@@ -822,28 +822,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.758</v>
+        <v>0.755</v>
       </c>
       <c r="C12" t="n">
-        <v>0.265</v>
+        <v>0.257</v>
       </c>
       <c r="D12" t="n">
-        <v>0.321</v>
+        <v>0.343</v>
       </c>
       <c r="E12" t="n">
-        <v>1.262</v>
+        <v>1.266</v>
       </c>
       <c r="F12" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>808</v>
+        <v>737</v>
       </c>
       <c r="I12" t="n">
-        <v>547</v>
+        <v>519</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -856,28 +856,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.172</v>
+        <v>0.177</v>
       </c>
       <c r="C13" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.089</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="E13" t="n">
-        <v>0.329</v>
+        <v>0.338</v>
       </c>
       <c r="F13" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G13" t="n">
         <v>0.003</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.002</v>
-      </c>
       <c r="H13" t="n">
-        <v>1100</v>
+        <v>1399</v>
       </c>
       <c r="I13" t="n">
-        <v>706</v>
+        <v>831</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -890,31 +890,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.44</v>
+        <v>1.405</v>
       </c>
       <c r="C14" t="n">
-        <v>0.593</v>
+        <v>0.569</v>
       </c>
       <c r="D14" t="n">
-        <v>0.527</v>
+        <v>0.492</v>
       </c>
       <c r="E14" t="n">
-        <v>2.588</v>
+        <v>2.452</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02</v>
+        <v>0.022</v>
       </c>
       <c r="G14" t="n">
-        <v>0.014</v>
+        <v>0.017</v>
       </c>
       <c r="H14" t="n">
-        <v>802</v>
+        <v>607</v>
       </c>
       <c r="I14" t="n">
-        <v>755</v>
+        <v>500</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="15">
@@ -924,28 +924,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.422</v>
+        <v>2.418</v>
       </c>
       <c r="C15" t="n">
-        <v>0.533</v>
+        <v>0.521</v>
       </c>
       <c r="D15" t="n">
-        <v>1.462</v>
+        <v>1.477</v>
       </c>
       <c r="E15" t="n">
-        <v>3.456</v>
+        <v>3.424</v>
       </c>
       <c r="F15" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01</v>
+        <v>0.018</v>
       </c>
       <c r="H15" t="n">
-        <v>1413</v>
+        <v>1046</v>
       </c>
       <c r="I15" t="n">
-        <v>591</v>
+        <v>713</v>
       </c>
       <c r="J15" t="n">
         <v>1.01</v>
@@ -958,31 +958,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.097</v>
+        <v>3.044</v>
       </c>
       <c r="C16" t="n">
-        <v>1.141</v>
+        <v>1.179</v>
       </c>
       <c r="D16" t="n">
-        <v>1.505</v>
+        <v>1.501</v>
       </c>
       <c r="E16" t="n">
-        <v>5.117</v>
+        <v>5.213</v>
       </c>
       <c r="F16" t="n">
-        <v>0.04</v>
+        <v>0.046</v>
       </c>
       <c r="G16" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="H16" t="n">
-        <v>806</v>
+        <v>612</v>
       </c>
       <c r="I16" t="n">
-        <v>575</v>
+        <v>379</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="17">
@@ -992,31 +992,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.539</v>
+        <v>0.524</v>
       </c>
       <c r="C17" t="n">
-        <v>0.307</v>
+        <v>0.308</v>
       </c>
       <c r="D17" t="n">
-        <v>0.074</v>
+        <v>0.017</v>
       </c>
       <c r="E17" t="n">
-        <v>1.094</v>
+        <v>1.046</v>
       </c>
       <c r="F17" t="n">
         <v>0.01</v>
       </c>
       <c r="G17" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="H17" t="n">
-        <v>865</v>
+        <v>875</v>
       </c>
       <c r="I17" t="n">
-        <v>737</v>
+        <v>587</v>
       </c>
       <c r="J17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1026,31 +1026,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.576</v>
+        <v>0.591</v>
       </c>
       <c r="C18" t="n">
-        <v>0.264</v>
+        <v>0.3</v>
       </c>
       <c r="D18" t="n">
-        <v>0.155</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="F18" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="H18" t="n">
-        <v>1061</v>
+        <v>1123</v>
       </c>
       <c r="I18" t="n">
-        <v>588</v>
+        <v>524</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="19">
@@ -1060,31 +1060,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22.687</v>
+        <v>22.692</v>
       </c>
       <c r="C19" t="n">
-        <v>1.769</v>
+        <v>1.774</v>
       </c>
       <c r="D19" t="n">
-        <v>20.02</v>
+        <v>20.002</v>
       </c>
       <c r="E19" t="n">
-        <v>25.532</v>
+        <v>25.639</v>
       </c>
       <c r="F19" t="n">
-        <v>0.049</v>
+        <v>0.056</v>
       </c>
       <c r="G19" t="n">
-        <v>0.035</v>
+        <v>0.036</v>
       </c>
       <c r="H19" t="n">
-        <v>1251</v>
+        <v>931</v>
       </c>
       <c r="I19" t="n">
-        <v>693</v>
+        <v>736</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="20">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.666</v>
+        <v>0.674</v>
       </c>
       <c r="C20" t="n">
-        <v>0.194</v>
+        <v>0.19</v>
       </c>
       <c r="D20" t="n">
-        <v>0.349</v>
+        <v>0.316</v>
       </c>
       <c r="E20" t="n">
-        <v>1.045</v>
+        <v>1.006</v>
       </c>
       <c r="F20" t="n">
         <v>0.006</v>
       </c>
       <c r="G20" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="H20" t="n">
-        <v>1010</v>
+        <v>1019</v>
       </c>
       <c r="I20" t="n">
-        <v>671</v>
+        <v>815</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -1128,28 +1128,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.208</v>
+        <v>0.213</v>
       </c>
       <c r="C21" t="n">
-        <v>0.059</v>
+        <v>0.061</v>
       </c>
       <c r="D21" t="n">
-        <v>0.114</v>
+        <v>0.122</v>
       </c>
       <c r="E21" t="n">
-        <v>0.32</v>
+        <v>0.331</v>
       </c>
       <c r="F21" t="n">
         <v>0.002</v>
       </c>
       <c r="G21" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H21" t="n">
-        <v>707</v>
+        <v>900</v>
       </c>
       <c r="I21" t="n">
-        <v>793</v>
+        <v>664</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -1171,7 +1171,7 @@
         <v>0.043</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1180,13 +1180,13 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>577</v>
+        <v>505</v>
       </c>
       <c r="I22" t="n">
-        <v>712</v>
+        <v>662</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="23">
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.128</v>
+        <v>0.131</v>
       </c>
       <c r="D23" t="n">
-        <v>0.436</v>
+        <v>0.461</v>
       </c>
       <c r="E23" t="n">
-        <v>0.903</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="F23" t="n">
         <v>0.004</v>
       </c>
       <c r="G23" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H23" t="n">
-        <v>1188</v>
+        <v>1152</v>
       </c>
       <c r="I23" t="n">
-        <v>686</v>
+        <v>671</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -1230,31 +1230,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.049</v>
+        <v>0.052</v>
       </c>
       <c r="C24" t="n">
         <v>0.019</v>
       </c>
       <c r="D24" t="n">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F24" t="n">
         <v>0.001</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>1377</v>
+        <v>1178</v>
       </c>
       <c r="I24" t="n">
-        <v>479</v>
+        <v>503</v>
       </c>
       <c r="J24" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1270,10 +1270,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="E25" t="n">
-        <v>0.055</v>
+        <v>0.053</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1282,10 +1282,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1151</v>
+        <v>1111</v>
       </c>
       <c r="I25" t="n">
-        <v>757</v>
+        <v>782</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -1304,10 +1304,10 @@
         <v>0.006</v>
       </c>
       <c r="D26" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="E26" t="n">
-        <v>0.033</v>
+        <v>0.034</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1316,13 +1316,13 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1075</v>
+        <v>1124</v>
       </c>
       <c r="I26" t="n">
-        <v>647</v>
+        <v>572</v>
       </c>
       <c r="J26" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1332,31 +1332,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.183</v>
+        <v>3.218</v>
       </c>
       <c r="C27" t="n">
-        <v>0.657</v>
+        <v>0.653</v>
       </c>
       <c r="D27" t="n">
-        <v>2.044</v>
+        <v>2.109</v>
       </c>
       <c r="E27" t="n">
-        <v>4.485</v>
+        <v>4.434</v>
       </c>
       <c r="F27" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="G27" t="n">
-        <v>0.013</v>
+        <v>0.019</v>
       </c>
       <c r="H27" t="n">
-        <v>1489</v>
+        <v>1564</v>
       </c>
       <c r="I27" t="n">
-        <v>691</v>
+        <v>901</v>
       </c>
       <c r="J27" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1369,25 +1369,25 @@
         <v>0.076</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="D28" t="n">
-        <v>0.041</v>
+        <v>0.046</v>
       </c>
       <c r="E28" t="n">
-        <v>0.113</v>
+        <v>0.112</v>
       </c>
       <c r="F28" t="n">
         <v>0.001</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>1376</v>
+        <v>1450</v>
       </c>
       <c r="I28" t="n">
-        <v>712</v>
+        <v>837</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -1400,28 +1400,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.223</v>
+        <v>0.228</v>
       </c>
       <c r="C29" t="n">
-        <v>0.063</v>
+        <v>0.059</v>
       </c>
       <c r="D29" t="n">
-        <v>0.123</v>
+        <v>0.12</v>
       </c>
       <c r="E29" t="n">
-        <v>0.358</v>
+        <v>0.339</v>
       </c>
       <c r="F29" t="n">
         <v>0.002</v>
       </c>
       <c r="G29" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H29" t="n">
-        <v>1409</v>
+        <v>1137</v>
       </c>
       <c r="I29" t="n">
-        <v>647</v>
+        <v>746</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -1434,28 +1434,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.062</v>
+        <v>1.049</v>
       </c>
       <c r="C30" t="n">
-        <v>0.209</v>
+        <v>0.212</v>
       </c>
       <c r="D30" t="n">
-        <v>0.711</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>1.453</v>
+        <v>1.467</v>
       </c>
       <c r="F30" t="n">
         <v>0.006</v>
       </c>
       <c r="G30" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="H30" t="n">
-        <v>1192</v>
+        <v>1214</v>
       </c>
       <c r="I30" t="n">
-        <v>791</v>
+        <v>672</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -1486,10 +1486,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>993</v>
+        <v>707</v>
       </c>
       <c r="I31" t="n">
-        <v>589</v>
+        <v>440</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -1502,31 +1502,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>19567.849</v>
+        <v>135925.22</v>
       </c>
       <c r="C32" t="n">
-        <v>48793.661</v>
+        <v>1826803.736</v>
       </c>
       <c r="D32" t="n">
-        <v>640.046</v>
+        <v>577.106</v>
       </c>
       <c r="E32" t="n">
-        <v>65003.745</v>
+        <v>110364.044</v>
       </c>
       <c r="F32" t="n">
-        <v>2111.952</v>
+        <v>72592.818</v>
       </c>
       <c r="G32" t="n">
-        <v>1494.192</v>
+        <v>640158.107</v>
       </c>
       <c r="H32" t="n">
-        <v>993</v>
+        <v>707</v>
       </c>
       <c r="I32" t="n">
-        <v>589</v>
+        <v>440</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
   </sheetData>

--- a/output/diagnostics/Bayesian_parameter(results).xlsx
+++ b/output/diagnostics/Bayesian_parameter(results).xlsx
@@ -482,28 +482,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.956</v>
+        <v>0.966</v>
       </c>
       <c r="C2" t="n">
-        <v>0.194</v>
+        <v>0.201</v>
       </c>
       <c r="D2" t="n">
-        <v>0.593</v>
+        <v>0.595</v>
       </c>
       <c r="E2" t="n">
-        <v>1.291</v>
+        <v>1.319</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="G2" t="n">
         <v>0.006</v>
       </c>
       <c r="H2" t="n">
-        <v>780</v>
+        <v>1157</v>
       </c>
       <c r="I2" t="n">
-        <v>672</v>
+        <v>653</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -516,31 +516,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.483</v>
+        <v>0.475</v>
       </c>
       <c r="C3" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="D3" t="n">
-        <v>0.197</v>
+        <v>0.188</v>
       </c>
       <c r="E3" t="n">
-        <v>0.782</v>
+        <v>0.757</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="G3" t="n">
         <v>0.006</v>
       </c>
       <c r="H3" t="n">
-        <v>1629</v>
+        <v>1210</v>
       </c>
       <c r="I3" t="n">
-        <v>577</v>
+        <v>738</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -550,28 +550,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.442</v>
+        <v>0.44</v>
       </c>
       <c r="C4" t="n">
-        <v>0.143</v>
+        <v>0.14</v>
       </c>
       <c r="D4" t="n">
-        <v>0.219</v>
+        <v>0.213</v>
       </c>
       <c r="E4" t="n">
-        <v>0.705</v>
+        <v>0.697</v>
       </c>
       <c r="F4" t="n">
         <v>0.005</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="H4" t="n">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="I4" t="n">
-        <v>660</v>
+        <v>615</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -584,16 +584,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.124</v>
+        <v>0.119</v>
       </c>
       <c r="C5" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.154</v>
+        <v>0.145</v>
       </c>
       <c r="F5" t="n">
         <v>0.001</v>
@@ -602,13 +602,13 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>493</v>
+        <v>439</v>
       </c>
       <c r="I5" t="n">
-        <v>477</v>
+        <v>529</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="6">
@@ -618,16 +618,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>0.035</v>
+        <v>0.037</v>
       </c>
       <c r="D6" t="n">
-        <v>0.028</v>
+        <v>0.021</v>
       </c>
       <c r="E6" t="n">
-        <v>0.153</v>
+        <v>0.15</v>
       </c>
       <c r="F6" t="n">
         <v>0.001</v>
@@ -636,10 +636,10 @@
         <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>1153</v>
+        <v>1276</v>
       </c>
       <c r="I6" t="n">
-        <v>670</v>
+        <v>687</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -652,31 +652,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.258</v>
+        <v>1.266</v>
       </c>
       <c r="C7" t="n">
-        <v>0.401</v>
+        <v>0.467</v>
       </c>
       <c r="D7" t="n">
-        <v>0.554</v>
+        <v>0.502</v>
       </c>
       <c r="E7" t="n">
-        <v>2.024</v>
+        <v>2.07</v>
       </c>
       <c r="F7" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
       <c r="G7" t="n">
-        <v>0.013</v>
+        <v>0.023</v>
       </c>
       <c r="H7" t="n">
-        <v>876</v>
+        <v>1014</v>
       </c>
       <c r="I7" t="n">
-        <v>669</v>
+        <v>714</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="8">
@@ -689,13 +689,13 @@
         <v>0.041</v>
       </c>
       <c r="C8" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="D8" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="E8" t="n">
-        <v>0.057</v>
+        <v>0.059</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>854</v>
+        <v>1051</v>
       </c>
       <c r="I8" t="n">
-        <v>746</v>
+        <v>660</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.259</v>
+        <v>0.252</v>
       </c>
       <c r="C9" t="n">
         <v>0.055</v>
       </c>
       <c r="D9" t="n">
-        <v>0.148</v>
+        <v>0.145</v>
       </c>
       <c r="E9" t="n">
-        <v>0.354</v>
+        <v>0.349</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="G9" t="n">
         <v>0.002</v>
       </c>
       <c r="H9" t="n">
-        <v>1151</v>
+        <v>1448</v>
       </c>
       <c r="I9" t="n">
-        <v>740</v>
+        <v>856</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="10">
@@ -754,31 +754,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.355</v>
+        <v>0.359</v>
       </c>
       <c r="C10" t="n">
         <v>0.075</v>
       </c>
       <c r="D10" t="n">
-        <v>0.225</v>
+        <v>0.213</v>
       </c>
       <c r="E10" t="n">
-        <v>0.498</v>
+        <v>0.49</v>
       </c>
       <c r="F10" t="n">
         <v>0.002</v>
       </c>
       <c r="G10" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H10" t="n">
-        <v>1356</v>
+        <v>1198</v>
       </c>
       <c r="I10" t="n">
-        <v>606</v>
+        <v>738</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -806,10 +806,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>503</v>
+        <v>462</v>
       </c>
       <c r="I11" t="n">
-        <v>626</v>
+        <v>666</v>
       </c>
       <c r="J11" t="n">
         <v>1.01</v>
@@ -822,28 +822,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.755</v>
+        <v>0.756</v>
       </c>
       <c r="C12" t="n">
-        <v>0.257</v>
+        <v>0.252</v>
       </c>
       <c r="D12" t="n">
-        <v>0.343</v>
+        <v>0.334</v>
       </c>
       <c r="E12" t="n">
-        <v>1.266</v>
+        <v>1.222</v>
       </c>
       <c r="F12" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="G12" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="H12" t="n">
-        <v>737</v>
+        <v>1403</v>
       </c>
       <c r="I12" t="n">
-        <v>519</v>
+        <v>850</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -856,28 +856,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.177</v>
+        <v>0.169</v>
       </c>
       <c r="C13" t="n">
-        <v>0.089</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.025</v>
+        <v>0.021</v>
       </c>
       <c r="E13" t="n">
-        <v>0.338</v>
+        <v>0.321</v>
       </c>
       <c r="F13" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="G13" t="n">
         <v>0.003</v>
       </c>
       <c r="H13" t="n">
-        <v>1399</v>
+        <v>1010</v>
       </c>
       <c r="I13" t="n">
-        <v>831</v>
+        <v>476</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -890,28 +890,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.405</v>
+        <v>1.486</v>
       </c>
       <c r="C14" t="n">
-        <v>0.569</v>
+        <v>0.644</v>
       </c>
       <c r="D14" t="n">
-        <v>0.492</v>
+        <v>0.402</v>
       </c>
       <c r="E14" t="n">
-        <v>2.452</v>
+        <v>2.673</v>
       </c>
       <c r="F14" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="G14" t="n">
-        <v>0.017</v>
+        <v>0.024</v>
       </c>
       <c r="H14" t="n">
-        <v>607</v>
+        <v>769</v>
       </c>
       <c r="I14" t="n">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="J14" t="n">
         <v>1.01</v>
@@ -924,31 +924,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.418</v>
+        <v>2.405</v>
       </c>
       <c r="C15" t="n">
-        <v>0.521</v>
+        <v>0.516</v>
       </c>
       <c r="D15" t="n">
-        <v>1.477</v>
+        <v>1.406</v>
       </c>
       <c r="E15" t="n">
-        <v>3.424</v>
+        <v>3.324</v>
       </c>
       <c r="F15" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="G15" t="n">
         <v>0.016</v>
       </c>
-      <c r="G15" t="n">
-        <v>0.018</v>
-      </c>
       <c r="H15" t="n">
-        <v>1046</v>
+        <v>1242</v>
       </c>
       <c r="I15" t="n">
-        <v>713</v>
+        <v>801</v>
       </c>
       <c r="J15" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -958,31 +958,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.044</v>
+        <v>3.203</v>
       </c>
       <c r="C16" t="n">
-        <v>1.179</v>
+        <v>1.206</v>
       </c>
       <c r="D16" t="n">
-        <v>1.501</v>
+        <v>1.505</v>
       </c>
       <c r="E16" t="n">
-        <v>5.213</v>
+        <v>5.333</v>
       </c>
       <c r="F16" t="n">
-        <v>0.046</v>
+        <v>0.039</v>
       </c>
       <c r="G16" t="n">
-        <v>0.029</v>
+        <v>0.027</v>
       </c>
       <c r="H16" t="n">
-        <v>612</v>
+        <v>947</v>
       </c>
       <c r="I16" t="n">
-        <v>379</v>
+        <v>710</v>
       </c>
       <c r="J16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -992,28 +992,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.524</v>
+        <v>0.665</v>
       </c>
       <c r="C17" t="n">
-        <v>0.308</v>
+        <v>0.294</v>
       </c>
       <c r="D17" t="n">
-        <v>0.017</v>
+        <v>0.165</v>
       </c>
       <c r="E17" t="n">
-        <v>1.046</v>
+        <v>1.185</v>
       </c>
       <c r="F17" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="G17" t="n">
         <v>0.01</v>
       </c>
-      <c r="G17" t="n">
-        <v>0.011</v>
-      </c>
       <c r="H17" t="n">
-        <v>875</v>
+        <v>728</v>
       </c>
       <c r="I17" t="n">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -1026,31 +1026,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.591</v>
+        <v>0.585</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3</v>
+        <v>0.264</v>
       </c>
       <c r="D18" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="E18" t="n">
-        <v>1.09</v>
+        <v>1.046</v>
       </c>
       <c r="F18" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="H18" t="n">
-        <v>1123</v>
+        <v>1071</v>
       </c>
       <c r="I18" t="n">
-        <v>524</v>
+        <v>675</v>
       </c>
       <c r="J18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1060,28 +1060,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22.692</v>
+        <v>22.558</v>
       </c>
       <c r="C19" t="n">
-        <v>1.774</v>
+        <v>1.711</v>
       </c>
       <c r="D19" t="n">
-        <v>20.002</v>
+        <v>20.007</v>
       </c>
       <c r="E19" t="n">
-        <v>25.639</v>
+        <v>25.468</v>
       </c>
       <c r="F19" t="n">
-        <v>0.056</v>
+        <v>0.054</v>
       </c>
       <c r="G19" t="n">
-        <v>0.036</v>
+        <v>0.041</v>
       </c>
       <c r="H19" t="n">
-        <v>931</v>
+        <v>966</v>
       </c>
       <c r="I19" t="n">
-        <v>736</v>
+        <v>606</v>
       </c>
       <c r="J19" t="n">
         <v>1.01</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.674</v>
+        <v>0.663</v>
       </c>
       <c r="C20" t="n">
-        <v>0.19</v>
+        <v>0.207</v>
       </c>
       <c r="D20" t="n">
-        <v>0.316</v>
+        <v>0.319</v>
       </c>
       <c r="E20" t="n">
-        <v>1.006</v>
+        <v>1.052</v>
       </c>
       <c r="F20" t="n">
         <v>0.006</v>
       </c>
       <c r="G20" t="n">
-        <v>0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>1019</v>
+        <v>1219</v>
       </c>
       <c r="I20" t="n">
-        <v>815</v>
+        <v>740</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="21">
@@ -1128,28 +1128,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.213</v>
+        <v>0.227</v>
       </c>
       <c r="C21" t="n">
-        <v>0.061</v>
+        <v>0.062</v>
       </c>
       <c r="D21" t="n">
         <v>0.122</v>
       </c>
       <c r="E21" t="n">
-        <v>0.331</v>
+        <v>0.341</v>
       </c>
       <c r="F21" t="n">
         <v>0.002</v>
       </c>
       <c r="G21" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H21" t="n">
-        <v>900</v>
+        <v>834</v>
       </c>
       <c r="I21" t="n">
-        <v>664</v>
+        <v>675</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>505</v>
+        <v>461</v>
       </c>
       <c r="I22" t="n">
-        <v>662</v>
+        <v>688</v>
       </c>
       <c r="J22" t="n">
         <v>1.01</v>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="D23" t="n">
-        <v>0.461</v>
+        <v>0.435</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="F23" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="G23" t="n">
         <v>0.004</v>
       </c>
       <c r="H23" t="n">
-        <v>1152</v>
+        <v>1458</v>
       </c>
       <c r="I23" t="n">
-        <v>671</v>
+        <v>594</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="24">
@@ -1230,16 +1230,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.052</v>
+        <v>0.05</v>
       </c>
       <c r="C24" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="D24" t="n">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="F24" t="n">
         <v>0.001</v>
@@ -1248,13 +1248,13 @@
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>1178</v>
+        <v>1476</v>
       </c>
       <c r="I24" t="n">
-        <v>503</v>
+        <v>475</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="25">
@@ -1273,7 +1273,7 @@
         <v>0.022</v>
       </c>
       <c r="E25" t="n">
-        <v>0.053</v>
+        <v>0.054</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1282,10 +1282,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1111</v>
+        <v>1478</v>
       </c>
       <c r="I25" t="n">
-        <v>782</v>
+        <v>724</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -1298,13 +1298,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="C26" t="n">
         <v>0.006</v>
       </c>
       <c r="D26" t="n">
-        <v>0.012</v>
+        <v>0.014</v>
       </c>
       <c r="E26" t="n">
         <v>0.034</v>
@@ -1316,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1124</v>
+        <v>2199</v>
       </c>
       <c r="I26" t="n">
-        <v>572</v>
+        <v>751</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -1332,31 +1332,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.218</v>
+        <v>3.163</v>
       </c>
       <c r="C27" t="n">
-        <v>0.653</v>
+        <v>0.617</v>
       </c>
       <c r="D27" t="n">
-        <v>2.109</v>
+        <v>2.152</v>
       </c>
       <c r="E27" t="n">
-        <v>4.434</v>
+        <v>4.365</v>
       </c>
       <c r="F27" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="G27" t="n">
-        <v>0.019</v>
+        <v>0.023</v>
       </c>
       <c r="H27" t="n">
-        <v>1564</v>
+        <v>1624</v>
       </c>
       <c r="I27" t="n">
-        <v>901</v>
+        <v>793</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="28">
@@ -1369,13 +1369,13 @@
         <v>0.076</v>
       </c>
       <c r="C28" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="D28" t="n">
-        <v>0.046</v>
+        <v>0.043</v>
       </c>
       <c r="E28" t="n">
-        <v>0.112</v>
+        <v>0.11</v>
       </c>
       <c r="F28" t="n">
         <v>0.001</v>
@@ -1384,10 +1384,10 @@
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>1450</v>
+        <v>1129</v>
       </c>
       <c r="I28" t="n">
-        <v>837</v>
+        <v>750</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.228</v>
+        <v>0.223</v>
       </c>
       <c r="C29" t="n">
-        <v>0.059</v>
+        <v>0.063</v>
       </c>
       <c r="D29" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="E29" t="n">
-        <v>0.339</v>
+        <v>0.334</v>
       </c>
       <c r="F29" t="n">
         <v>0.002</v>
@@ -1418,10 +1418,10 @@
         <v>0.002</v>
       </c>
       <c r="H29" t="n">
-        <v>1137</v>
+        <v>1144</v>
       </c>
       <c r="I29" t="n">
-        <v>746</v>
+        <v>654</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -1434,28 +1434,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.049</v>
+        <v>1.054</v>
       </c>
       <c r="C30" t="n">
-        <v>0.212</v>
+        <v>0.209</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.702</v>
       </c>
       <c r="E30" t="n">
-        <v>1.467</v>
+        <v>1.461</v>
       </c>
       <c r="F30" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="G30" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="H30" t="n">
-        <v>1214</v>
+        <v>1857</v>
       </c>
       <c r="I30" t="n">
-        <v>672</v>
+        <v>834</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -1486,10 +1486,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>707</v>
+        <v>745</v>
       </c>
       <c r="I31" t="n">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -1502,31 +1502,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>135925.22</v>
+        <v>19507.604</v>
       </c>
       <c r="C32" t="n">
-        <v>1826803.736</v>
+        <v>66975.349</v>
       </c>
       <c r="D32" t="n">
-        <v>577.106</v>
+        <v>727.14</v>
       </c>
       <c r="E32" t="n">
-        <v>110364.044</v>
+        <v>50288.463</v>
       </c>
       <c r="F32" t="n">
-        <v>72592.818</v>
+        <v>3677.31</v>
       </c>
       <c r="G32" t="n">
-        <v>640158.107</v>
+        <v>16221.246</v>
       </c>
       <c r="H32" t="n">
-        <v>707</v>
+        <v>745</v>
       </c>
       <c r="I32" t="n">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="J32" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/diagnostics/Bayesian_parameter(results).xlsx
+++ b/output/diagnostics/Bayesian_parameter(results).xlsx
@@ -482,16 +482,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.966</v>
+        <v>0.953</v>
       </c>
       <c r="C2" t="n">
-        <v>0.201</v>
+        <v>0.204</v>
       </c>
       <c r="D2" t="n">
-        <v>0.595</v>
+        <v>0.579</v>
       </c>
       <c r="E2" t="n">
-        <v>1.319</v>
+        <v>1.321</v>
       </c>
       <c r="F2" t="n">
         <v>0.006</v>
@@ -500,13 +500,13 @@
         <v>0.006</v>
       </c>
       <c r="H2" t="n">
-        <v>1157</v>
+        <v>1188</v>
       </c>
       <c r="I2" t="n">
-        <v>653</v>
+        <v>808</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="3">
@@ -516,16 +516,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.475</v>
+        <v>0.47</v>
       </c>
       <c r="C3" t="n">
         <v>0.165</v>
       </c>
       <c r="D3" t="n">
-        <v>0.188</v>
+        <v>0.206</v>
       </c>
       <c r="E3" t="n">
-        <v>0.757</v>
+        <v>0.78</v>
       </c>
       <c r="F3" t="n">
         <v>0.005</v>
@@ -534,10 +534,10 @@
         <v>0.006</v>
       </c>
       <c r="H3" t="n">
-        <v>1210</v>
+        <v>1061</v>
       </c>
       <c r="I3" t="n">
-        <v>738</v>
+        <v>527</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -550,28 +550,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.44</v>
+        <v>0.432</v>
       </c>
       <c r="C4" t="n">
-        <v>0.14</v>
+        <v>0.132</v>
       </c>
       <c r="D4" t="n">
-        <v>0.213</v>
+        <v>0.225</v>
       </c>
       <c r="E4" t="n">
-        <v>0.697</v>
+        <v>0.669</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="H4" t="n">
-        <v>854</v>
+        <v>1258</v>
       </c>
       <c r="I4" t="n">
-        <v>615</v>
+        <v>880</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -587,13 +587,13 @@
         <v>0.119</v>
       </c>
       <c r="C5" t="n">
-        <v>0.015</v>
+        <v>0.016</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="E5" t="n">
-        <v>0.145</v>
+        <v>0.146</v>
       </c>
       <c r="F5" t="n">
         <v>0.001</v>
@@ -602,10 +602,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>439</v>
+        <v>489</v>
       </c>
       <c r="I5" t="n">
-        <v>529</v>
+        <v>742</v>
       </c>
       <c r="J5" t="n">
         <v>1.01</v>
@@ -618,16 +618,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.037</v>
+        <v>0.034</v>
       </c>
       <c r="D6" t="n">
-        <v>0.021</v>
+        <v>0.028</v>
       </c>
       <c r="E6" t="n">
-        <v>0.15</v>
+        <v>0.144</v>
       </c>
       <c r="F6" t="n">
         <v>0.001</v>
@@ -636,10 +636,10 @@
         <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>1276</v>
+        <v>1157</v>
       </c>
       <c r="I6" t="n">
-        <v>687</v>
+        <v>770</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -652,31 +652,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.266</v>
+        <v>1.282</v>
       </c>
       <c r="C7" t="n">
-        <v>0.467</v>
+        <v>0.461</v>
       </c>
       <c r="D7" t="n">
-        <v>0.502</v>
+        <v>0.508</v>
       </c>
       <c r="E7" t="n">
-        <v>2.07</v>
+        <v>2.084</v>
       </c>
       <c r="F7" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="G7" t="n">
-        <v>0.023</v>
+        <v>0.016</v>
       </c>
       <c r="H7" t="n">
-        <v>1014</v>
+        <v>1543</v>
       </c>
       <c r="I7" t="n">
-        <v>714</v>
+        <v>747</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="C8" t="n">
         <v>0.01</v>
       </c>
       <c r="D8" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="E8" t="n">
         <v>0.059</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1051</v>
+        <v>975</v>
       </c>
       <c r="I8" t="n">
-        <v>660</v>
+        <v>783</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.252</v>
+        <v>0.253</v>
       </c>
       <c r="C9" t="n">
-        <v>0.055</v>
+        <v>0.057</v>
       </c>
       <c r="D9" t="n">
-        <v>0.145</v>
+        <v>0.154</v>
       </c>
       <c r="E9" t="n">
-        <v>0.349</v>
+        <v>0.366</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="G9" t="n">
         <v>0.002</v>
       </c>
       <c r="H9" t="n">
-        <v>1448</v>
+        <v>1214</v>
       </c>
       <c r="I9" t="n">
-        <v>856</v>
+        <v>781</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -754,16 +754,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.359</v>
+        <v>0.355</v>
       </c>
       <c r="C10" t="n">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.213</v>
+        <v>0.236</v>
       </c>
       <c r="E10" t="n">
-        <v>0.49</v>
+        <v>0.489</v>
       </c>
       <c r="F10" t="n">
         <v>0.002</v>
@@ -772,10 +772,10 @@
         <v>0.002</v>
       </c>
       <c r="H10" t="n">
-        <v>1198</v>
+        <v>1653</v>
       </c>
       <c r="I10" t="n">
-        <v>738</v>
+        <v>946</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -794,7 +794,7 @@
         <v>0.005</v>
       </c>
       <c r="D11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="E11" t="n">
         <v>0.026</v>
@@ -806,10 +806,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>462</v>
+        <v>570</v>
       </c>
       <c r="I11" t="n">
-        <v>666</v>
+        <v>547</v>
       </c>
       <c r="J11" t="n">
         <v>1.01</v>
@@ -825,13 +825,13 @@
         <v>0.756</v>
       </c>
       <c r="C12" t="n">
-        <v>0.252</v>
+        <v>0.248</v>
       </c>
       <c r="D12" t="n">
-        <v>0.334</v>
+        <v>0.317</v>
       </c>
       <c r="E12" t="n">
-        <v>1.222</v>
+        <v>1.235</v>
       </c>
       <c r="F12" t="n">
         <v>0.007</v>
@@ -840,13 +840,13 @@
         <v>0.008</v>
       </c>
       <c r="H12" t="n">
-        <v>1403</v>
+        <v>1189</v>
       </c>
       <c r="I12" t="n">
-        <v>850</v>
+        <v>600</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="13">
@@ -856,28 +856,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.169</v>
+        <v>0.175</v>
       </c>
       <c r="C13" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.091</v>
       </c>
       <c r="D13" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>0.321</v>
+        <v>0.336</v>
       </c>
       <c r="F13" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="G13" t="n">
         <v>0.003</v>
       </c>
       <c r="H13" t="n">
-        <v>1010</v>
+        <v>1324</v>
       </c>
       <c r="I13" t="n">
-        <v>476</v>
+        <v>664</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -890,31 +890,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.486</v>
+        <v>1.544</v>
       </c>
       <c r="C14" t="n">
-        <v>0.644</v>
+        <v>0.655</v>
       </c>
       <c r="D14" t="n">
-        <v>0.402</v>
+        <v>0.492</v>
       </c>
       <c r="E14" t="n">
-        <v>2.673</v>
+        <v>2.839</v>
       </c>
       <c r="F14" t="n">
-        <v>0.023</v>
+        <v>0.019</v>
       </c>
       <c r="G14" t="n">
-        <v>0.024</v>
+        <v>0.019</v>
       </c>
       <c r="H14" t="n">
-        <v>769</v>
+        <v>1145</v>
       </c>
       <c r="I14" t="n">
-        <v>516</v>
+        <v>644</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -924,28 +924,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.405</v>
+        <v>2.415</v>
       </c>
       <c r="C15" t="n">
-        <v>0.516</v>
+        <v>0.538</v>
       </c>
       <c r="D15" t="n">
-        <v>1.406</v>
+        <v>1.465</v>
       </c>
       <c r="E15" t="n">
-        <v>3.324</v>
+        <v>3.396</v>
       </c>
       <c r="F15" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="G15" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="H15" t="n">
-        <v>1242</v>
+        <v>1221</v>
       </c>
       <c r="I15" t="n">
-        <v>801</v>
+        <v>717</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -958,31 +958,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.203</v>
+        <v>3.259</v>
       </c>
       <c r="C16" t="n">
-        <v>1.206</v>
+        <v>1.248</v>
       </c>
       <c r="D16" t="n">
-        <v>1.505</v>
+        <v>1.508</v>
       </c>
       <c r="E16" t="n">
-        <v>5.333</v>
+        <v>5.466</v>
       </c>
       <c r="F16" t="n">
-        <v>0.039</v>
+        <v>0.035</v>
       </c>
       <c r="G16" t="n">
         <v>0.027</v>
       </c>
       <c r="H16" t="n">
-        <v>947</v>
+        <v>1313</v>
       </c>
       <c r="I16" t="n">
-        <v>710</v>
+        <v>628</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="17">
@@ -992,28 +992,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.665</v>
+        <v>0.646</v>
       </c>
       <c r="C17" t="n">
-        <v>0.294</v>
+        <v>0.299</v>
       </c>
       <c r="D17" t="n">
-        <v>0.165</v>
+        <v>0.17</v>
       </c>
       <c r="E17" t="n">
-        <v>1.185</v>
+        <v>1.224</v>
       </c>
       <c r="F17" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>728</v>
+        <v>803</v>
       </c>
       <c r="I17" t="n">
-        <v>596</v>
+        <v>559</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -1026,28 +1026,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.585</v>
+        <v>0.597</v>
       </c>
       <c r="C18" t="n">
-        <v>0.264</v>
+        <v>0.283</v>
       </c>
       <c r="D18" t="n">
-        <v>0.14</v>
+        <v>0.152</v>
       </c>
       <c r="E18" t="n">
-        <v>1.046</v>
+        <v>1.082</v>
       </c>
       <c r="F18" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="G18" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>1071</v>
+        <v>1455</v>
       </c>
       <c r="I18" t="n">
-        <v>675</v>
+        <v>742</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -1060,31 +1060,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22.558</v>
+        <v>22.541</v>
       </c>
       <c r="C19" t="n">
-        <v>1.711</v>
+        <v>1.671</v>
       </c>
       <c r="D19" t="n">
-        <v>20.007</v>
+        <v>20.001</v>
       </c>
       <c r="E19" t="n">
-        <v>25.468</v>
+        <v>25.424</v>
       </c>
       <c r="F19" t="n">
-        <v>0.054</v>
+        <v>0.042</v>
       </c>
       <c r="G19" t="n">
-        <v>0.041</v>
+        <v>0.04</v>
       </c>
       <c r="H19" t="n">
-        <v>966</v>
+        <v>1409</v>
       </c>
       <c r="I19" t="n">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="J19" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1097,28 +1097,28 @@
         <v>0.663</v>
       </c>
       <c r="C20" t="n">
-        <v>0.207</v>
+        <v>0.2</v>
       </c>
       <c r="D20" t="n">
-        <v>0.319</v>
+        <v>0.31</v>
       </c>
       <c r="E20" t="n">
-        <v>1.052</v>
+        <v>1.04</v>
       </c>
       <c r="F20" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="G20" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="H20" t="n">
-        <v>1219</v>
+        <v>1613</v>
       </c>
       <c r="I20" t="n">
-        <v>740</v>
+        <v>887</v>
       </c>
       <c r="J20" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1128,28 +1128,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.227</v>
+        <v>0.237</v>
       </c>
       <c r="C21" t="n">
-        <v>0.062</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>0.122</v>
+        <v>0.132</v>
       </c>
       <c r="E21" t="n">
-        <v>0.341</v>
+        <v>0.37</v>
       </c>
       <c r="F21" t="n">
         <v>0.002</v>
       </c>
       <c r="G21" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H21" t="n">
-        <v>834</v>
+        <v>1004</v>
       </c>
       <c r="I21" t="n">
-        <v>675</v>
+        <v>861</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -1168,10 +1168,10 @@
         <v>0.005</v>
       </c>
       <c r="D22" t="n">
-        <v>0.043</v>
+        <v>0.041</v>
       </c>
       <c r="E22" t="n">
-        <v>0.061</v>
+        <v>0.06</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>461</v>
+        <v>568</v>
       </c>
       <c r="I22" t="n">
-        <v>688</v>
+        <v>566</v>
       </c>
       <c r="J22" t="n">
         <v>1.01</v>
@@ -1199,13 +1199,13 @@
         <v>0.6919999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.132</v>
+        <v>0.127</v>
       </c>
       <c r="D23" t="n">
-        <v>0.435</v>
+        <v>0.472</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9</v>
+        <v>0.929</v>
       </c>
       <c r="F23" t="n">
         <v>0.003</v>
@@ -1214,13 +1214,13 @@
         <v>0.004</v>
       </c>
       <c r="H23" t="n">
-        <v>1458</v>
+        <v>1809</v>
       </c>
       <c r="I23" t="n">
-        <v>594</v>
+        <v>760</v>
       </c>
       <c r="J23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1230,16 +1230,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
       <c r="C24" t="n">
         <v>0.02</v>
       </c>
       <c r="D24" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F24" t="n">
         <v>0.001</v>
@@ -1248,13 +1248,13 @@
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>1476</v>
+        <v>1016</v>
       </c>
       <c r="I24" t="n">
-        <v>475</v>
+        <v>432</v>
       </c>
       <c r="J24" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1273,7 +1273,7 @@
         <v>0.022</v>
       </c>
       <c r="E25" t="n">
-        <v>0.054</v>
+        <v>0.055</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1282,10 +1282,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1478</v>
+        <v>1523</v>
       </c>
       <c r="I25" t="n">
-        <v>724</v>
+        <v>882</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -1298,13 +1298,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="C26" t="n">
         <v>0.006</v>
       </c>
       <c r="D26" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="E26" t="n">
         <v>0.034</v>
@@ -1316,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2199</v>
+        <v>2197</v>
       </c>
       <c r="I26" t="n">
-        <v>751</v>
+        <v>676</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -1332,31 +1332,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.163</v>
+        <v>3.181</v>
       </c>
       <c r="C27" t="n">
-        <v>0.617</v>
+        <v>0.645</v>
       </c>
       <c r="D27" t="n">
-        <v>2.152</v>
+        <v>2.045</v>
       </c>
       <c r="E27" t="n">
-        <v>4.365</v>
+        <v>4.341</v>
       </c>
       <c r="F27" t="n">
-        <v>0.016</v>
+        <v>0.019</v>
       </c>
       <c r="G27" t="n">
-        <v>0.023</v>
+        <v>0.019</v>
       </c>
       <c r="H27" t="n">
-        <v>1624</v>
+        <v>1220</v>
       </c>
       <c r="I27" t="n">
         <v>793</v>
       </c>
       <c r="J27" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1366,28 +1366,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.076</v>
+        <v>0.077</v>
       </c>
       <c r="C28" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
       <c r="D28" t="n">
-        <v>0.043</v>
+        <v>0.041</v>
       </c>
       <c r="E28" t="n">
-        <v>0.11</v>
+        <v>0.114</v>
       </c>
       <c r="F28" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>1129</v>
+        <v>1749</v>
       </c>
       <c r="I28" t="n">
-        <v>750</v>
+        <v>598</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.223</v>
+        <v>0.226</v>
       </c>
       <c r="C29" t="n">
         <v>0.063</v>
       </c>
       <c r="D29" t="n">
-        <v>0.108</v>
+        <v>0.11</v>
       </c>
       <c r="E29" t="n">
-        <v>0.334</v>
+        <v>0.339</v>
       </c>
       <c r="F29" t="n">
         <v>0.002</v>
@@ -1418,13 +1418,13 @@
         <v>0.002</v>
       </c>
       <c r="H29" t="n">
-        <v>1144</v>
+        <v>1564</v>
       </c>
       <c r="I29" t="n">
-        <v>654</v>
+        <v>762</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="30">
@@ -1434,28 +1434,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.054</v>
+        <v>1.069</v>
       </c>
       <c r="C30" t="n">
-        <v>0.209</v>
+        <v>0.227</v>
       </c>
       <c r="D30" t="n">
-        <v>0.702</v>
+        <v>0.664</v>
       </c>
       <c r="E30" t="n">
-        <v>1.461</v>
+        <v>1.477</v>
       </c>
       <c r="F30" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="G30" t="n">
         <v>0.007</v>
       </c>
       <c r="H30" t="n">
-        <v>1857</v>
+        <v>1765</v>
       </c>
       <c r="I30" t="n">
-        <v>834</v>
+        <v>781</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -1486,10 +1486,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>745</v>
+        <v>2219</v>
       </c>
       <c r="I31" t="n">
-        <v>449</v>
+        <v>603</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -1502,31 +1502,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>19507.604</v>
+        <v>21110.717</v>
       </c>
       <c r="C32" t="n">
-        <v>66975.349</v>
+        <v>100164.887</v>
       </c>
       <c r="D32" t="n">
-        <v>727.14</v>
+        <v>541.569</v>
       </c>
       <c r="E32" t="n">
-        <v>50288.463</v>
+        <v>54427.107</v>
       </c>
       <c r="F32" t="n">
-        <v>3677.31</v>
+        <v>3421.01</v>
       </c>
       <c r="G32" t="n">
-        <v>16221.246</v>
+        <v>32125.367</v>
       </c>
       <c r="H32" t="n">
-        <v>745</v>
+        <v>2219</v>
       </c>
       <c r="I32" t="n">
-        <v>449</v>
+        <v>603</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
   </sheetData>

--- a/output/diagnostics/Bayesian_parameter(results).xlsx
+++ b/output/diagnostics/Bayesian_parameter(results).xlsx
@@ -482,31 +482,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.953</v>
+        <v>0.878</v>
       </c>
       <c r="C2" t="n">
-        <v>0.204</v>
+        <v>0.197</v>
       </c>
       <c r="D2" t="n">
-        <v>0.579</v>
+        <v>0.529</v>
       </c>
       <c r="E2" t="n">
-        <v>1.321</v>
+        <v>1.221</v>
       </c>
       <c r="F2" t="n">
         <v>0.006</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="H2" t="n">
-        <v>1188</v>
+        <v>1273</v>
       </c>
       <c r="I2" t="n">
-        <v>808</v>
+        <v>853</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -516,16 +516,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.47</v>
+        <v>0.508</v>
       </c>
       <c r="C3" t="n">
-        <v>0.165</v>
+        <v>0.175</v>
       </c>
       <c r="D3" t="n">
-        <v>0.206</v>
+        <v>0.2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.78</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="F3" t="n">
         <v>0.005</v>
@@ -534,13 +534,13 @@
         <v>0.006</v>
       </c>
       <c r="H3" t="n">
-        <v>1061</v>
+        <v>1246</v>
       </c>
       <c r="I3" t="n">
-        <v>527</v>
+        <v>728</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="4">
@@ -550,25 +550,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.432</v>
+        <v>0.489</v>
       </c>
       <c r="C4" t="n">
-        <v>0.132</v>
+        <v>0.192</v>
       </c>
       <c r="D4" t="n">
-        <v>0.225</v>
+        <v>0.167</v>
       </c>
       <c r="E4" t="n">
-        <v>0.669</v>
+        <v>0.844</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="G4" t="n">
         <v>0.006</v>
       </c>
       <c r="H4" t="n">
-        <v>1258</v>
+        <v>1267</v>
       </c>
       <c r="I4" t="n">
         <v>880</v>
@@ -584,28 +584,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.119</v>
+        <v>0.121</v>
       </c>
       <c r="C5" t="n">
-        <v>0.016</v>
+        <v>0.021</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.146</v>
+        <v>0.16</v>
       </c>
       <c r="F5" t="n">
         <v>0.001</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H5" t="n">
-        <v>489</v>
+        <v>519</v>
       </c>
       <c r="I5" t="n">
-        <v>742</v>
+        <v>564</v>
       </c>
       <c r="J5" t="n">
         <v>1.01</v>
@@ -618,16 +618,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.034</v>
+        <v>0.037</v>
       </c>
       <c r="D6" t="n">
-        <v>0.028</v>
+        <v>0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>0.144</v>
+        <v>0.152</v>
       </c>
       <c r="F6" t="n">
         <v>0.001</v>
@@ -636,10 +636,10 @@
         <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>1157</v>
+        <v>993</v>
       </c>
       <c r="I6" t="n">
-        <v>770</v>
+        <v>658</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -652,28 +652,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.282</v>
+        <v>1.043</v>
       </c>
       <c r="C7" t="n">
-        <v>0.461</v>
+        <v>0.442</v>
       </c>
       <c r="D7" t="n">
-        <v>0.508</v>
+        <v>0.372</v>
       </c>
       <c r="E7" t="n">
-        <v>2.084</v>
+        <v>1.825</v>
       </c>
       <c r="F7" t="n">
-        <v>0.012</v>
+        <v>0.014</v>
       </c>
       <c r="G7" t="n">
-        <v>0.016</v>
+        <v>0.019</v>
       </c>
       <c r="H7" t="n">
-        <v>1543</v>
+        <v>1176</v>
       </c>
       <c r="I7" t="n">
-        <v>747</v>
+        <v>733</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.042</v>
+        <v>0.049</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="D8" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="E8" t="n">
-        <v>0.059</v>
+        <v>0.074</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>975</v>
+        <v>814</v>
       </c>
       <c r="I8" t="n">
-        <v>783</v>
+        <v>620</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.253</v>
+        <v>0.262</v>
       </c>
       <c r="C9" t="n">
         <v>0.057</v>
       </c>
       <c r="D9" t="n">
-        <v>0.154</v>
+        <v>0.158</v>
       </c>
       <c r="E9" t="n">
-        <v>0.366</v>
+        <v>0.368</v>
       </c>
       <c r="F9" t="n">
         <v>0.002</v>
@@ -738,10 +738,10 @@
         <v>0.002</v>
       </c>
       <c r="H9" t="n">
-        <v>1214</v>
+        <v>982</v>
       </c>
       <c r="I9" t="n">
-        <v>781</v>
+        <v>698</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -754,31 +754,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="C10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="D10" t="n">
-        <v>0.236</v>
+        <v>0.209</v>
       </c>
       <c r="E10" t="n">
-        <v>0.489</v>
+        <v>0.487</v>
       </c>
       <c r="F10" t="n">
         <v>0.002</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H10" t="n">
-        <v>1653</v>
+        <v>1519</v>
       </c>
       <c r="I10" t="n">
-        <v>946</v>
+        <v>757</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="11">
@@ -788,16 +788,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="C11" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="D11" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>0.026</v>
+        <v>0.03</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -806,10 +806,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>570</v>
+        <v>634</v>
       </c>
       <c r="I11" t="n">
-        <v>547</v>
+        <v>418</v>
       </c>
       <c r="J11" t="n">
         <v>1.01</v>
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.756</v>
+        <v>0.716</v>
       </c>
       <c r="C12" t="n">
-        <v>0.248</v>
+        <v>0.244</v>
       </c>
       <c r="D12" t="n">
-        <v>0.317</v>
+        <v>0.312</v>
       </c>
       <c r="E12" t="n">
-        <v>1.235</v>
+        <v>1.18</v>
       </c>
       <c r="F12" t="n">
         <v>0.007</v>
@@ -840,10 +840,10 @@
         <v>0.008</v>
       </c>
       <c r="H12" t="n">
-        <v>1189</v>
+        <v>1208</v>
       </c>
       <c r="I12" t="n">
-        <v>600</v>
+        <v>840</v>
       </c>
       <c r="J12" t="n">
         <v>1.01</v>
@@ -856,28 +856,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.175</v>
+        <v>0.176</v>
       </c>
       <c r="C13" t="n">
-        <v>0.091</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02</v>
+        <v>0.036</v>
       </c>
       <c r="E13" t="n">
-        <v>0.336</v>
+        <v>0.333</v>
       </c>
       <c r="F13" t="n">
         <v>0.002</v>
       </c>
       <c r="G13" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H13" t="n">
-        <v>1324</v>
+        <v>1291</v>
       </c>
       <c r="I13" t="n">
-        <v>664</v>
+        <v>767</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -890,28 +890,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.544</v>
+        <v>1.762</v>
       </c>
       <c r="C14" t="n">
-        <v>0.655</v>
+        <v>0.773</v>
       </c>
       <c r="D14" t="n">
-        <v>0.492</v>
+        <v>0.434</v>
       </c>
       <c r="E14" t="n">
-        <v>2.839</v>
+        <v>3.168</v>
       </c>
       <c r="F14" t="n">
-        <v>0.019</v>
+        <v>0.024</v>
       </c>
       <c r="G14" t="n">
-        <v>0.019</v>
+        <v>0.028</v>
       </c>
       <c r="H14" t="n">
-        <v>1145</v>
+        <v>965</v>
       </c>
       <c r="I14" t="n">
-        <v>644</v>
+        <v>578</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -924,28 +924,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.415</v>
+        <v>2.446</v>
       </c>
       <c r="C15" t="n">
-        <v>0.538</v>
+        <v>0.575</v>
       </c>
       <c r="D15" t="n">
-        <v>1.465</v>
+        <v>1.442</v>
       </c>
       <c r="E15" t="n">
-        <v>3.396</v>
+        <v>3.549</v>
       </c>
       <c r="F15" t="n">
-        <v>0.015</v>
+        <v>0.017</v>
       </c>
       <c r="G15" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="H15" t="n">
-        <v>1221</v>
+        <v>1131</v>
       </c>
       <c r="I15" t="n">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -958,28 +958,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.259</v>
+        <v>3.504</v>
       </c>
       <c r="C16" t="n">
-        <v>1.248</v>
+        <v>1.233</v>
       </c>
       <c r="D16" t="n">
-        <v>1.508</v>
+        <v>1.5</v>
       </c>
       <c r="E16" t="n">
-        <v>5.466</v>
+        <v>5.505</v>
       </c>
       <c r="F16" t="n">
-        <v>0.035</v>
+        <v>0.046</v>
       </c>
       <c r="G16" t="n">
         <v>0.027</v>
       </c>
       <c r="H16" t="n">
-        <v>1313</v>
+        <v>576</v>
       </c>
       <c r="I16" t="n">
-        <v>628</v>
+        <v>386</v>
       </c>
       <c r="J16" t="n">
         <v>1.01</v>
@@ -992,28 +992,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.646</v>
+        <v>0.754</v>
       </c>
       <c r="C17" t="n">
-        <v>0.299</v>
+        <v>0.463</v>
       </c>
       <c r="D17" t="n">
-        <v>0.17</v>
+        <v>0.044</v>
       </c>
       <c r="E17" t="n">
-        <v>1.224</v>
+        <v>1.551</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="G17" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.018</v>
       </c>
       <c r="H17" t="n">
-        <v>803</v>
+        <v>943</v>
       </c>
       <c r="I17" t="n">
-        <v>559</v>
+        <v>480</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -1026,31 +1026,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.597</v>
+        <v>0.627</v>
       </c>
       <c r="C18" t="n">
-        <v>0.283</v>
+        <v>0.288</v>
       </c>
       <c r="D18" t="n">
-        <v>0.152</v>
+        <v>0.146</v>
       </c>
       <c r="E18" t="n">
-        <v>1.082</v>
+        <v>1.151</v>
       </c>
       <c r="F18" t="n">
         <v>0.007</v>
       </c>
       <c r="G18" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="H18" t="n">
-        <v>1455</v>
+        <v>1323</v>
       </c>
       <c r="I18" t="n">
-        <v>742</v>
+        <v>709</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="19">
@@ -1060,28 +1060,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22.541</v>
+        <v>23.031</v>
       </c>
       <c r="C19" t="n">
-        <v>1.671</v>
+        <v>1.803</v>
       </c>
       <c r="D19" t="n">
-        <v>20.001</v>
+        <v>20.157</v>
       </c>
       <c r="E19" t="n">
-        <v>25.424</v>
+        <v>25.833</v>
       </c>
       <c r="F19" t="n">
-        <v>0.042</v>
+        <v>0.044</v>
       </c>
       <c r="G19" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="H19" t="n">
-        <v>1409</v>
+        <v>1692</v>
       </c>
       <c r="I19" t="n">
-        <v>596</v>
+        <v>680</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.663</v>
+        <v>0.664</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2</v>
+        <v>0.197</v>
       </c>
       <c r="D20" t="n">
-        <v>0.31</v>
+        <v>0.334</v>
       </c>
       <c r="E20" t="n">
-        <v>1.04</v>
+        <v>1.034</v>
       </c>
       <c r="F20" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="G20" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="H20" t="n">
-        <v>1613</v>
+        <v>1039</v>
       </c>
       <c r="I20" t="n">
-        <v>887</v>
+        <v>786</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.237</v>
+        <v>0.232</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.094</v>
       </c>
       <c r="D21" t="n">
-        <v>0.132</v>
+        <v>0.076</v>
       </c>
       <c r="E21" t="n">
-        <v>0.37</v>
+        <v>0.387</v>
       </c>
       <c r="F21" t="n">
         <v>0.002</v>
@@ -1146,10 +1146,10 @@
         <v>0.003</v>
       </c>
       <c r="H21" t="n">
-        <v>1004</v>
+        <v>1673</v>
       </c>
       <c r="I21" t="n">
-        <v>861</v>
+        <v>831</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -1162,16 +1162,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="C22" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="D22" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06</v>
+        <v>0.064</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1180,13 +1180,13 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>568</v>
+        <v>635</v>
       </c>
       <c r="I22" t="n">
-        <v>566</v>
+        <v>465</v>
       </c>
       <c r="J22" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.127</v>
+        <v>0.132</v>
       </c>
       <c r="D23" t="n">
-        <v>0.472</v>
+        <v>0.434</v>
       </c>
       <c r="E23" t="n">
-        <v>0.929</v>
+        <v>0.915</v>
       </c>
       <c r="F23" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="G23" t="n">
         <v>0.004</v>
       </c>
       <c r="H23" t="n">
-        <v>1809</v>
+        <v>1113</v>
       </c>
       <c r="I23" t="n">
-        <v>760</v>
+        <v>624</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -1236,10 +1236,10 @@
         <v>0.02</v>
       </c>
       <c r="D24" t="n">
-        <v>0.013</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F24" t="n">
         <v>0.001</v>
@@ -1248,13 +1248,13 @@
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>1016</v>
+        <v>1106</v>
       </c>
       <c r="I24" t="n">
-        <v>432</v>
+        <v>354</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="25">
@@ -1264,16 +1264,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.038</v>
+        <v>0.035</v>
       </c>
       <c r="C25" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="D25" t="n">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
       <c r="E25" t="n">
-        <v>0.055</v>
+        <v>0.052</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1282,13 +1282,13 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1523</v>
+        <v>1139</v>
       </c>
       <c r="I25" t="n">
-        <v>882</v>
+        <v>627</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="26">
@@ -1301,10 +1301,10 @@
         <v>0.023</v>
       </c>
       <c r="C26" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="D26" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="E26" t="n">
         <v>0.034</v>
@@ -1316,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2197</v>
+        <v>1556</v>
       </c>
       <c r="I26" t="n">
-        <v>676</v>
+        <v>693</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -1332,28 +1332,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.181</v>
+        <v>3.195</v>
       </c>
       <c r="C27" t="n">
-        <v>0.645</v>
+        <v>0.61</v>
       </c>
       <c r="D27" t="n">
-        <v>2.045</v>
+        <v>2.213</v>
       </c>
       <c r="E27" t="n">
-        <v>4.341</v>
+        <v>4.325</v>
       </c>
       <c r="F27" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="G27" t="n">
-        <v>0.019</v>
+        <v>0.022</v>
       </c>
       <c r="H27" t="n">
-        <v>1220</v>
+        <v>1187</v>
       </c>
       <c r="I27" t="n">
-        <v>793</v>
+        <v>648</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -1369,25 +1369,25 @@
         <v>0.077</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="D28" t="n">
-        <v>0.041</v>
+        <v>0.044</v>
       </c>
       <c r="E28" t="n">
-        <v>0.114</v>
+        <v>0.113</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>1749</v>
+        <v>1297</v>
       </c>
       <c r="I28" t="n">
-        <v>598</v>
+        <v>732</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.226</v>
+        <v>0.224</v>
       </c>
       <c r="C29" t="n">
-        <v>0.063</v>
+        <v>0.059</v>
       </c>
       <c r="D29" t="n">
-        <v>0.11</v>
+        <v>0.122</v>
       </c>
       <c r="E29" t="n">
-        <v>0.339</v>
+        <v>0.331</v>
       </c>
       <c r="F29" t="n">
         <v>0.002</v>
@@ -1418,13 +1418,13 @@
         <v>0.002</v>
       </c>
       <c r="H29" t="n">
-        <v>1564</v>
+        <v>1122</v>
       </c>
       <c r="I29" t="n">
-        <v>762</v>
+        <v>791</v>
       </c>
       <c r="J29" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1434,16 +1434,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.069</v>
+        <v>1.058</v>
       </c>
       <c r="C30" t="n">
-        <v>0.227</v>
+        <v>0.206</v>
       </c>
       <c r="D30" t="n">
-        <v>0.664</v>
+        <v>0.673</v>
       </c>
       <c r="E30" t="n">
-        <v>1.477</v>
+        <v>1.435</v>
       </c>
       <c r="F30" t="n">
         <v>0.006</v>
@@ -1452,10 +1452,10 @@
         <v>0.007</v>
       </c>
       <c r="H30" t="n">
-        <v>1765</v>
+        <v>1291</v>
       </c>
       <c r="I30" t="n">
-        <v>781</v>
+        <v>820</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -1468,16 +1468,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.001</v>
+        <v>0.013</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1486,10 +1486,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2219</v>
+        <v>739</v>
       </c>
       <c r="I31" t="n">
-        <v>603</v>
+        <v>237</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -1502,28 +1502,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>21110.717</v>
+        <v>1290.173</v>
       </c>
       <c r="C32" t="n">
-        <v>100164.887</v>
+        <v>7380.567</v>
       </c>
       <c r="D32" t="n">
-        <v>541.569</v>
+        <v>22.837</v>
       </c>
       <c r="E32" t="n">
-        <v>54427.107</v>
+        <v>2480.435</v>
       </c>
       <c r="F32" t="n">
-        <v>3421.01</v>
+        <v>338.627</v>
       </c>
       <c r="G32" t="n">
-        <v>32125.367</v>
+        <v>2057.892</v>
       </c>
       <c r="H32" t="n">
-        <v>2219</v>
+        <v>739</v>
       </c>
       <c r="I32" t="n">
-        <v>603</v>
+        <v>237</v>
       </c>
       <c r="J32" t="n">
         <v>1.01</v>

--- a/output/diagnostics/Bayesian_parameter(results).xlsx
+++ b/output/diagnostics/Bayesian_parameter(results).xlsx
@@ -482,28 +482,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.878</v>
+        <v>0.889</v>
       </c>
       <c r="C2" t="n">
-        <v>0.197</v>
+        <v>0.217</v>
       </c>
       <c r="D2" t="n">
-        <v>0.529</v>
+        <v>0.477</v>
       </c>
       <c r="E2" t="n">
-        <v>1.221</v>
+        <v>1.256</v>
       </c>
       <c r="F2" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="G2" t="n">
         <v>0.008</v>
       </c>
       <c r="H2" t="n">
-        <v>1273</v>
+        <v>1681</v>
       </c>
       <c r="I2" t="n">
-        <v>853</v>
+        <v>733</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -516,28 +516,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.508</v>
+        <v>0.509</v>
       </c>
       <c r="C3" t="n">
-        <v>0.175</v>
+        <v>0.18</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2</v>
+        <v>0.202</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.843</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="H3" t="n">
-        <v>1246</v>
+        <v>1657</v>
       </c>
       <c r="I3" t="n">
-        <v>728</v>
+        <v>540</v>
       </c>
       <c r="J3" t="n">
         <v>1.01</v>
@@ -550,28 +550,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.489</v>
+        <v>0.488</v>
       </c>
       <c r="C4" t="n">
-        <v>0.192</v>
+        <v>0.2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.167</v>
+        <v>0.163</v>
       </c>
       <c r="E4" t="n">
-        <v>0.844</v>
+        <v>0.832</v>
       </c>
       <c r="F4" t="n">
         <v>0.005</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="H4" t="n">
-        <v>1267</v>
+        <v>2106</v>
       </c>
       <c r="I4" t="n">
-        <v>880</v>
+        <v>724</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -584,16 +584,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.121</v>
+        <v>0.123</v>
       </c>
       <c r="C5" t="n">
-        <v>0.021</v>
+        <v>0.019</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.091</v>
       </c>
       <c r="E5" t="n">
-        <v>0.16</v>
+        <v>0.161</v>
       </c>
       <c r="F5" t="n">
         <v>0.001</v>
@@ -602,13 +602,13 @@
         <v>0.001</v>
       </c>
       <c r="H5" t="n">
-        <v>519</v>
+        <v>1237</v>
       </c>
       <c r="I5" t="n">
-        <v>564</v>
+        <v>785</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -618,16 +618,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C6" t="n">
         <v>0.037</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="E6" t="n">
-        <v>0.152</v>
+        <v>0.153</v>
       </c>
       <c r="F6" t="n">
         <v>0.001</v>
@@ -636,10 +636,10 @@
         <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>993</v>
+        <v>1690</v>
       </c>
       <c r="I6" t="n">
-        <v>658</v>
+        <v>772</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -652,28 +652,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.043</v>
+        <v>1.068</v>
       </c>
       <c r="C7" t="n">
-        <v>0.442</v>
+        <v>0.454</v>
       </c>
       <c r="D7" t="n">
-        <v>0.372</v>
+        <v>0.4</v>
       </c>
       <c r="E7" t="n">
-        <v>1.825</v>
+        <v>1.952</v>
       </c>
       <c r="F7" t="n">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="G7" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="H7" t="n">
-        <v>1176</v>
+        <v>2189</v>
       </c>
       <c r="I7" t="n">
-        <v>733</v>
+        <v>696</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -689,13 +689,13 @@
         <v>0.049</v>
       </c>
       <c r="C8" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="D8" t="n">
-        <v>0.021</v>
+        <v>0.024</v>
       </c>
       <c r="E8" t="n">
-        <v>0.074</v>
+        <v>0.078</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>814</v>
+        <v>1670</v>
       </c>
       <c r="I8" t="n">
-        <v>620</v>
+        <v>744</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.262</v>
+        <v>0.259</v>
       </c>
       <c r="C9" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
       <c r="D9" t="n">
-        <v>0.158</v>
+        <v>0.156</v>
       </c>
       <c r="E9" t="n">
-        <v>0.368</v>
+        <v>0.361</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="G9" t="n">
         <v>0.002</v>
       </c>
       <c r="H9" t="n">
-        <v>982</v>
+        <v>2484</v>
       </c>
       <c r="I9" t="n">
-        <v>698</v>
+        <v>756</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="10">
@@ -754,28 +754,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.356</v>
+        <v>0.358</v>
       </c>
       <c r="C10" t="n">
-        <v>0.077</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.209</v>
+        <v>0.225</v>
       </c>
       <c r="E10" t="n">
-        <v>0.487</v>
+        <v>0.489</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="G10" t="n">
         <v>0.003</v>
       </c>
       <c r="H10" t="n">
-        <v>1519</v>
+        <v>2314</v>
       </c>
       <c r="I10" t="n">
-        <v>757</v>
+        <v>694</v>
       </c>
       <c r="J10" t="n">
         <v>1.01</v>
@@ -791,13 +791,13 @@
         <v>0.018</v>
       </c>
       <c r="C11" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -806,10 +806,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>634</v>
+        <v>1027</v>
       </c>
       <c r="I11" t="n">
-        <v>418</v>
+        <v>735</v>
       </c>
       <c r="J11" t="n">
         <v>1.01</v>
@@ -822,28 +822,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.716</v>
+        <v>0.717</v>
       </c>
       <c r="C12" t="n">
-        <v>0.244</v>
+        <v>0.239</v>
       </c>
       <c r="D12" t="n">
-        <v>0.312</v>
+        <v>0.288</v>
       </c>
       <c r="E12" t="n">
-        <v>1.18</v>
+        <v>1.147</v>
       </c>
       <c r="F12" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="G12" t="n">
         <v>0.007</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.008</v>
-      </c>
       <c r="H12" t="n">
-        <v>1208</v>
+        <v>1415</v>
       </c>
       <c r="I12" t="n">
-        <v>840</v>
+        <v>707</v>
       </c>
       <c r="J12" t="n">
         <v>1.01</v>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.176</v>
+        <v>0.17</v>
       </c>
       <c r="C13" t="n">
         <v>0.08500000000000001</v>
@@ -865,22 +865,22 @@
         <v>0.036</v>
       </c>
       <c r="E13" t="n">
-        <v>0.333</v>
+        <v>0.326</v>
       </c>
       <c r="F13" t="n">
         <v>0.002</v>
       </c>
       <c r="G13" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H13" t="n">
-        <v>1291</v>
+        <v>1722</v>
       </c>
       <c r="I13" t="n">
-        <v>767</v>
+        <v>880</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="14">
@@ -890,28 +890,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.762</v>
+        <v>1.707</v>
       </c>
       <c r="C14" t="n">
-        <v>0.773</v>
+        <v>0.726</v>
       </c>
       <c r="D14" t="n">
-        <v>0.434</v>
+        <v>0.506</v>
       </c>
       <c r="E14" t="n">
-        <v>3.168</v>
+        <v>3.07</v>
       </c>
       <c r="F14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G14" t="n">
         <v>0.024</v>
       </c>
-      <c r="G14" t="n">
-        <v>0.028</v>
-      </c>
       <c r="H14" t="n">
-        <v>965</v>
+        <v>1348</v>
       </c>
       <c r="I14" t="n">
-        <v>578</v>
+        <v>811</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -924,28 +924,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.446</v>
+        <v>2.399</v>
       </c>
       <c r="C15" t="n">
-        <v>0.575</v>
+        <v>0.532</v>
       </c>
       <c r="D15" t="n">
-        <v>1.442</v>
+        <v>1.416</v>
       </c>
       <c r="E15" t="n">
-        <v>3.549</v>
+        <v>3.392</v>
       </c>
       <c r="F15" t="n">
-        <v>0.017</v>
+        <v>0.013</v>
       </c>
       <c r="G15" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="H15" t="n">
-        <v>1131</v>
+        <v>1659</v>
       </c>
       <c r="I15" t="n">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -958,28 +958,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.504</v>
+        <v>3.515</v>
       </c>
       <c r="C16" t="n">
-        <v>1.233</v>
+        <v>1.273</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5</v>
+        <v>1.551</v>
       </c>
       <c r="E16" t="n">
-        <v>5.505</v>
+        <v>5.658</v>
       </c>
       <c r="F16" t="n">
-        <v>0.046</v>
+        <v>0.027</v>
       </c>
       <c r="G16" t="n">
         <v>0.027</v>
       </c>
       <c r="H16" t="n">
-        <v>576</v>
+        <v>2296</v>
       </c>
       <c r="I16" t="n">
-        <v>386</v>
+        <v>659</v>
       </c>
       <c r="J16" t="n">
         <v>1.01</v>
@@ -992,28 +992,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.754</v>
+        <v>0.746</v>
       </c>
       <c r="C17" t="n">
-        <v>0.463</v>
+        <v>0.428</v>
       </c>
       <c r="D17" t="n">
-        <v>0.044</v>
+        <v>0.082</v>
       </c>
       <c r="E17" t="n">
-        <v>1.551</v>
+        <v>1.489</v>
       </c>
       <c r="F17" t="n">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="G17" t="n">
-        <v>0.018</v>
+        <v>0.013</v>
       </c>
       <c r="H17" t="n">
-        <v>943</v>
+        <v>1358</v>
       </c>
       <c r="I17" t="n">
-        <v>480</v>
+        <v>693</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -1026,28 +1026,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.627</v>
+        <v>0.612</v>
       </c>
       <c r="C18" t="n">
-        <v>0.288</v>
+        <v>0.27</v>
       </c>
       <c r="D18" t="n">
-        <v>0.146</v>
+        <v>0.16</v>
       </c>
       <c r="E18" t="n">
-        <v>1.151</v>
+        <v>1.109</v>
       </c>
       <c r="F18" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>1323</v>
+        <v>1603</v>
       </c>
       <c r="I18" t="n">
-        <v>709</v>
+        <v>819</v>
       </c>
       <c r="J18" t="n">
         <v>1.01</v>
@@ -1060,28 +1060,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23.031</v>
+        <v>23.013</v>
       </c>
       <c r="C19" t="n">
-        <v>1.803</v>
+        <v>1.78</v>
       </c>
       <c r="D19" t="n">
-        <v>20.157</v>
+        <v>20.28</v>
       </c>
       <c r="E19" t="n">
-        <v>25.833</v>
+        <v>25.933</v>
       </c>
       <c r="F19" t="n">
-        <v>0.044</v>
+        <v>0.04</v>
       </c>
       <c r="G19" t="n">
-        <v>0.041</v>
+        <v>0.038</v>
       </c>
       <c r="H19" t="n">
-        <v>1692</v>
+        <v>1903</v>
       </c>
       <c r="I19" t="n">
-        <v>680</v>
+        <v>618</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.664</v>
+        <v>0.666</v>
       </c>
       <c r="C20" t="n">
-        <v>0.197</v>
+        <v>0.198</v>
       </c>
       <c r="D20" t="n">
-        <v>0.334</v>
+        <v>0.327</v>
       </c>
       <c r="E20" t="n">
-        <v>1.034</v>
+        <v>1.043</v>
       </c>
       <c r="F20" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="G20" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="H20" t="n">
-        <v>1039</v>
+        <v>1614</v>
       </c>
       <c r="I20" t="n">
-        <v>786</v>
+        <v>615</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="21">
@@ -1128,31 +1128,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.232</v>
+        <v>0.224</v>
       </c>
       <c r="C21" t="n">
-        <v>0.094</v>
+        <v>0.092</v>
       </c>
       <c r="D21" t="n">
-        <v>0.076</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>0.387</v>
+        <v>0.399</v>
       </c>
       <c r="F21" t="n">
         <v>0.002</v>
       </c>
       <c r="G21" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H21" t="n">
-        <v>1673</v>
+        <v>1351</v>
       </c>
       <c r="I21" t="n">
-        <v>831</v>
+        <v>728</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="22">
@@ -1168,10 +1168,10 @@
         <v>0.006</v>
       </c>
       <c r="D22" t="n">
-        <v>0.042</v>
+        <v>0.043</v>
       </c>
       <c r="E22" t="n">
-        <v>0.064</v>
+        <v>0.063</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1180,13 +1180,13 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>635</v>
+        <v>1014</v>
       </c>
       <c r="I22" t="n">
-        <v>465</v>
+        <v>615</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="23">
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.132</v>
+        <v>0.13</v>
       </c>
       <c r="D23" t="n">
-        <v>0.434</v>
+        <v>0.449</v>
       </c>
       <c r="E23" t="n">
-        <v>0.915</v>
+        <v>0.913</v>
       </c>
       <c r="F23" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="G23" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="H23" t="n">
-        <v>1113</v>
+        <v>1521</v>
       </c>
       <c r="I23" t="n">
-        <v>624</v>
+        <v>691</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="24">
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="C24" t="n">
         <v>0.02</v>
       </c>
       <c r="D24" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.013</v>
       </c>
       <c r="E24" t="n">
         <v>0.08599999999999999</v>
@@ -1248,13 +1248,13 @@
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>1106</v>
+        <v>1202</v>
       </c>
       <c r="I24" t="n">
-        <v>354</v>
+        <v>489</v>
       </c>
       <c r="J24" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1267,13 +1267,13 @@
         <v>0.035</v>
       </c>
       <c r="C25" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D25" t="n">
         <v>0.02</v>
       </c>
       <c r="E25" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1282,13 +1282,13 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1139</v>
+        <v>1502</v>
       </c>
       <c r="I25" t="n">
-        <v>627</v>
+        <v>561</v>
       </c>
       <c r="J25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1301,13 +1301,13 @@
         <v>0.023</v>
       </c>
       <c r="C26" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="D26" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="E26" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1316,13 +1316,13 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1556</v>
+        <v>1862</v>
       </c>
       <c r="I26" t="n">
-        <v>693</v>
+        <v>803</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="27">
@@ -1332,31 +1332,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.195</v>
+        <v>3.175</v>
       </c>
       <c r="C27" t="n">
-        <v>0.61</v>
+        <v>0.611</v>
       </c>
       <c r="D27" t="n">
-        <v>2.213</v>
+        <v>2.04</v>
       </c>
       <c r="E27" t="n">
-        <v>4.325</v>
+        <v>4.276</v>
       </c>
       <c r="F27" t="n">
-        <v>0.018</v>
+        <v>0.015</v>
       </c>
       <c r="G27" t="n">
         <v>0.022</v>
       </c>
       <c r="H27" t="n">
-        <v>1187</v>
+        <v>1844</v>
       </c>
       <c r="I27" t="n">
-        <v>648</v>
+        <v>741</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="28">
@@ -1372,22 +1372,22 @@
         <v>0.019</v>
       </c>
       <c r="D28" t="n">
-        <v>0.044</v>
+        <v>0.038</v>
       </c>
       <c r="E28" t="n">
-        <v>0.113</v>
+        <v>0.11</v>
       </c>
       <c r="F28" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>1297</v>
+        <v>1822</v>
       </c>
       <c r="I28" t="n">
-        <v>732</v>
+        <v>576</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -1400,28 +1400,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.224</v>
+        <v>0.222</v>
       </c>
       <c r="C29" t="n">
-        <v>0.059</v>
+        <v>0.061</v>
       </c>
       <c r="D29" t="n">
-        <v>0.122</v>
+        <v>0.121</v>
       </c>
       <c r="E29" t="n">
-        <v>0.331</v>
+        <v>0.339</v>
       </c>
       <c r="F29" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="G29" t="n">
         <v>0.002</v>
       </c>
       <c r="H29" t="n">
-        <v>1122</v>
+        <v>1813</v>
       </c>
       <c r="I29" t="n">
-        <v>791</v>
+        <v>836</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -1437,25 +1437,25 @@
         <v>1.058</v>
       </c>
       <c r="C30" t="n">
-        <v>0.206</v>
+        <v>0.214</v>
       </c>
       <c r="D30" t="n">
-        <v>0.673</v>
+        <v>0.645</v>
       </c>
       <c r="E30" t="n">
-        <v>1.435</v>
+        <v>1.427</v>
       </c>
       <c r="F30" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="G30" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="H30" t="n">
-        <v>1291</v>
+        <v>1822</v>
       </c>
       <c r="I30" t="n">
-        <v>820</v>
+        <v>680</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -1486,10 +1486,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>739</v>
+        <v>1122</v>
       </c>
       <c r="I31" t="n">
-        <v>237</v>
+        <v>560</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -1502,31 +1502,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1290.173</v>
+        <v>2015.107</v>
       </c>
       <c r="C32" t="n">
-        <v>7380.567</v>
+        <v>11867.161</v>
       </c>
       <c r="D32" t="n">
-        <v>22.837</v>
+        <v>24.148</v>
       </c>
       <c r="E32" t="n">
-        <v>2480.435</v>
+        <v>4011.734</v>
       </c>
       <c r="F32" t="n">
-        <v>338.627</v>
+        <v>444.263</v>
       </c>
       <c r="G32" t="n">
-        <v>2057.892</v>
+        <v>3679.616</v>
       </c>
       <c r="H32" t="n">
-        <v>739</v>
+        <v>1122</v>
       </c>
       <c r="I32" t="n">
-        <v>237</v>
+        <v>560</v>
       </c>
       <c r="J32" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/diagnostics/Bayesian_parameter(results).xlsx
+++ b/output/diagnostics/Bayesian_parameter(results).xlsx
@@ -482,28 +482,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.889</v>
+        <v>0.968</v>
       </c>
       <c r="C2" t="n">
-        <v>0.217</v>
+        <v>0.203</v>
       </c>
       <c r="D2" t="n">
-        <v>0.477</v>
+        <v>0.615</v>
       </c>
       <c r="E2" t="n">
-        <v>1.256</v>
+        <v>1.358</v>
       </c>
       <c r="F2" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="G2" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="H2" t="n">
-        <v>1681</v>
+        <v>806</v>
       </c>
       <c r="I2" t="n">
-        <v>733</v>
+        <v>658</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -516,31 +516,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.509</v>
+        <v>0.482</v>
       </c>
       <c r="C3" t="n">
-        <v>0.18</v>
+        <v>0.171</v>
       </c>
       <c r="D3" t="n">
-        <v>0.202</v>
+        <v>0.181</v>
       </c>
       <c r="E3" t="n">
-        <v>0.843</v>
+        <v>0.79</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="H3" t="n">
-        <v>1657</v>
+        <v>944</v>
       </c>
       <c r="I3" t="n">
-        <v>540</v>
+        <v>647</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -550,28 +550,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.488</v>
+        <v>0.437</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2</v>
+        <v>0.138</v>
       </c>
       <c r="D4" t="n">
-        <v>0.163</v>
+        <v>0.218</v>
       </c>
       <c r="E4" t="n">
-        <v>0.832</v>
+        <v>0.697</v>
       </c>
       <c r="F4" t="n">
         <v>0.005</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="H4" t="n">
-        <v>2106</v>
+        <v>931</v>
       </c>
       <c r="I4" t="n">
-        <v>724</v>
+        <v>779</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -584,16 +584,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.123</v>
+        <v>0.121</v>
       </c>
       <c r="C5" t="n">
-        <v>0.019</v>
+        <v>0.014</v>
       </c>
       <c r="D5" t="n">
-        <v>0.091</v>
+        <v>0.096</v>
       </c>
       <c r="E5" t="n">
-        <v>0.161</v>
+        <v>0.148</v>
       </c>
       <c r="F5" t="n">
         <v>0.001</v>
@@ -602,13 +602,13 @@
         <v>0.001</v>
       </c>
       <c r="H5" t="n">
-        <v>1237</v>
+        <v>448</v>
       </c>
       <c r="I5" t="n">
-        <v>785</v>
+        <v>315</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="6">
@@ -618,16 +618,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.037</v>
+        <v>0.038</v>
       </c>
       <c r="D6" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="E6" t="n">
-        <v>0.153</v>
+        <v>0.161</v>
       </c>
       <c r="F6" t="n">
         <v>0.001</v>
@@ -636,10 +636,10 @@
         <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>1690</v>
+        <v>1449</v>
       </c>
       <c r="I6" t="n">
-        <v>772</v>
+        <v>696</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -652,28 +652,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.068</v>
+        <v>1.247</v>
       </c>
       <c r="C7" t="n">
-        <v>0.454</v>
+        <v>0.435</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>1.952</v>
+        <v>2.101</v>
       </c>
       <c r="F7" t="n">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
       <c r="G7" t="n">
-        <v>0.018</v>
+        <v>0.015</v>
       </c>
       <c r="H7" t="n">
-        <v>2189</v>
+        <v>813</v>
       </c>
       <c r="I7" t="n">
-        <v>696</v>
+        <v>748</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.049</v>
+        <v>0.039</v>
       </c>
       <c r="C8" t="n">
-        <v>0.015</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="E8" t="n">
-        <v>0.078</v>
+        <v>0.056</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -704,13 +704,13 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1670</v>
+        <v>812</v>
       </c>
       <c r="I8" t="n">
-        <v>744</v>
+        <v>716</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="9">
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.259</v>
+        <v>0.257</v>
       </c>
       <c r="C9" t="n">
         <v>0.058</v>
       </c>
       <c r="D9" t="n">
-        <v>0.156</v>
+        <v>0.15</v>
       </c>
       <c r="E9" t="n">
-        <v>0.361</v>
+        <v>0.365</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="G9" t="n">
         <v>0.002</v>
       </c>
       <c r="H9" t="n">
-        <v>2484</v>
+        <v>1048</v>
       </c>
       <c r="I9" t="n">
-        <v>756</v>
+        <v>792</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -754,31 +754,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.358</v>
+        <v>0.362</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D10" t="n">
-        <v>0.225</v>
+        <v>0.226</v>
       </c>
       <c r="E10" t="n">
-        <v>0.489</v>
+        <v>0.518</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="G10" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H10" t="n">
-        <v>2314</v>
+        <v>1132</v>
       </c>
       <c r="I10" t="n">
-        <v>694</v>
+        <v>732</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -788,16 +788,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="C11" t="n">
         <v>0.005</v>
       </c>
       <c r="D11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="E11" t="n">
-        <v>0.029</v>
+        <v>0.026</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -806,10 +806,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1027</v>
+        <v>473</v>
       </c>
       <c r="I11" t="n">
-        <v>735</v>
+        <v>621</v>
       </c>
       <c r="J11" t="n">
         <v>1.01</v>
@@ -822,31 +822,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.717</v>
+        <v>0.766</v>
       </c>
       <c r="C12" t="n">
-        <v>0.239</v>
+        <v>0.249</v>
       </c>
       <c r="D12" t="n">
-        <v>0.288</v>
+        <v>0.334</v>
       </c>
       <c r="E12" t="n">
-        <v>1.147</v>
+        <v>1.236</v>
       </c>
       <c r="F12" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="G12" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="H12" t="n">
-        <v>1415</v>
+        <v>1346</v>
       </c>
       <c r="I12" t="n">
-        <v>707</v>
+        <v>782</v>
       </c>
       <c r="J12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -856,16 +856,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.17</v>
+        <v>0.173</v>
       </c>
       <c r="C13" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.036</v>
+        <v>0.026</v>
       </c>
       <c r="E13" t="n">
-        <v>0.326</v>
+        <v>0.332</v>
       </c>
       <c r="F13" t="n">
         <v>0.002</v>
@@ -874,13 +874,13 @@
         <v>0.003</v>
       </c>
       <c r="H13" t="n">
-        <v>1722</v>
+        <v>1284</v>
       </c>
       <c r="I13" t="n">
-        <v>880</v>
+        <v>484</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -890,31 +890,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.707</v>
+        <v>1.438</v>
       </c>
       <c r="C14" t="n">
-        <v>0.726</v>
+        <v>0.59</v>
       </c>
       <c r="D14" t="n">
-        <v>0.506</v>
+        <v>0.428</v>
       </c>
       <c r="E14" t="n">
-        <v>3.07</v>
+        <v>2.458</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="G14" t="n">
-        <v>0.024</v>
+        <v>0.016</v>
       </c>
       <c r="H14" t="n">
-        <v>1348</v>
+        <v>900</v>
       </c>
       <c r="I14" t="n">
-        <v>811</v>
+        <v>883</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="15">
@@ -924,28 +924,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.399</v>
+        <v>2.407</v>
       </c>
       <c r="C15" t="n">
-        <v>0.532</v>
+        <v>0.538</v>
       </c>
       <c r="D15" t="n">
-        <v>1.416</v>
+        <v>1.448</v>
       </c>
       <c r="E15" t="n">
-        <v>3.392</v>
+        <v>3.439</v>
       </c>
       <c r="F15" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
       <c r="G15" t="n">
         <v>0.019</v>
       </c>
       <c r="H15" t="n">
-        <v>1659</v>
+        <v>1211</v>
       </c>
       <c r="I15" t="n">
-        <v>726</v>
+        <v>617</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -958,31 +958,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.515</v>
+        <v>3.167</v>
       </c>
       <c r="C16" t="n">
-        <v>1.273</v>
+        <v>1.154</v>
       </c>
       <c r="D16" t="n">
-        <v>1.551</v>
+        <v>1.504</v>
       </c>
       <c r="E16" t="n">
-        <v>5.658</v>
+        <v>5.282</v>
       </c>
       <c r="F16" t="n">
-        <v>0.027</v>
+        <v>0.039</v>
       </c>
       <c r="G16" t="n">
-        <v>0.027</v>
+        <v>0.024</v>
       </c>
       <c r="H16" t="n">
-        <v>2296</v>
+        <v>871</v>
       </c>
       <c r="I16" t="n">
-        <v>659</v>
+        <v>765</v>
       </c>
       <c r="J16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -992,31 +992,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.746</v>
+        <v>0.543</v>
       </c>
       <c r="C17" t="n">
-        <v>0.428</v>
+        <v>0.311</v>
       </c>
       <c r="D17" t="n">
-        <v>0.082</v>
+        <v>0.061</v>
       </c>
       <c r="E17" t="n">
-        <v>1.489</v>
+        <v>1.074</v>
       </c>
       <c r="F17" t="n">
-        <v>0.011</v>
+        <v>0.016</v>
       </c>
       <c r="G17" t="n">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
       <c r="H17" t="n">
-        <v>1358</v>
+        <v>508</v>
       </c>
       <c r="I17" t="n">
-        <v>693</v>
+        <v>400</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="18">
@@ -1026,31 +1026,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.612</v>
+        <v>0.582</v>
       </c>
       <c r="C18" t="n">
-        <v>0.27</v>
+        <v>0.264</v>
       </c>
       <c r="D18" t="n">
-        <v>0.16</v>
+        <v>0.158</v>
       </c>
       <c r="E18" t="n">
-        <v>1.109</v>
+        <v>1.072</v>
       </c>
       <c r="F18" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="G18" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="H18" t="n">
-        <v>1603</v>
+        <v>1053</v>
       </c>
       <c r="I18" t="n">
-        <v>819</v>
+        <v>761</v>
       </c>
       <c r="J18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1060,28 +1060,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23.013</v>
+        <v>22.631</v>
       </c>
       <c r="C19" t="n">
-        <v>1.78</v>
+        <v>1.739</v>
       </c>
       <c r="D19" t="n">
-        <v>20.28</v>
+        <v>20.014</v>
       </c>
       <c r="E19" t="n">
-        <v>25.933</v>
+        <v>25.517</v>
       </c>
       <c r="F19" t="n">
-        <v>0.04</v>
+        <v>0.052</v>
       </c>
       <c r="G19" t="n">
-        <v>0.038</v>
+        <v>0.033</v>
       </c>
       <c r="H19" t="n">
-        <v>1903</v>
+        <v>1003</v>
       </c>
       <c r="I19" t="n">
-        <v>618</v>
+        <v>764</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.666</v>
+        <v>0.671</v>
       </c>
       <c r="C20" t="n">
-        <v>0.198</v>
+        <v>0.204</v>
       </c>
       <c r="D20" t="n">
-        <v>0.327</v>
+        <v>0.361</v>
       </c>
       <c r="E20" t="n">
-        <v>1.043</v>
+        <v>1.088</v>
       </c>
       <c r="F20" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="G20" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="H20" t="n">
-        <v>1614</v>
+        <v>1152</v>
       </c>
       <c r="I20" t="n">
-        <v>615</v>
+        <v>751</v>
       </c>
       <c r="J20" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1128,28 +1128,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.224</v>
+        <v>0.212</v>
       </c>
       <c r="C21" t="n">
-        <v>0.092</v>
+        <v>0.06</v>
       </c>
       <c r="D21" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.118</v>
       </c>
       <c r="E21" t="n">
-        <v>0.399</v>
+        <v>0.327</v>
       </c>
       <c r="F21" t="n">
         <v>0.002</v>
       </c>
       <c r="G21" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H21" t="n">
-        <v>1351</v>
+        <v>763</v>
       </c>
       <c r="I21" t="n">
-        <v>728</v>
+        <v>824</v>
       </c>
       <c r="J21" t="n">
         <v>1.01</v>
@@ -1162,16 +1162,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="C22" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="D22" t="n">
-        <v>0.043</v>
+        <v>0.042</v>
       </c>
       <c r="E22" t="n">
-        <v>0.063</v>
+        <v>0.061</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1014</v>
+        <v>476</v>
       </c>
       <c r="I22" t="n">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="J22" t="n">
         <v>1.01</v>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>0.13</v>
+        <v>0.134</v>
       </c>
       <c r="D23" t="n">
         <v>0.449</v>
       </c>
       <c r="E23" t="n">
-        <v>0.913</v>
+        <v>0.928</v>
       </c>
       <c r="F23" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="G23" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="H23" t="n">
-        <v>1521</v>
+        <v>1362</v>
       </c>
       <c r="I23" t="n">
-        <v>691</v>
+        <v>834</v>
       </c>
       <c r="J23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1230,16 +1230,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
       <c r="C24" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="D24" t="n">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F24" t="n">
         <v>0.001</v>
@@ -1248,10 +1248,10 @@
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>1202</v>
+        <v>1073</v>
       </c>
       <c r="I24" t="n">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -1264,16 +1264,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.035</v>
+        <v>0.038</v>
       </c>
       <c r="C25" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="E25" t="n">
-        <v>0.051</v>
+        <v>0.054</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1282,10 +1282,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1502</v>
+        <v>1071</v>
       </c>
       <c r="I25" t="n">
-        <v>561</v>
+        <v>791</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -1316,13 +1316,13 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1862</v>
+        <v>1115</v>
       </c>
       <c r="I26" t="n">
-        <v>803</v>
+        <v>874</v>
       </c>
       <c r="J26" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1332,28 +1332,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.175</v>
+        <v>3.188</v>
       </c>
       <c r="C27" t="n">
-        <v>0.611</v>
+        <v>0.651</v>
       </c>
       <c r="D27" t="n">
-        <v>2.04</v>
+        <v>2.069</v>
       </c>
       <c r="E27" t="n">
-        <v>4.276</v>
+        <v>4.407</v>
       </c>
       <c r="F27" t="n">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
       <c r="G27" t="n">
         <v>0.022</v>
       </c>
       <c r="H27" t="n">
-        <v>1844</v>
+        <v>1259</v>
       </c>
       <c r="I27" t="n">
-        <v>741</v>
+        <v>810</v>
       </c>
       <c r="J27" t="n">
         <v>1.01</v>
@@ -1366,28 +1366,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.077</v>
+        <v>0.076</v>
       </c>
       <c r="C28" t="n">
         <v>0.019</v>
       </c>
       <c r="D28" t="n">
-        <v>0.038</v>
+        <v>0.043</v>
       </c>
       <c r="E28" t="n">
         <v>0.11</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>1822</v>
+        <v>1308</v>
       </c>
       <c r="I28" t="n">
-        <v>576</v>
+        <v>811</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -1400,28 +1400,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.222</v>
+        <v>0.228</v>
       </c>
       <c r="C29" t="n">
-        <v>0.061</v>
+        <v>0.062</v>
       </c>
       <c r="D29" t="n">
-        <v>0.121</v>
+        <v>0.122</v>
       </c>
       <c r="E29" t="n">
-        <v>0.339</v>
+        <v>0.337</v>
       </c>
       <c r="F29" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="G29" t="n">
         <v>0.002</v>
       </c>
       <c r="H29" t="n">
-        <v>1813</v>
+        <v>1036</v>
       </c>
       <c r="I29" t="n">
-        <v>836</v>
+        <v>768</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -1434,28 +1434,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.058</v>
+        <v>1.051</v>
       </c>
       <c r="C30" t="n">
-        <v>0.214</v>
+        <v>0.206</v>
       </c>
       <c r="D30" t="n">
-        <v>0.645</v>
+        <v>0.704</v>
       </c>
       <c r="E30" t="n">
-        <v>1.427</v>
+        <v>1.446</v>
       </c>
       <c r="F30" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="G30" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="H30" t="n">
-        <v>1822</v>
+        <v>978</v>
       </c>
       <c r="I30" t="n">
-        <v>680</v>
+        <v>796</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -1468,16 +1468,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.013</v>
+        <v>0.001</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1486,13 +1486,13 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1122</v>
+        <v>455</v>
       </c>
       <c r="I31" t="n">
-        <v>560</v>
+        <v>234</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="32">
@@ -1502,31 +1502,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2015.107</v>
+        <v>42218.176</v>
       </c>
       <c r="C32" t="n">
-        <v>11867.161</v>
+        <v>254035.325</v>
       </c>
       <c r="D32" t="n">
-        <v>24.148</v>
+        <v>480.848</v>
       </c>
       <c r="E32" t="n">
-        <v>4011.734</v>
+        <v>80903.37699999999</v>
       </c>
       <c r="F32" t="n">
-        <v>444.263</v>
+        <v>12197.789</v>
       </c>
       <c r="G32" t="n">
-        <v>3679.616</v>
+        <v>70706.46799999999</v>
       </c>
       <c r="H32" t="n">
-        <v>1122</v>
+        <v>455</v>
       </c>
       <c r="I32" t="n">
-        <v>560</v>
+        <v>234</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
   </sheetData>

--- a/output/diagnostics/Bayesian_parameter(results).xlsx
+++ b/output/diagnostics/Bayesian_parameter(results).xlsx
@@ -482,28 +482,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.968</v>
+        <v>0.882</v>
       </c>
       <c r="C2" t="n">
-        <v>0.203</v>
+        <v>0.217</v>
       </c>
       <c r="D2" t="n">
-        <v>0.615</v>
+        <v>0.519</v>
       </c>
       <c r="E2" t="n">
-        <v>1.358</v>
+        <v>1.313</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="H2" t="n">
-        <v>806</v>
+        <v>1306</v>
       </c>
       <c r="I2" t="n">
-        <v>658</v>
+        <v>890</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -516,28 +516,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.482</v>
+        <v>0.512</v>
       </c>
       <c r="C3" t="n">
-        <v>0.171</v>
+        <v>0.181</v>
       </c>
       <c r="D3" t="n">
-        <v>0.181</v>
+        <v>0.183</v>
       </c>
       <c r="E3" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="H3" t="n">
-        <v>944</v>
+        <v>867</v>
       </c>
       <c r="I3" t="n">
-        <v>647</v>
+        <v>605</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -550,28 +550,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.437</v>
+        <v>0.487</v>
       </c>
       <c r="C4" t="n">
-        <v>0.138</v>
+        <v>0.189</v>
       </c>
       <c r="D4" t="n">
-        <v>0.218</v>
+        <v>0.164</v>
       </c>
       <c r="E4" t="n">
-        <v>0.697</v>
+        <v>0.792</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>931</v>
+        <v>1079</v>
       </c>
       <c r="I4" t="n">
-        <v>779</v>
+        <v>814</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -584,16 +584,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.121</v>
+        <v>0.12</v>
       </c>
       <c r="C5" t="n">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
       <c r="D5" t="n">
-        <v>0.096</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.148</v>
+        <v>0.16</v>
       </c>
       <c r="F5" t="n">
         <v>0.001</v>
@@ -602,13 +602,13 @@
         <v>0.001</v>
       </c>
       <c r="H5" t="n">
-        <v>448</v>
+        <v>543</v>
       </c>
       <c r="I5" t="n">
-        <v>315</v>
+        <v>580</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -618,16 +618,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>0.038</v>
+        <v>0.035</v>
       </c>
       <c r="D6" t="n">
-        <v>0.024</v>
+        <v>0.031</v>
       </c>
       <c r="E6" t="n">
-        <v>0.161</v>
+        <v>0.155</v>
       </c>
       <c r="F6" t="n">
         <v>0.001</v>
@@ -636,10 +636,10 @@
         <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>1449</v>
+        <v>1514</v>
       </c>
       <c r="I6" t="n">
-        <v>696</v>
+        <v>569</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -652,28 +652,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.247</v>
+        <v>1.051</v>
       </c>
       <c r="C7" t="n">
-        <v>0.435</v>
+        <v>0.431</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.378</v>
       </c>
       <c r="E7" t="n">
-        <v>2.101</v>
+        <v>1.863</v>
       </c>
       <c r="F7" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="G7" t="n">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
       <c r="H7" t="n">
-        <v>813</v>
+        <v>1300</v>
       </c>
       <c r="I7" t="n">
-        <v>748</v>
+        <v>655</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.039</v>
+        <v>0.048</v>
       </c>
       <c r="C8" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.015</v>
       </c>
       <c r="D8" t="n">
         <v>0.023</v>
       </c>
       <c r="E8" t="n">
-        <v>0.056</v>
+        <v>0.076</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>812</v>
+        <v>1006</v>
       </c>
       <c r="I8" t="n">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="J8" t="n">
         <v>1.01</v>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.257</v>
+        <v>0.263</v>
       </c>
       <c r="C9" t="n">
         <v>0.058</v>
       </c>
       <c r="D9" t="n">
-        <v>0.15</v>
+        <v>0.166</v>
       </c>
       <c r="E9" t="n">
-        <v>0.365</v>
+        <v>0.368</v>
       </c>
       <c r="F9" t="n">
         <v>0.002</v>
@@ -738,13 +738,13 @@
         <v>0.002</v>
       </c>
       <c r="H9" t="n">
-        <v>1048</v>
+        <v>1225</v>
       </c>
       <c r="I9" t="n">
-        <v>792</v>
+        <v>929</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="10">
@@ -754,16 +754,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.362</v>
+        <v>0.359</v>
       </c>
       <c r="C10" t="n">
-        <v>0.08</v>
+        <v>0.073</v>
       </c>
       <c r="D10" t="n">
-        <v>0.226</v>
+        <v>0.213</v>
       </c>
       <c r="E10" t="n">
-        <v>0.518</v>
+        <v>0.484</v>
       </c>
       <c r="F10" t="n">
         <v>0.002</v>
@@ -772,10 +772,10 @@
         <v>0.002</v>
       </c>
       <c r="H10" t="n">
-        <v>1132</v>
+        <v>1376</v>
       </c>
       <c r="I10" t="n">
-        <v>732</v>
+        <v>751</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -788,16 +788,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="C11" t="n">
         <v>0.005</v>
       </c>
       <c r="D11" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.026</v>
+        <v>0.028</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -806,10 +806,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>473</v>
+        <v>504</v>
       </c>
       <c r="I11" t="n">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="J11" t="n">
         <v>1.01</v>
@@ -822,28 +822,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.766</v>
+        <v>0.734</v>
       </c>
       <c r="C12" t="n">
-        <v>0.249</v>
+        <v>0.259</v>
       </c>
       <c r="D12" t="n">
-        <v>0.334</v>
+        <v>0.283</v>
       </c>
       <c r="E12" t="n">
-        <v>1.236</v>
+        <v>1.213</v>
       </c>
       <c r="F12" t="n">
         <v>0.007</v>
       </c>
       <c r="G12" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="H12" t="n">
-        <v>1346</v>
+        <v>1221</v>
       </c>
       <c r="I12" t="n">
-        <v>782</v>
+        <v>481</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -856,16 +856,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.173</v>
+        <v>0.169</v>
       </c>
       <c r="C13" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.026</v>
+        <v>0.032</v>
       </c>
       <c r="E13" t="n">
-        <v>0.332</v>
+        <v>0.337</v>
       </c>
       <c r="F13" t="n">
         <v>0.002</v>
@@ -874,10 +874,10 @@
         <v>0.003</v>
       </c>
       <c r="H13" t="n">
-        <v>1284</v>
+        <v>1657</v>
       </c>
       <c r="I13" t="n">
-        <v>484</v>
+        <v>677</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -890,31 +890,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.438</v>
+        <v>1.752</v>
       </c>
       <c r="C14" t="n">
-        <v>0.59</v>
+        <v>0.777</v>
       </c>
       <c r="D14" t="n">
-        <v>0.428</v>
+        <v>0.521</v>
       </c>
       <c r="E14" t="n">
-        <v>2.458</v>
+        <v>3.203</v>
       </c>
       <c r="F14" t="n">
-        <v>0.019</v>
+        <v>0.026</v>
       </c>
       <c r="G14" t="n">
-        <v>0.016</v>
+        <v>0.032</v>
       </c>
       <c r="H14" t="n">
-        <v>900</v>
+        <v>815</v>
       </c>
       <c r="I14" t="n">
-        <v>883</v>
+        <v>522</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -924,28 +924,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.407</v>
+        <v>2.417</v>
       </c>
       <c r="C15" t="n">
-        <v>0.538</v>
+        <v>0.525</v>
       </c>
       <c r="D15" t="n">
-        <v>1.448</v>
+        <v>1.555</v>
       </c>
       <c r="E15" t="n">
-        <v>3.439</v>
+        <v>3.444</v>
       </c>
       <c r="F15" t="n">
         <v>0.015</v>
       </c>
       <c r="G15" t="n">
-        <v>0.019</v>
+        <v>0.015</v>
       </c>
       <c r="H15" t="n">
-        <v>1211</v>
+        <v>1119</v>
       </c>
       <c r="I15" t="n">
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -958,28 +958,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.167</v>
+        <v>3.614</v>
       </c>
       <c r="C16" t="n">
-        <v>1.154</v>
+        <v>1.324</v>
       </c>
       <c r="D16" t="n">
-        <v>1.504</v>
+        <v>1.5</v>
       </c>
       <c r="E16" t="n">
-        <v>5.282</v>
+        <v>5.711</v>
       </c>
       <c r="F16" t="n">
-        <v>0.039</v>
+        <v>0.043</v>
       </c>
       <c r="G16" t="n">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="H16" t="n">
-        <v>871</v>
+        <v>942</v>
       </c>
       <c r="I16" t="n">
-        <v>765</v>
+        <v>577</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -992,31 +992,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.543</v>
+        <v>0.749</v>
       </c>
       <c r="C17" t="n">
-        <v>0.311</v>
+        <v>0.425</v>
       </c>
       <c r="D17" t="n">
-        <v>0.061</v>
+        <v>0.094</v>
       </c>
       <c r="E17" t="n">
-        <v>1.074</v>
+        <v>1.533</v>
       </c>
       <c r="F17" t="n">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="G17" t="n">
-        <v>0.017</v>
+        <v>0.013</v>
       </c>
       <c r="H17" t="n">
-        <v>508</v>
+        <v>1084</v>
       </c>
       <c r="I17" t="n">
-        <v>400</v>
+        <v>728</v>
       </c>
       <c r="J17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1026,28 +1026,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.582</v>
+        <v>0.616</v>
       </c>
       <c r="C18" t="n">
-        <v>0.264</v>
+        <v>0.282</v>
       </c>
       <c r="D18" t="n">
-        <v>0.158</v>
+        <v>0.189</v>
       </c>
       <c r="E18" t="n">
-        <v>1.072</v>
+        <v>1.163</v>
       </c>
       <c r="F18" t="n">
         <v>0.008</v>
       </c>
       <c r="G18" t="n">
-        <v>0.008</v>
+        <v>0.014</v>
       </c>
       <c r="H18" t="n">
-        <v>1053</v>
+        <v>1176</v>
       </c>
       <c r="I18" t="n">
-        <v>761</v>
+        <v>581</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -1060,31 +1060,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22.631</v>
+        <v>23.011</v>
       </c>
       <c r="C19" t="n">
-        <v>1.739</v>
+        <v>1.7</v>
       </c>
       <c r="D19" t="n">
-        <v>20.014</v>
+        <v>20.024</v>
       </c>
       <c r="E19" t="n">
-        <v>25.517</v>
+        <v>25.618</v>
       </c>
       <c r="F19" t="n">
-        <v>0.052</v>
+        <v>0.05</v>
       </c>
       <c r="G19" t="n">
-        <v>0.033</v>
+        <v>0.041</v>
       </c>
       <c r="H19" t="n">
-        <v>1003</v>
+        <v>932</v>
       </c>
       <c r="I19" t="n">
-        <v>764</v>
+        <v>595</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="20">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.671</v>
+        <v>0.668</v>
       </c>
       <c r="C20" t="n">
-        <v>0.204</v>
+        <v>0.194</v>
       </c>
       <c r="D20" t="n">
-        <v>0.361</v>
+        <v>0.359</v>
       </c>
       <c r="E20" t="n">
-        <v>1.088</v>
+        <v>1.068</v>
       </c>
       <c r="F20" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="G20" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="H20" t="n">
-        <v>1152</v>
+        <v>1525</v>
       </c>
       <c r="I20" t="n">
-        <v>751</v>
+        <v>851</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="21">
@@ -1128,31 +1128,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.212</v>
+        <v>0.229</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06</v>
+        <v>0.093</v>
       </c>
       <c r="D21" t="n">
-        <v>0.118</v>
+        <v>0.08</v>
       </c>
       <c r="E21" t="n">
-        <v>0.327</v>
+        <v>0.401</v>
       </c>
       <c r="F21" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="G21" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="H21" t="n">
-        <v>763</v>
+        <v>1210</v>
       </c>
       <c r="I21" t="n">
-        <v>824</v>
+        <v>737</v>
       </c>
       <c r="J21" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1162,16 +1162,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="C22" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="D22" t="n">
         <v>0.042</v>
       </c>
       <c r="E22" t="n">
-        <v>0.061</v>
+        <v>0.063</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>476</v>
+        <v>507</v>
       </c>
       <c r="I22" t="n">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="J22" t="n">
         <v>1.01</v>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.134</v>
+        <v>0.13</v>
       </c>
       <c r="D23" t="n">
-        <v>0.449</v>
+        <v>0.447</v>
       </c>
       <c r="E23" t="n">
-        <v>0.928</v>
+        <v>0.92</v>
       </c>
       <c r="F23" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="G23" t="n">
         <v>0.004</v>
       </c>
       <c r="H23" t="n">
-        <v>1362</v>
+        <v>1528</v>
       </c>
       <c r="I23" t="n">
-        <v>834</v>
+        <v>753</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -1236,7 +1236,7 @@
         <v>0.018</v>
       </c>
       <c r="D24" t="n">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
       <c r="E24" t="n">
         <v>0.08500000000000001</v>
@@ -1248,13 +1248,13 @@
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>1073</v>
+        <v>1107</v>
       </c>
       <c r="I24" t="n">
-        <v>497</v>
+        <v>513</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="25">
@@ -1264,16 +1264,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.038</v>
+        <v>0.035</v>
       </c>
       <c r="C25" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.023</v>
+        <v>0.02</v>
       </c>
       <c r="E25" t="n">
-        <v>0.054</v>
+        <v>0.053</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1282,13 +1282,13 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1071</v>
+        <v>1141</v>
       </c>
       <c r="I25" t="n">
-        <v>791</v>
+        <v>609</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="26">
@@ -1304,7 +1304,7 @@
         <v>0.006</v>
       </c>
       <c r="D26" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
       <c r="E26" t="n">
         <v>0.033</v>
@@ -1316,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1115</v>
+        <v>990</v>
       </c>
       <c r="I26" t="n">
-        <v>874</v>
+        <v>617</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -1332,28 +1332,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.188</v>
+        <v>3.19</v>
       </c>
       <c r="C27" t="n">
-        <v>0.651</v>
+        <v>0.631</v>
       </c>
       <c r="D27" t="n">
-        <v>2.069</v>
+        <v>2.172</v>
       </c>
       <c r="E27" t="n">
-        <v>4.407</v>
+        <v>4.461</v>
       </c>
       <c r="F27" t="n">
         <v>0.019</v>
       </c>
       <c r="G27" t="n">
-        <v>0.022</v>
+        <v>0.025</v>
       </c>
       <c r="H27" t="n">
-        <v>1259</v>
+        <v>1220</v>
       </c>
       <c r="I27" t="n">
-        <v>810</v>
+        <v>668</v>
       </c>
       <c r="J27" t="n">
         <v>1.01</v>
@@ -1366,16 +1366,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.076</v>
+        <v>0.077</v>
       </c>
       <c r="C28" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="D28" t="n">
-        <v>0.043</v>
+        <v>0.044</v>
       </c>
       <c r="E28" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
       <c r="F28" t="n">
         <v>0.001</v>
@@ -1384,10 +1384,10 @@
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>1308</v>
+        <v>1123</v>
       </c>
       <c r="I28" t="n">
-        <v>811</v>
+        <v>673</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.228</v>
+        <v>0.221</v>
       </c>
       <c r="C29" t="n">
-        <v>0.062</v>
+        <v>0.058</v>
       </c>
       <c r="D29" t="n">
-        <v>0.122</v>
+        <v>0.119</v>
       </c>
       <c r="E29" t="n">
-        <v>0.337</v>
+        <v>0.326</v>
       </c>
       <c r="F29" t="n">
         <v>0.002</v>
@@ -1418,13 +1418,13 @@
         <v>0.002</v>
       </c>
       <c r="H29" t="n">
-        <v>1036</v>
+        <v>1022</v>
       </c>
       <c r="I29" t="n">
-        <v>768</v>
+        <v>820</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="30">
@@ -1434,28 +1434,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.051</v>
+        <v>1.062</v>
       </c>
       <c r="C30" t="n">
-        <v>0.206</v>
+        <v>0.233</v>
       </c>
       <c r="D30" t="n">
-        <v>0.704</v>
+        <v>0.654</v>
       </c>
       <c r="E30" t="n">
-        <v>1.446</v>
+        <v>1.501</v>
       </c>
       <c r="F30" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="G30" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="H30" t="n">
-        <v>978</v>
+        <v>1389</v>
       </c>
       <c r="I30" t="n">
-        <v>796</v>
+        <v>783</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -1468,16 +1468,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.001</v>
+        <v>0.012</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1486,13 +1486,13 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>455</v>
+        <v>756</v>
       </c>
       <c r="I31" t="n">
-        <v>234</v>
+        <v>361</v>
       </c>
       <c r="J31" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1502,28 +1502,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>42218.176</v>
+        <v>1702.673</v>
       </c>
       <c r="C32" t="n">
-        <v>254035.325</v>
+        <v>13143.777</v>
       </c>
       <c r="D32" t="n">
-        <v>480.848</v>
+        <v>20.572</v>
       </c>
       <c r="E32" t="n">
-        <v>80903.37699999999</v>
+        <v>4043.386</v>
       </c>
       <c r="F32" t="n">
-        <v>12197.789</v>
+        <v>442.994</v>
       </c>
       <c r="G32" t="n">
-        <v>70706.46799999999</v>
+        <v>5749.596</v>
       </c>
       <c r="H32" t="n">
-        <v>455</v>
+        <v>756</v>
       </c>
       <c r="I32" t="n">
-        <v>234</v>
+        <v>361</v>
       </c>
       <c r="J32" t="n">
         <v>1.01</v>

--- a/output/diagnostics/Bayesian_parameter(results).xlsx
+++ b/output/diagnostics/Bayesian_parameter(results).xlsx
@@ -482,28 +482,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.882</v>
+        <v>0.959</v>
       </c>
       <c r="C2" t="n">
-        <v>0.217</v>
+        <v>0.197</v>
       </c>
       <c r="D2" t="n">
-        <v>0.519</v>
+        <v>0.625</v>
       </c>
       <c r="E2" t="n">
-        <v>1.313</v>
+        <v>1.357</v>
       </c>
       <c r="F2" t="n">
         <v>0.006</v>
       </c>
       <c r="G2" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="H2" t="n">
-        <v>1306</v>
+        <v>1183</v>
       </c>
       <c r="I2" t="n">
-        <v>890</v>
+        <v>629</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -516,28 +516,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.512</v>
+        <v>0.471</v>
       </c>
       <c r="C3" t="n">
-        <v>0.181</v>
+        <v>0.149</v>
       </c>
       <c r="D3" t="n">
-        <v>0.183</v>
+        <v>0.21</v>
       </c>
       <c r="E3" t="n">
-        <v>0.83</v>
+        <v>0.751</v>
       </c>
       <c r="F3" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.006</v>
       </c>
-      <c r="G3" t="n">
-        <v>0.007</v>
-      </c>
       <c r="H3" t="n">
-        <v>867</v>
+        <v>2106</v>
       </c>
       <c r="I3" t="n">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -550,28 +550,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.487</v>
+        <v>0.44</v>
       </c>
       <c r="C4" t="n">
-        <v>0.189</v>
+        <v>0.143</v>
       </c>
       <c r="D4" t="n">
-        <v>0.164</v>
+        <v>0.236</v>
       </c>
       <c r="E4" t="n">
-        <v>0.792</v>
+        <v>0.722</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="H4" t="n">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="I4" t="n">
-        <v>814</v>
+        <v>854</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -584,28 +584,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.12</v>
+        <v>0.118</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.16</v>
+        <v>0.142</v>
       </c>
       <c r="F5" t="n">
         <v>0.001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>543</v>
+        <v>736</v>
       </c>
       <c r="I5" t="n">
-        <v>580</v>
+        <v>783</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -618,16 +618,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.035</v>
+        <v>0.033</v>
       </c>
       <c r="D6" t="n">
-        <v>0.031</v>
+        <v>0.024</v>
       </c>
       <c r="E6" t="n">
-        <v>0.155</v>
+        <v>0.148</v>
       </c>
       <c r="F6" t="n">
         <v>0.001</v>
@@ -636,10 +636,10 @@
         <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>1514</v>
+        <v>1219</v>
       </c>
       <c r="I6" t="n">
-        <v>569</v>
+        <v>733</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.051</v>
+        <v>1.295</v>
       </c>
       <c r="C7" t="n">
-        <v>0.431</v>
+        <v>0.48</v>
       </c>
       <c r="D7" t="n">
-        <v>0.378</v>
+        <v>0.606</v>
       </c>
       <c r="E7" t="n">
-        <v>1.863</v>
+        <v>2.215</v>
       </c>
       <c r="F7" t="n">
         <v>0.014</v>
@@ -670,13 +670,13 @@
         <v>0.019</v>
       </c>
       <c r="H7" t="n">
-        <v>1300</v>
+        <v>1202</v>
       </c>
       <c r="I7" t="n">
-        <v>655</v>
+        <v>733</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="8">
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.048</v>
+        <v>0.042</v>
       </c>
       <c r="C8" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D8" t="n">
-        <v>0.023</v>
+        <v>0.025</v>
       </c>
       <c r="E8" t="n">
-        <v>0.076</v>
+        <v>0.06</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1006</v>
+        <v>1639</v>
       </c>
       <c r="I8" t="n">
-        <v>717</v>
+        <v>750</v>
       </c>
       <c r="J8" t="n">
         <v>1.01</v>
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.263</v>
+        <v>0.253</v>
       </c>
       <c r="C9" t="n">
-        <v>0.058</v>
+        <v>0.055</v>
       </c>
       <c r="D9" t="n">
-        <v>0.166</v>
+        <v>0.155</v>
       </c>
       <c r="E9" t="n">
-        <v>0.368</v>
+        <v>0.36</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="G9" t="n">
         <v>0.002</v>
       </c>
       <c r="H9" t="n">
-        <v>1225</v>
+        <v>1629</v>
       </c>
       <c r="I9" t="n">
-        <v>929</v>
+        <v>657</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -754,16 +754,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.359</v>
+        <v>0.354</v>
       </c>
       <c r="C10" t="n">
-        <v>0.073</v>
+        <v>0.075</v>
       </c>
       <c r="D10" t="n">
-        <v>0.213</v>
+        <v>0.223</v>
       </c>
       <c r="E10" t="n">
-        <v>0.484</v>
+        <v>0.499</v>
       </c>
       <c r="F10" t="n">
         <v>0.002</v>
@@ -772,10 +772,10 @@
         <v>0.002</v>
       </c>
       <c r="H10" t="n">
-        <v>1376</v>
+        <v>1242</v>
       </c>
       <c r="I10" t="n">
-        <v>751</v>
+        <v>761</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -788,16 +788,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="C11" t="n">
         <v>0.005</v>
       </c>
       <c r="D11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="E11" t="n">
-        <v>0.028</v>
+        <v>0.025</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -806,10 +806,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>504</v>
+        <v>598</v>
       </c>
       <c r="I11" t="n">
-        <v>623</v>
+        <v>656</v>
       </c>
       <c r="J11" t="n">
         <v>1.01</v>
@@ -822,28 +822,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.734</v>
+        <v>0.755</v>
       </c>
       <c r="C12" t="n">
-        <v>0.259</v>
+        <v>0.235</v>
       </c>
       <c r="D12" t="n">
-        <v>0.283</v>
+        <v>0.384</v>
       </c>
       <c r="E12" t="n">
-        <v>1.213</v>
+        <v>1.254</v>
       </c>
       <c r="F12" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="G12" t="n">
         <v>0.007</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.01</v>
-      </c>
       <c r="H12" t="n">
-        <v>1221</v>
+        <v>1437</v>
       </c>
       <c r="I12" t="n">
-        <v>481</v>
+        <v>856</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -856,16 +856,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.169</v>
+        <v>0.175</v>
       </c>
       <c r="C13" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="D13" t="n">
-        <v>0.032</v>
+        <v>0.022</v>
       </c>
       <c r="E13" t="n">
-        <v>0.337</v>
+        <v>0.345</v>
       </c>
       <c r="F13" t="n">
         <v>0.002</v>
@@ -874,10 +874,10 @@
         <v>0.003</v>
       </c>
       <c r="H13" t="n">
-        <v>1657</v>
+        <v>1397</v>
       </c>
       <c r="I13" t="n">
-        <v>677</v>
+        <v>500</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -890,28 +890,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.752</v>
+        <v>1.521</v>
       </c>
       <c r="C14" t="n">
-        <v>0.777</v>
+        <v>0.644</v>
       </c>
       <c r="D14" t="n">
-        <v>0.521</v>
+        <v>0.485</v>
       </c>
       <c r="E14" t="n">
-        <v>3.203</v>
+        <v>2.763</v>
       </c>
       <c r="F14" t="n">
-        <v>0.026</v>
+        <v>0.02</v>
       </c>
       <c r="G14" t="n">
-        <v>0.032</v>
+        <v>0.02</v>
       </c>
       <c r="H14" t="n">
-        <v>815</v>
+        <v>983</v>
       </c>
       <c r="I14" t="n">
-        <v>522</v>
+        <v>812</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -924,28 +924,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.417</v>
+        <v>2.419</v>
       </c>
       <c r="C15" t="n">
-        <v>0.525</v>
+        <v>0.541</v>
       </c>
       <c r="D15" t="n">
-        <v>1.555</v>
+        <v>1.388</v>
       </c>
       <c r="E15" t="n">
-        <v>3.444</v>
+        <v>3.382</v>
       </c>
       <c r="F15" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="G15" t="n">
-        <v>0.015</v>
+        <v>0.018</v>
       </c>
       <c r="H15" t="n">
-        <v>1119</v>
+        <v>1364</v>
       </c>
       <c r="I15" t="n">
-        <v>629</v>
+        <v>591</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -958,31 +958,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.614</v>
+        <v>3.294</v>
       </c>
       <c r="C16" t="n">
-        <v>1.324</v>
+        <v>1.244</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5</v>
+        <v>1.505</v>
       </c>
       <c r="E16" t="n">
-        <v>5.711</v>
+        <v>5.52</v>
       </c>
       <c r="F16" t="n">
-        <v>0.043</v>
+        <v>0.039</v>
       </c>
       <c r="G16" t="n">
-        <v>0.026</v>
+        <v>0.028</v>
       </c>
       <c r="H16" t="n">
-        <v>942</v>
+        <v>1048</v>
       </c>
       <c r="I16" t="n">
-        <v>577</v>
+        <v>738</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="17">
@@ -992,28 +992,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.749</v>
+        <v>0.667</v>
       </c>
       <c r="C17" t="n">
-        <v>0.425</v>
+        <v>0.298</v>
       </c>
       <c r="D17" t="n">
-        <v>0.094</v>
+        <v>0.173</v>
       </c>
       <c r="E17" t="n">
-        <v>1.533</v>
+        <v>1.171</v>
       </c>
       <c r="F17" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="G17" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="H17" t="n">
-        <v>1084</v>
+        <v>800</v>
       </c>
       <c r="I17" t="n">
-        <v>728</v>
+        <v>806</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -1026,28 +1026,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.616</v>
+        <v>0.599</v>
       </c>
       <c r="C18" t="n">
-        <v>0.282</v>
+        <v>0.288</v>
       </c>
       <c r="D18" t="n">
-        <v>0.189</v>
+        <v>0.125</v>
       </c>
       <c r="E18" t="n">
-        <v>1.163</v>
+        <v>1.113</v>
       </c>
       <c r="F18" t="n">
         <v>0.008</v>
       </c>
       <c r="G18" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="H18" t="n">
-        <v>1176</v>
+        <v>1395</v>
       </c>
       <c r="I18" t="n">
-        <v>581</v>
+        <v>697</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -1060,31 +1060,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23.011</v>
+        <v>22.528</v>
       </c>
       <c r="C19" t="n">
-        <v>1.7</v>
+        <v>1.644</v>
       </c>
       <c r="D19" t="n">
-        <v>20.024</v>
+        <v>20.019</v>
       </c>
       <c r="E19" t="n">
-        <v>25.618</v>
+        <v>25.282</v>
       </c>
       <c r="F19" t="n">
-        <v>0.05</v>
+        <v>0.044</v>
       </c>
       <c r="G19" t="n">
-        <v>0.041</v>
+        <v>0.032</v>
       </c>
       <c r="H19" t="n">
-        <v>932</v>
+        <v>1359</v>
       </c>
       <c r="I19" t="n">
-        <v>595</v>
+        <v>709</v>
       </c>
       <c r="J19" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.668</v>
+        <v>0.667</v>
       </c>
       <c r="C20" t="n">
-        <v>0.194</v>
+        <v>0.191</v>
       </c>
       <c r="D20" t="n">
-        <v>0.359</v>
+        <v>0.329</v>
       </c>
       <c r="E20" t="n">
-        <v>1.068</v>
+        <v>1.022</v>
       </c>
       <c r="F20" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="G20" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="H20" t="n">
-        <v>1525</v>
+        <v>1743</v>
       </c>
       <c r="I20" t="n">
-        <v>851</v>
+        <v>664</v>
       </c>
       <c r="J20" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1128,31 +1128,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.229</v>
+        <v>0.237</v>
       </c>
       <c r="C21" t="n">
-        <v>0.093</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>0.08</v>
+        <v>0.134</v>
       </c>
       <c r="E21" t="n">
-        <v>0.401</v>
+        <v>0.368</v>
       </c>
       <c r="F21" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G21" t="n">
         <v>0.003</v>
       </c>
-      <c r="G21" t="n">
-        <v>0.004</v>
-      </c>
       <c r="H21" t="n">
-        <v>1210</v>
+        <v>1081</v>
       </c>
       <c r="I21" t="n">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="22">
@@ -1162,16 +1162,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="C22" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="D22" t="n">
-        <v>0.042</v>
+        <v>0.041</v>
       </c>
       <c r="E22" t="n">
-        <v>0.063</v>
+        <v>0.059</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1180,13 +1180,13 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>507</v>
+        <v>595</v>
       </c>
       <c r="I22" t="n">
-        <v>610</v>
+        <v>694</v>
       </c>
       <c r="J22" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>0.13</v>
+        <v>0.138</v>
       </c>
       <c r="D23" t="n">
-        <v>0.447</v>
+        <v>0.417</v>
       </c>
       <c r="E23" t="n">
-        <v>0.92</v>
+        <v>0.907</v>
       </c>
       <c r="F23" t="n">
         <v>0.003</v>
@@ -1214,13 +1214,13 @@
         <v>0.004</v>
       </c>
       <c r="H23" t="n">
-        <v>1528</v>
+        <v>1791</v>
       </c>
       <c r="I23" t="n">
-        <v>753</v>
+        <v>630</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="24">
@@ -1233,25 +1233,25 @@
         <v>0.049</v>
       </c>
       <c r="C24" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="D24" t="n">
-        <v>0.019</v>
+        <v>0.014</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="F24" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>1107</v>
+        <v>1846</v>
       </c>
       <c r="I24" t="n">
-        <v>513</v>
+        <v>768</v>
       </c>
       <c r="J24" t="n">
         <v>1.01</v>
@@ -1264,16 +1264,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.035</v>
+        <v>0.037</v>
       </c>
       <c r="C25" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="E25" t="n">
-        <v>0.053</v>
+        <v>0.056</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1282,13 +1282,13 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1141</v>
+        <v>1545</v>
       </c>
       <c r="I25" t="n">
-        <v>609</v>
+        <v>805</v>
       </c>
       <c r="J25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1298,13 +1298,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="C26" t="n">
         <v>0.006</v>
       </c>
       <c r="D26" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="E26" t="n">
         <v>0.033</v>
@@ -1316,13 +1316,13 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>990</v>
+        <v>1820</v>
       </c>
       <c r="I26" t="n">
-        <v>617</v>
+        <v>510</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="27">
@@ -1332,31 +1332,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.19</v>
+        <v>3.213</v>
       </c>
       <c r="C27" t="n">
-        <v>0.631</v>
+        <v>0.652</v>
       </c>
       <c r="D27" t="n">
-        <v>2.172</v>
+        <v>2.105</v>
       </c>
       <c r="E27" t="n">
-        <v>4.461</v>
+        <v>4.448</v>
       </c>
       <c r="F27" t="n">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
       <c r="G27" t="n">
-        <v>0.025</v>
+        <v>0.022</v>
       </c>
       <c r="H27" t="n">
-        <v>1220</v>
+        <v>1449</v>
       </c>
       <c r="I27" t="n">
-        <v>668</v>
+        <v>805</v>
       </c>
       <c r="J27" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1372,25 +1372,25 @@
         <v>0.018</v>
       </c>
       <c r="D28" t="n">
-        <v>0.044</v>
+        <v>0.045</v>
       </c>
       <c r="E28" t="n">
         <v>0.109</v>
       </c>
       <c r="F28" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>1123</v>
+        <v>3000</v>
       </c>
       <c r="I28" t="n">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="29">
@@ -1400,28 +1400,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.221</v>
+        <v>0.225</v>
       </c>
       <c r="C29" t="n">
-        <v>0.058</v>
+        <v>0.061</v>
       </c>
       <c r="D29" t="n">
-        <v>0.119</v>
+        <v>0.125</v>
       </c>
       <c r="E29" t="n">
-        <v>0.326</v>
+        <v>0.345</v>
       </c>
       <c r="F29" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="G29" t="n">
         <v>0.002</v>
       </c>
       <c r="H29" t="n">
-        <v>1022</v>
+        <v>1947</v>
       </c>
       <c r="I29" t="n">
-        <v>820</v>
+        <v>893</v>
       </c>
       <c r="J29" t="n">
         <v>1.01</v>
@@ -1434,28 +1434,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.062</v>
+        <v>1.067</v>
       </c>
       <c r="C30" t="n">
-        <v>0.233</v>
+        <v>0.218</v>
       </c>
       <c r="D30" t="n">
-        <v>0.654</v>
+        <v>0.655</v>
       </c>
       <c r="E30" t="n">
-        <v>1.501</v>
+        <v>1.45</v>
       </c>
       <c r="F30" t="n">
         <v>0.006</v>
       </c>
       <c r="G30" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>1389</v>
+        <v>1645</v>
       </c>
       <c r="I30" t="n">
-        <v>783</v>
+        <v>661</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -1468,16 +1468,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.012</v>
+        <v>0.001</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1486,10 +1486,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>756</v>
+        <v>1188</v>
       </c>
       <c r="I31" t="n">
-        <v>361</v>
+        <v>509</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -1502,31 +1502,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1702.673</v>
+        <v>30866.62</v>
       </c>
       <c r="C32" t="n">
-        <v>13143.777</v>
+        <v>307440.105</v>
       </c>
       <c r="D32" t="n">
-        <v>20.572</v>
+        <v>498.659</v>
       </c>
       <c r="E32" t="n">
-        <v>4043.386</v>
+        <v>62924.794</v>
       </c>
       <c r="F32" t="n">
-        <v>442.994</v>
+        <v>9800.559999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>5749.596</v>
+        <v>142624.822</v>
       </c>
       <c r="H32" t="n">
-        <v>756</v>
+        <v>1188</v>
       </c>
       <c r="I32" t="n">
-        <v>361</v>
+        <v>509</v>
       </c>
       <c r="J32" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/diagnostics/Bayesian_parameter(results).xlsx
+++ b/output/diagnostics/Bayesian_parameter(results).xlsx
@@ -482,28 +482,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.959</v>
+        <v>0.998</v>
       </c>
       <c r="C2" t="n">
-        <v>0.197</v>
+        <v>0.208</v>
       </c>
       <c r="D2" t="n">
-        <v>0.625</v>
+        <v>0.624</v>
       </c>
       <c r="E2" t="n">
-        <v>1.357</v>
+        <v>1.404</v>
       </c>
       <c r="F2" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="G2" t="n">
         <v>0.006</v>
       </c>
       <c r="H2" t="n">
-        <v>1183</v>
+        <v>887</v>
       </c>
       <c r="I2" t="n">
-        <v>629</v>
+        <v>722</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -516,28 +516,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.471</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.149</v>
+        <v>0.177</v>
       </c>
       <c r="D3" t="n">
-        <v>0.21</v>
+        <v>0.257</v>
       </c>
       <c r="E3" t="n">
-        <v>0.751</v>
+        <v>0.874</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="G3" t="n">
         <v>0.006</v>
       </c>
       <c r="H3" t="n">
-        <v>2106</v>
+        <v>1182</v>
       </c>
       <c r="I3" t="n">
-        <v>593</v>
+        <v>792</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -550,28 +550,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.44</v>
+        <v>0.586</v>
       </c>
       <c r="C4" t="n">
-        <v>0.143</v>
+        <v>0.178</v>
       </c>
       <c r="D4" t="n">
-        <v>0.236</v>
+        <v>0.271</v>
       </c>
       <c r="E4" t="n">
-        <v>0.722</v>
+        <v>0.899</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="H4" t="n">
-        <v>1077</v>
+        <v>886</v>
       </c>
       <c r="I4" t="n">
-        <v>854</v>
+        <v>757</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -584,16 +584,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.118</v>
+        <v>0.12</v>
       </c>
       <c r="C5" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.095</v>
       </c>
       <c r="E5" t="n">
-        <v>0.142</v>
+        <v>0.148</v>
       </c>
       <c r="F5" t="n">
         <v>0.001</v>
@@ -602,10 +602,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>736</v>
+        <v>464</v>
       </c>
       <c r="I5" t="n">
-        <v>783</v>
+        <v>677</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -618,16 +618,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.033</v>
+        <v>0.036</v>
       </c>
       <c r="D6" t="n">
-        <v>0.024</v>
+        <v>0.022</v>
       </c>
       <c r="E6" t="n">
-        <v>0.148</v>
+        <v>0.15</v>
       </c>
       <c r="F6" t="n">
         <v>0.001</v>
@@ -636,10 +636,10 @@
         <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>1219</v>
+        <v>1113</v>
       </c>
       <c r="I6" t="n">
-        <v>733</v>
+        <v>588</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -652,31 +652,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.295</v>
+        <v>1.37</v>
       </c>
       <c r="C7" t="n">
-        <v>0.48</v>
+        <v>0.494</v>
       </c>
       <c r="D7" t="n">
-        <v>0.606</v>
+        <v>0.521</v>
       </c>
       <c r="E7" t="n">
-        <v>2.215</v>
+        <v>2.24</v>
       </c>
       <c r="F7" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="G7" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="H7" t="n">
-        <v>1202</v>
+        <v>928</v>
       </c>
       <c r="I7" t="n">
-        <v>733</v>
+        <v>622</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -689,13 +689,13 @@
         <v>0.042</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D8" t="n">
         <v>0.025</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06</v>
+        <v>0.058</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1639</v>
+        <v>989</v>
       </c>
       <c r="I8" t="n">
-        <v>750</v>
+        <v>733</v>
       </c>
       <c r="J8" t="n">
         <v>1.01</v>
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.253</v>
+        <v>0.257</v>
       </c>
       <c r="C9" t="n">
-        <v>0.055</v>
+        <v>0.06</v>
       </c>
       <c r="D9" t="n">
-        <v>0.155</v>
+        <v>0.145</v>
       </c>
       <c r="E9" t="n">
-        <v>0.36</v>
+        <v>0.367</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="G9" t="n">
         <v>0.002</v>
       </c>
       <c r="H9" t="n">
-        <v>1629</v>
+        <v>792</v>
       </c>
       <c r="I9" t="n">
-        <v>657</v>
+        <v>580</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="10">
@@ -754,16 +754,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.354</v>
+        <v>0.356</v>
       </c>
       <c r="C10" t="n">
-        <v>0.075</v>
+        <v>0.074</v>
       </c>
       <c r="D10" t="n">
         <v>0.223</v>
       </c>
       <c r="E10" t="n">
-        <v>0.499</v>
+        <v>0.498</v>
       </c>
       <c r="F10" t="n">
         <v>0.002</v>
@@ -772,10 +772,10 @@
         <v>0.002</v>
       </c>
       <c r="H10" t="n">
-        <v>1242</v>
+        <v>1154</v>
       </c>
       <c r="I10" t="n">
-        <v>761</v>
+        <v>739</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -797,7 +797,7 @@
         <v>0.008</v>
       </c>
       <c r="E11" t="n">
-        <v>0.025</v>
+        <v>0.027</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -806,10 +806,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>598</v>
+        <v>405</v>
       </c>
       <c r="I11" t="n">
-        <v>656</v>
+        <v>508</v>
       </c>
       <c r="J11" t="n">
         <v>1.01</v>
@@ -822,28 +822,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.755</v>
+        <v>0.779</v>
       </c>
       <c r="C12" t="n">
-        <v>0.235</v>
+        <v>0.263</v>
       </c>
       <c r="D12" t="n">
-        <v>0.384</v>
+        <v>0.331</v>
       </c>
       <c r="E12" t="n">
-        <v>1.254</v>
+        <v>1.271</v>
       </c>
       <c r="F12" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="G12" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="H12" t="n">
-        <v>1437</v>
+        <v>973</v>
       </c>
       <c r="I12" t="n">
-        <v>856</v>
+        <v>667</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -859,28 +859,28 @@
         <v>0.175</v>
       </c>
       <c r="C13" t="n">
-        <v>0.092</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.022</v>
+        <v>0.031</v>
       </c>
       <c r="E13" t="n">
-        <v>0.345</v>
+        <v>0.333</v>
       </c>
       <c r="F13" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="G13" t="n">
         <v>0.003</v>
       </c>
       <c r="H13" t="n">
-        <v>1397</v>
+        <v>1115</v>
       </c>
       <c r="I13" t="n">
-        <v>500</v>
+        <v>588</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="14">
@@ -890,28 +890,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.521</v>
+        <v>1.495</v>
       </c>
       <c r="C14" t="n">
-        <v>0.644</v>
+        <v>0.635</v>
       </c>
       <c r="D14" t="n">
-        <v>0.485</v>
+        <v>0.508</v>
       </c>
       <c r="E14" t="n">
-        <v>2.763</v>
+        <v>2.684</v>
       </c>
       <c r="F14" t="n">
         <v>0.02</v>
       </c>
       <c r="G14" t="n">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="H14" t="n">
-        <v>983</v>
+        <v>930</v>
       </c>
       <c r="I14" t="n">
-        <v>812</v>
+        <v>731</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -924,28 +924,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.419</v>
+        <v>2.399</v>
       </c>
       <c r="C15" t="n">
-        <v>0.541</v>
+        <v>0.537</v>
       </c>
       <c r="D15" t="n">
-        <v>1.388</v>
+        <v>1.424</v>
       </c>
       <c r="E15" t="n">
-        <v>3.382</v>
+        <v>3.32</v>
       </c>
       <c r="F15" t="n">
         <v>0.014</v>
       </c>
       <c r="G15" t="n">
-        <v>0.018</v>
+        <v>0.022</v>
       </c>
       <c r="H15" t="n">
-        <v>1364</v>
+        <v>1457</v>
       </c>
       <c r="I15" t="n">
-        <v>591</v>
+        <v>742</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -958,31 +958,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.294</v>
+        <v>3.232</v>
       </c>
       <c r="C16" t="n">
-        <v>1.244</v>
+        <v>1.222</v>
       </c>
       <c r="D16" t="n">
-        <v>1.505</v>
+        <v>1.501</v>
       </c>
       <c r="E16" t="n">
-        <v>5.52</v>
+        <v>5.403</v>
       </c>
       <c r="F16" t="n">
-        <v>0.039</v>
+        <v>0.045</v>
       </c>
       <c r="G16" t="n">
-        <v>0.028</v>
+        <v>0.024</v>
       </c>
       <c r="H16" t="n">
-        <v>1048</v>
+        <v>718</v>
       </c>
       <c r="I16" t="n">
-        <v>738</v>
+        <v>659</v>
       </c>
       <c r="J16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -992,28 +992,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.667</v>
+        <v>0.672</v>
       </c>
       <c r="C17" t="n">
-        <v>0.298</v>
+        <v>0.344</v>
       </c>
       <c r="D17" t="n">
-        <v>0.173</v>
+        <v>0.127</v>
       </c>
       <c r="E17" t="n">
-        <v>1.171</v>
+        <v>1.338</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="H17" t="n">
-        <v>800</v>
+        <v>680</v>
       </c>
       <c r="I17" t="n">
-        <v>806</v>
+        <v>593</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -1026,28 +1026,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.599</v>
+        <v>0.6</v>
       </c>
       <c r="C18" t="n">
-        <v>0.288</v>
+        <v>0.276</v>
       </c>
       <c r="D18" t="n">
-        <v>0.125</v>
+        <v>0.185</v>
       </c>
       <c r="E18" t="n">
-        <v>1.113</v>
+        <v>1.109</v>
       </c>
       <c r="F18" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="H18" t="n">
-        <v>1395</v>
+        <v>957</v>
       </c>
       <c r="I18" t="n">
-        <v>697</v>
+        <v>655</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -1060,28 +1060,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22.528</v>
+        <v>22.681</v>
       </c>
       <c r="C19" t="n">
-        <v>1.644</v>
+        <v>1.619</v>
       </c>
       <c r="D19" t="n">
-        <v>20.019</v>
+        <v>20.013</v>
       </c>
       <c r="E19" t="n">
-        <v>25.282</v>
+        <v>25.315</v>
       </c>
       <c r="F19" t="n">
-        <v>0.044</v>
+        <v>0.045</v>
       </c>
       <c r="G19" t="n">
-        <v>0.032</v>
+        <v>0.034</v>
       </c>
       <c r="H19" t="n">
-        <v>1359</v>
+        <v>1181</v>
       </c>
       <c r="I19" t="n">
-        <v>709</v>
+        <v>739</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.667</v>
+        <v>0.629</v>
       </c>
       <c r="C20" t="n">
-        <v>0.191</v>
+        <v>0.2</v>
       </c>
       <c r="D20" t="n">
-        <v>0.329</v>
+        <v>0.31</v>
       </c>
       <c r="E20" t="n">
-        <v>1.022</v>
+        <v>1.024</v>
       </c>
       <c r="F20" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="G20" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="H20" t="n">
-        <v>1743</v>
+        <v>993</v>
       </c>
       <c r="I20" t="n">
-        <v>664</v>
+        <v>606</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -1128,31 +1128,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.237</v>
+        <v>0.21</v>
       </c>
       <c r="C21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.053</v>
       </c>
       <c r="D21" t="n">
-        <v>0.134</v>
+        <v>0.125</v>
       </c>
       <c r="E21" t="n">
-        <v>0.368</v>
+        <v>0.3</v>
       </c>
       <c r="F21" t="n">
         <v>0.002</v>
       </c>
       <c r="G21" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H21" t="n">
-        <v>1081</v>
+        <v>718</v>
       </c>
       <c r="I21" t="n">
-        <v>731</v>
+        <v>547</v>
       </c>
       <c r="J21" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1168,10 +1168,10 @@
         <v>0.005</v>
       </c>
       <c r="D22" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="E22" t="n">
-        <v>0.059</v>
+        <v>0.062</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1180,13 +1180,13 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>595</v>
+        <v>400</v>
       </c>
       <c r="I22" t="n">
-        <v>694</v>
+        <v>537</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="23">
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>0.138</v>
+        <v>0.136</v>
       </c>
       <c r="D23" t="n">
-        <v>0.417</v>
+        <v>0.422</v>
       </c>
       <c r="E23" t="n">
-        <v>0.907</v>
+        <v>0.911</v>
       </c>
       <c r="F23" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="G23" t="n">
         <v>0.004</v>
       </c>
       <c r="H23" t="n">
-        <v>1791</v>
+        <v>1016</v>
       </c>
       <c r="I23" t="n">
-        <v>630</v>
+        <v>737</v>
       </c>
       <c r="J23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="24">
@@ -1230,28 +1230,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="C24" t="n">
         <v>0.019</v>
       </c>
       <c r="D24" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="E24" t="n">
-        <v>0.082</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>1846</v>
+        <v>661</v>
       </c>
       <c r="I24" t="n">
-        <v>768</v>
+        <v>352</v>
       </c>
       <c r="J24" t="n">
         <v>1.01</v>
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.037</v>
+        <v>0.039</v>
       </c>
       <c r="C25" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="E25" t="n">
         <v>0.056</v>
@@ -1282,10 +1282,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1545</v>
+        <v>1370</v>
       </c>
       <c r="I25" t="n">
-        <v>805</v>
+        <v>883</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="C26" t="n">
         <v>0.006</v>
@@ -1316,13 +1316,13 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1820</v>
+        <v>1259</v>
       </c>
       <c r="I26" t="n">
-        <v>510</v>
+        <v>731</v>
       </c>
       <c r="J26" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1332,28 +1332,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.213</v>
+        <v>3.21</v>
       </c>
       <c r="C27" t="n">
-        <v>0.652</v>
+        <v>0.627</v>
       </c>
       <c r="D27" t="n">
-        <v>2.105</v>
+        <v>2.078</v>
       </c>
       <c r="E27" t="n">
-        <v>4.448</v>
+        <v>4.398</v>
       </c>
       <c r="F27" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="G27" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="H27" t="n">
-        <v>1449</v>
+        <v>1546</v>
       </c>
       <c r="I27" t="n">
-        <v>805</v>
+        <v>690</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -1369,28 +1369,28 @@
         <v>0.077</v>
       </c>
       <c r="C28" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="D28" t="n">
-        <v>0.045</v>
+        <v>0.043</v>
       </c>
       <c r="E28" t="n">
-        <v>0.109</v>
+        <v>0.111</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>3000</v>
+        <v>1292</v>
       </c>
       <c r="I28" t="n">
-        <v>666</v>
+        <v>704</v>
       </c>
       <c r="J28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="29">
@@ -1400,31 +1400,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.225</v>
+        <v>0.215</v>
       </c>
       <c r="C29" t="n">
-        <v>0.061</v>
+        <v>0.062</v>
       </c>
       <c r="D29" t="n">
-        <v>0.125</v>
+        <v>0.104</v>
       </c>
       <c r="E29" t="n">
-        <v>0.345</v>
+        <v>0.324</v>
       </c>
       <c r="F29" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="G29" t="n">
         <v>0.002</v>
       </c>
       <c r="H29" t="n">
-        <v>1947</v>
+        <v>1071</v>
       </c>
       <c r="I29" t="n">
-        <v>893</v>
+        <v>733</v>
       </c>
       <c r="J29" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1434,28 +1434,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.067</v>
+        <v>1.056</v>
       </c>
       <c r="C30" t="n">
-        <v>0.218</v>
+        <v>0.212</v>
       </c>
       <c r="D30" t="n">
-        <v>0.655</v>
+        <v>0.7</v>
       </c>
       <c r="E30" t="n">
-        <v>1.45</v>
+        <v>1.445</v>
       </c>
       <c r="F30" t="n">
         <v>0.006</v>
       </c>
       <c r="G30" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="H30" t="n">
-        <v>1645</v>
+        <v>1118</v>
       </c>
       <c r="I30" t="n">
-        <v>661</v>
+        <v>571</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -1486,10 +1486,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1188</v>
+        <v>989</v>
       </c>
       <c r="I31" t="n">
-        <v>509</v>
+        <v>547</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -1502,31 +1502,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>30866.62</v>
+        <v>27976.857</v>
       </c>
       <c r="C32" t="n">
-        <v>307440.105</v>
+        <v>103001.69</v>
       </c>
       <c r="D32" t="n">
-        <v>498.659</v>
+        <v>611.255</v>
       </c>
       <c r="E32" t="n">
-        <v>62924.794</v>
+        <v>75672.251</v>
       </c>
       <c r="F32" t="n">
-        <v>9800.559999999999</v>
+        <v>4375.107</v>
       </c>
       <c r="G32" t="n">
-        <v>142624.822</v>
+        <v>19509.196</v>
       </c>
       <c r="H32" t="n">
-        <v>1188</v>
+        <v>989</v>
       </c>
       <c r="I32" t="n">
-        <v>509</v>
+        <v>547</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
   </sheetData>

--- a/output/diagnostics/Bayesian_parameter(results).xlsx
+++ b/output/diagnostics/Bayesian_parameter(results).xlsx
@@ -482,28 +482,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.998</v>
+        <v>0.989</v>
       </c>
       <c r="C2" t="n">
-        <v>0.208</v>
+        <v>0.212</v>
       </c>
       <c r="D2" t="n">
-        <v>0.624</v>
+        <v>0.608</v>
       </c>
       <c r="E2" t="n">
-        <v>1.404</v>
+        <v>1.367</v>
       </c>
       <c r="F2" t="n">
         <v>0.007</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="H2" t="n">
-        <v>887</v>
+        <v>965</v>
       </c>
       <c r="I2" t="n">
-        <v>722</v>
+        <v>697</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -516,28 +516,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.553</v>
       </c>
       <c r="C3" t="n">
         <v>0.177</v>
       </c>
       <c r="D3" t="n">
-        <v>0.257</v>
+        <v>0.241</v>
       </c>
       <c r="E3" t="n">
-        <v>0.874</v>
+        <v>0.867</v>
       </c>
       <c r="F3" t="n">
         <v>0.005</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="H3" t="n">
-        <v>1182</v>
+        <v>969</v>
       </c>
       <c r="I3" t="n">
-        <v>792</v>
+        <v>647</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -550,28 +550,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.586</v>
+        <v>0.597</v>
       </c>
       <c r="C4" t="n">
-        <v>0.178</v>
+        <v>0.19</v>
       </c>
       <c r="D4" t="n">
-        <v>0.271</v>
+        <v>0.298</v>
       </c>
       <c r="E4" t="n">
-        <v>0.899</v>
+        <v>0.985</v>
       </c>
       <c r="F4" t="n">
         <v>0.006</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="H4" t="n">
-        <v>886</v>
+        <v>990</v>
       </c>
       <c r="I4" t="n">
-        <v>757</v>
+        <v>670</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -584,16 +584,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.12</v>
+        <v>0.119</v>
       </c>
       <c r="C5" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="D5" t="n">
-        <v>0.095</v>
+        <v>0.094</v>
       </c>
       <c r="E5" t="n">
-        <v>0.148</v>
+        <v>0.147</v>
       </c>
       <c r="F5" t="n">
         <v>0.001</v>
@@ -602,10 +602,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>464</v>
+        <v>521</v>
       </c>
       <c r="I5" t="n">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -618,16 +618,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.036</v>
+        <v>0.037</v>
       </c>
       <c r="D6" t="n">
-        <v>0.022</v>
+        <v>0.025</v>
       </c>
       <c r="E6" t="n">
-        <v>0.15</v>
+        <v>0.153</v>
       </c>
       <c r="F6" t="n">
         <v>0.001</v>
@@ -636,10 +636,10 @@
         <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>1113</v>
+        <v>1234</v>
       </c>
       <c r="I6" t="n">
-        <v>588</v>
+        <v>711</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -652,28 +652,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="C7" t="n">
-        <v>0.494</v>
+        <v>0.513</v>
       </c>
       <c r="D7" t="n">
-        <v>0.521</v>
+        <v>0.592</v>
       </c>
       <c r="E7" t="n">
-        <v>2.24</v>
+        <v>2.401</v>
       </c>
       <c r="F7" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="G7" t="n">
         <v>0.018</v>
       </c>
       <c r="H7" t="n">
-        <v>928</v>
+        <v>984</v>
       </c>
       <c r="I7" t="n">
-        <v>622</v>
+        <v>666</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -689,13 +689,13 @@
         <v>0.042</v>
       </c>
       <c r="C8" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="D8" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="E8" t="n">
-        <v>0.058</v>
+        <v>0.059</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>989</v>
+        <v>744</v>
       </c>
       <c r="I8" t="n">
-        <v>733</v>
+        <v>523</v>
       </c>
       <c r="J8" t="n">
         <v>1.01</v>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.257</v>
+        <v>0.258</v>
       </c>
       <c r="C9" t="n">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="D9" t="n">
-        <v>0.145</v>
+        <v>0.151</v>
       </c>
       <c r="E9" t="n">
-        <v>0.367</v>
+        <v>0.354</v>
       </c>
       <c r="F9" t="n">
         <v>0.002</v>
@@ -738,13 +738,13 @@
         <v>0.002</v>
       </c>
       <c r="H9" t="n">
-        <v>792</v>
+        <v>1287</v>
       </c>
       <c r="I9" t="n">
-        <v>580</v>
+        <v>708</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -754,16 +754,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="C10" t="n">
-        <v>0.074</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.223</v>
+        <v>0.234</v>
       </c>
       <c r="E10" t="n">
-        <v>0.498</v>
+        <v>0.493</v>
       </c>
       <c r="F10" t="n">
         <v>0.002</v>
@@ -772,10 +772,10 @@
         <v>0.002</v>
       </c>
       <c r="H10" t="n">
-        <v>1154</v>
+        <v>1255</v>
       </c>
       <c r="I10" t="n">
-        <v>739</v>
+        <v>769</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -794,7 +794,7 @@
         <v>0.005</v>
       </c>
       <c r="D11" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E11" t="n">
         <v>0.027</v>
@@ -806,10 +806,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>405</v>
+        <v>614</v>
       </c>
       <c r="I11" t="n">
-        <v>508</v>
+        <v>602</v>
       </c>
       <c r="J11" t="n">
         <v>1.01</v>
@@ -822,28 +822,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.779</v>
+        <v>0.793</v>
       </c>
       <c r="C12" t="n">
-        <v>0.263</v>
+        <v>0.251</v>
       </c>
       <c r="D12" t="n">
-        <v>0.331</v>
+        <v>0.36</v>
       </c>
       <c r="E12" t="n">
-        <v>1.271</v>
+        <v>1.258</v>
       </c>
       <c r="F12" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="G12" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>973</v>
+        <v>1212</v>
       </c>
       <c r="I12" t="n">
-        <v>667</v>
+        <v>632</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -856,28 +856,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.175</v>
+        <v>0.172</v>
       </c>
       <c r="C13" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="E13" t="n">
-        <v>0.333</v>
+        <v>0.325</v>
       </c>
       <c r="F13" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="G13" t="n">
         <v>0.003</v>
       </c>
       <c r="H13" t="n">
-        <v>1115</v>
+        <v>1036</v>
       </c>
       <c r="I13" t="n">
-        <v>588</v>
+        <v>524</v>
       </c>
       <c r="J13" t="n">
         <v>1.01</v>
@@ -890,28 +890,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.495</v>
+        <v>1.519</v>
       </c>
       <c r="C14" t="n">
-        <v>0.635</v>
+        <v>0.63</v>
       </c>
       <c r="D14" t="n">
-        <v>0.508</v>
+        <v>0.519</v>
       </c>
       <c r="E14" t="n">
-        <v>2.684</v>
+        <v>2.766</v>
       </c>
       <c r="F14" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="G14" t="n">
         <v>0.02</v>
       </c>
-      <c r="G14" t="n">
-        <v>0.024</v>
-      </c>
       <c r="H14" t="n">
-        <v>930</v>
+        <v>840</v>
       </c>
       <c r="I14" t="n">
-        <v>731</v>
+        <v>668</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -924,28 +924,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.399</v>
+        <v>2.421</v>
       </c>
       <c r="C15" t="n">
-        <v>0.537</v>
+        <v>0.514</v>
       </c>
       <c r="D15" t="n">
-        <v>1.424</v>
+        <v>1.448</v>
       </c>
       <c r="E15" t="n">
-        <v>3.32</v>
+        <v>3.346</v>
       </c>
       <c r="F15" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="G15" t="n">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
       <c r="H15" t="n">
-        <v>1457</v>
+        <v>1899</v>
       </c>
       <c r="I15" t="n">
-        <v>742</v>
+        <v>555</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -958,28 +958,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.232</v>
+        <v>3.196</v>
       </c>
       <c r="C16" t="n">
-        <v>1.222</v>
+        <v>1.241</v>
       </c>
       <c r="D16" t="n">
-        <v>1.501</v>
+        <v>1.5</v>
       </c>
       <c r="E16" t="n">
-        <v>5.403</v>
+        <v>5.438</v>
       </c>
       <c r="F16" t="n">
         <v>0.045</v>
       </c>
       <c r="G16" t="n">
-        <v>0.024</v>
+        <v>0.029</v>
       </c>
       <c r="H16" t="n">
-        <v>718</v>
+        <v>755</v>
       </c>
       <c r="I16" t="n">
-        <v>659</v>
+        <v>597</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -992,16 +992,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.672</v>
+        <v>0.681</v>
       </c>
       <c r="C17" t="n">
-        <v>0.344</v>
+        <v>0.349</v>
       </c>
       <c r="D17" t="n">
-        <v>0.127</v>
+        <v>0.107</v>
       </c>
       <c r="E17" t="n">
-        <v>1.338</v>
+        <v>1.293</v>
       </c>
       <c r="F17" t="n">
         <v>0.013</v>
@@ -1010,10 +1010,10 @@
         <v>0.011</v>
       </c>
       <c r="H17" t="n">
-        <v>680</v>
+        <v>722</v>
       </c>
       <c r="I17" t="n">
-        <v>593</v>
+        <v>675</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -1026,31 +1026,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6</v>
+        <v>0.602</v>
       </c>
       <c r="C18" t="n">
-        <v>0.276</v>
+        <v>0.271</v>
       </c>
       <c r="D18" t="n">
-        <v>0.185</v>
+        <v>0.146</v>
       </c>
       <c r="E18" t="n">
-        <v>1.109</v>
+        <v>1.084</v>
       </c>
       <c r="F18" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="G18" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="G18" t="n">
-        <v>0.01</v>
-      </c>
       <c r="H18" t="n">
-        <v>957</v>
+        <v>1452</v>
       </c>
       <c r="I18" t="n">
-        <v>655</v>
+        <v>821</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="19">
@@ -1060,28 +1060,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22.681</v>
+        <v>22.624</v>
       </c>
       <c r="C19" t="n">
-        <v>1.619</v>
+        <v>1.665</v>
       </c>
       <c r="D19" t="n">
-        <v>20.013</v>
+        <v>20.014</v>
       </c>
       <c r="E19" t="n">
-        <v>25.315</v>
+        <v>25.381</v>
       </c>
       <c r="F19" t="n">
-        <v>0.045</v>
+        <v>0.051</v>
       </c>
       <c r="G19" t="n">
-        <v>0.034</v>
+        <v>0.04</v>
       </c>
       <c r="H19" t="n">
-        <v>1181</v>
+        <v>963</v>
       </c>
       <c r="I19" t="n">
-        <v>739</v>
+        <v>543</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.629</v>
+        <v>0.614</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2</v>
+        <v>0.196</v>
       </c>
       <c r="D20" t="n">
-        <v>0.31</v>
+        <v>0.297</v>
       </c>
       <c r="E20" t="n">
-        <v>1.024</v>
+        <v>0.997</v>
       </c>
       <c r="F20" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G20" t="n">
         <v>0.006</v>
       </c>
-      <c r="G20" t="n">
-        <v>0.007</v>
-      </c>
       <c r="H20" t="n">
-        <v>993</v>
+        <v>1319</v>
       </c>
       <c r="I20" t="n">
-        <v>606</v>
+        <v>763</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.21</v>
+        <v>0.214</v>
       </c>
       <c r="C21" t="n">
-        <v>0.053</v>
+        <v>0.056</v>
       </c>
       <c r="D21" t="n">
-        <v>0.125</v>
+        <v>0.12</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3</v>
+        <v>0.315</v>
       </c>
       <c r="F21" t="n">
         <v>0.002</v>
@@ -1146,10 +1146,10 @@
         <v>0.002</v>
       </c>
       <c r="H21" t="n">
-        <v>718</v>
+        <v>840</v>
       </c>
       <c r="I21" t="n">
-        <v>547</v>
+        <v>776</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -1168,10 +1168,10 @@
         <v>0.005</v>
       </c>
       <c r="D22" t="n">
-        <v>0.042</v>
+        <v>0.043</v>
       </c>
       <c r="E22" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>400</v>
+        <v>613</v>
       </c>
       <c r="I22" t="n">
-        <v>537</v>
+        <v>715</v>
       </c>
       <c r="J22" t="n">
         <v>1.01</v>
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.136</v>
+        <v>0.132</v>
       </c>
       <c r="D23" t="n">
-        <v>0.422</v>
+        <v>0.446</v>
       </c>
       <c r="E23" t="n">
-        <v>0.911</v>
+        <v>0.91</v>
       </c>
       <c r="F23" t="n">
         <v>0.004</v>
@@ -1214,13 +1214,13 @@
         <v>0.004</v>
       </c>
       <c r="H23" t="n">
-        <v>1016</v>
+        <v>1162</v>
       </c>
       <c r="I23" t="n">
-        <v>737</v>
+        <v>869</v>
       </c>
       <c r="J23" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1233,13 +1233,13 @@
         <v>0.05</v>
       </c>
       <c r="C24" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="D24" t="n">
-        <v>0.015</v>
+        <v>0.017</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F24" t="n">
         <v>0.001</v>
@@ -1248,13 +1248,13 @@
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>661</v>
+        <v>1149</v>
       </c>
       <c r="I24" t="n">
-        <v>352</v>
+        <v>476</v>
       </c>
       <c r="J24" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1270,7 +1270,7 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="E25" t="n">
         <v>0.056</v>
@@ -1282,10 +1282,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1370</v>
+        <v>1305</v>
       </c>
       <c r="I25" t="n">
-        <v>883</v>
+        <v>870</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -1316,13 +1316,13 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1259</v>
+        <v>1143</v>
       </c>
       <c r="I26" t="n">
-        <v>731</v>
+        <v>676</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="27">
@@ -1332,28 +1332,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.21</v>
+        <v>3.172</v>
       </c>
       <c r="C27" t="n">
-        <v>0.627</v>
+        <v>0.638</v>
       </c>
       <c r="D27" t="n">
-        <v>2.078</v>
+        <v>2.062</v>
       </c>
       <c r="E27" t="n">
-        <v>4.398</v>
+        <v>4.326</v>
       </c>
       <c r="F27" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="G27" t="n">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="H27" t="n">
-        <v>1546</v>
+        <v>1341</v>
       </c>
       <c r="I27" t="n">
-        <v>690</v>
+        <v>778</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -1369,13 +1369,13 @@
         <v>0.077</v>
       </c>
       <c r="C28" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="D28" t="n">
-        <v>0.043</v>
+        <v>0.045</v>
       </c>
       <c r="E28" t="n">
-        <v>0.111</v>
+        <v>0.118</v>
       </c>
       <c r="F28" t="n">
         <v>0.001</v>
@@ -1384,13 +1384,13 @@
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>1292</v>
+        <v>1472</v>
       </c>
       <c r="I28" t="n">
-        <v>704</v>
+        <v>650</v>
       </c>
       <c r="J28" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.215</v>
+        <v>0.218</v>
       </c>
       <c r="C29" t="n">
         <v>0.062</v>
       </c>
       <c r="D29" t="n">
-        <v>0.104</v>
+        <v>0.11</v>
       </c>
       <c r="E29" t="n">
-        <v>0.324</v>
+        <v>0.335</v>
       </c>
       <c r="F29" t="n">
         <v>0.002</v>
@@ -1418,10 +1418,10 @@
         <v>0.002</v>
       </c>
       <c r="H29" t="n">
-        <v>1071</v>
+        <v>1466</v>
       </c>
       <c r="I29" t="n">
-        <v>733</v>
+        <v>685</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -1434,28 +1434,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.056</v>
+        <v>1.059</v>
       </c>
       <c r="C30" t="n">
-        <v>0.212</v>
+        <v>0.218</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7</v>
+        <v>0.622</v>
       </c>
       <c r="E30" t="n">
-        <v>1.445</v>
+        <v>1.43</v>
       </c>
       <c r="F30" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="G30" t="n">
         <v>0.008</v>
       </c>
       <c r="H30" t="n">
-        <v>1118</v>
+        <v>1590</v>
       </c>
       <c r="I30" t="n">
-        <v>571</v>
+        <v>828</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -1486,10 +1486,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>989</v>
+        <v>869</v>
       </c>
       <c r="I31" t="n">
-        <v>547</v>
+        <v>475</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -1502,28 +1502,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>27976.857</v>
+        <v>41469.012</v>
       </c>
       <c r="C32" t="n">
-        <v>103001.69</v>
+        <v>210239.05</v>
       </c>
       <c r="D32" t="n">
-        <v>611.255</v>
+        <v>588.725</v>
       </c>
       <c r="E32" t="n">
-        <v>75672.251</v>
+        <v>72870.086</v>
       </c>
       <c r="F32" t="n">
-        <v>4375.107</v>
+        <v>10723.404</v>
       </c>
       <c r="G32" t="n">
-        <v>19509.196</v>
+        <v>59958.06</v>
       </c>
       <c r="H32" t="n">
-        <v>989</v>
+        <v>869</v>
       </c>
       <c r="I32" t="n">
-        <v>547</v>
+        <v>475</v>
       </c>
       <c r="J32" t="n">
         <v>1.01</v>

--- a/output/diagnostics/Bayesian_parameter(results).xlsx
+++ b/output/diagnostics/Bayesian_parameter(results).xlsx
@@ -482,28 +482,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.989</v>
+        <v>0.974</v>
       </c>
       <c r="C2" t="n">
         <v>0.212</v>
       </c>
       <c r="D2" t="n">
-        <v>0.608</v>
+        <v>0.601</v>
       </c>
       <c r="E2" t="n">
-        <v>1.367</v>
+        <v>1.372</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="G2" t="n">
         <v>0.007</v>
       </c>
       <c r="H2" t="n">
-        <v>965</v>
+        <v>1172</v>
       </c>
       <c r="I2" t="n">
-        <v>697</v>
+        <v>776</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -516,31 +516,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.553</v>
+        <v>0.494</v>
       </c>
       <c r="C3" t="n">
-        <v>0.177</v>
+        <v>0.17</v>
       </c>
       <c r="D3" t="n">
-        <v>0.241</v>
+        <v>0.194</v>
       </c>
       <c r="E3" t="n">
-        <v>0.867</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="F3" t="n">
         <v>0.005</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="H3" t="n">
-        <v>969</v>
+        <v>1157</v>
       </c>
       <c r="I3" t="n">
-        <v>647</v>
+        <v>517</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="4">
@@ -550,28 +550,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.597</v>
+        <v>0.52</v>
       </c>
       <c r="C4" t="n">
-        <v>0.19</v>
+        <v>0.171</v>
       </c>
       <c r="D4" t="n">
-        <v>0.298</v>
+        <v>0.26</v>
       </c>
       <c r="E4" t="n">
-        <v>0.985</v>
+        <v>0.849</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="H4" t="n">
-        <v>990</v>
+        <v>1258</v>
       </c>
       <c r="I4" t="n">
-        <v>670</v>
+        <v>881</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -584,16 +584,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.119</v>
+        <v>0.12</v>
       </c>
       <c r="C5" t="n">
         <v>0.015</v>
       </c>
       <c r="D5" t="n">
-        <v>0.094</v>
+        <v>0.093</v>
       </c>
       <c r="E5" t="n">
-        <v>0.147</v>
+        <v>0.149</v>
       </c>
       <c r="F5" t="n">
         <v>0.001</v>
@@ -602,10 +602,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>521</v>
+        <v>496</v>
       </c>
       <c r="I5" t="n">
-        <v>671</v>
+        <v>510</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -618,16 +618,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="C6" t="n">
         <v>0.037</v>
       </c>
       <c r="D6" t="n">
-        <v>0.025</v>
+        <v>0.029</v>
       </c>
       <c r="E6" t="n">
-        <v>0.153</v>
+        <v>0.154</v>
       </c>
       <c r="F6" t="n">
         <v>0.001</v>
@@ -636,10 +636,10 @@
         <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>1234</v>
+        <v>1253</v>
       </c>
       <c r="I6" t="n">
-        <v>711</v>
+        <v>794</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -652,28 +652,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.39</v>
+        <v>1.271</v>
       </c>
       <c r="C7" t="n">
-        <v>0.513</v>
+        <v>0.429</v>
       </c>
       <c r="D7" t="n">
-        <v>0.592</v>
+        <v>0.627</v>
       </c>
       <c r="E7" t="n">
-        <v>2.401</v>
+        <v>2.094</v>
       </c>
       <c r="F7" t="n">
-        <v>0.017</v>
+        <v>0.013</v>
       </c>
       <c r="G7" t="n">
-        <v>0.018</v>
+        <v>0.014</v>
       </c>
       <c r="H7" t="n">
-        <v>984</v>
+        <v>1150</v>
       </c>
       <c r="I7" t="n">
-        <v>666</v>
+        <v>911</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.042</v>
+        <v>0.041</v>
       </c>
       <c r="C8" t="n">
         <v>0.01</v>
       </c>
       <c r="D8" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="E8" t="n">
         <v>0.059</v>
@@ -704,13 +704,13 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>744</v>
+        <v>807</v>
       </c>
       <c r="I8" t="n">
         <v>523</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.258</v>
+        <v>0.256</v>
       </c>
       <c r="C9" t="n">
         <v>0.055</v>
       </c>
       <c r="D9" t="n">
-        <v>0.151</v>
+        <v>0.166</v>
       </c>
       <c r="E9" t="n">
-        <v>0.354</v>
+        <v>0.364</v>
       </c>
       <c r="F9" t="n">
         <v>0.002</v>
@@ -738,10 +738,10 @@
         <v>0.002</v>
       </c>
       <c r="H9" t="n">
-        <v>1287</v>
+        <v>1372</v>
       </c>
       <c r="I9" t="n">
-        <v>708</v>
+        <v>762</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -754,16 +754,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.357</v>
+        <v>0.356</v>
       </c>
       <c r="C10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.234</v>
+        <v>0.224</v>
       </c>
       <c r="E10" t="n">
-        <v>0.493</v>
+        <v>0.499</v>
       </c>
       <c r="F10" t="n">
         <v>0.002</v>
@@ -772,10 +772,10 @@
         <v>0.002</v>
       </c>
       <c r="H10" t="n">
-        <v>1255</v>
+        <v>1343</v>
       </c>
       <c r="I10" t="n">
-        <v>769</v>
+        <v>732</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -797,7 +797,7 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -806,13 +806,13 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>614</v>
+        <v>492</v>
       </c>
       <c r="I11" t="n">
-        <v>602</v>
+        <v>715</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -822,28 +822,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.793</v>
+        <v>0.744</v>
       </c>
       <c r="C12" t="n">
-        <v>0.251</v>
+        <v>0.243</v>
       </c>
       <c r="D12" t="n">
-        <v>0.36</v>
+        <v>0.334</v>
       </c>
       <c r="E12" t="n">
-        <v>1.258</v>
+        <v>1.194</v>
       </c>
       <c r="F12" t="n">
         <v>0.007</v>
       </c>
       <c r="G12" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="H12" t="n">
-        <v>1212</v>
+        <v>1040</v>
       </c>
       <c r="I12" t="n">
-        <v>632</v>
+        <v>759</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -856,16 +856,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.172</v>
+        <v>0.169</v>
       </c>
       <c r="C13" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.029</v>
+        <v>0.025</v>
       </c>
       <c r="E13" t="n">
-        <v>0.325</v>
+        <v>0.328</v>
       </c>
       <c r="F13" t="n">
         <v>0.002</v>
@@ -874,13 +874,13 @@
         <v>0.003</v>
       </c>
       <c r="H13" t="n">
-        <v>1036</v>
+        <v>1252</v>
       </c>
       <c r="I13" t="n">
-        <v>524</v>
+        <v>622</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -890,28 +890,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.519</v>
+        <v>1.511</v>
       </c>
       <c r="C14" t="n">
-        <v>0.63</v>
+        <v>0.656</v>
       </c>
       <c r="D14" t="n">
-        <v>0.519</v>
+        <v>0.477</v>
       </c>
       <c r="E14" t="n">
-        <v>2.766</v>
+        <v>2.703</v>
       </c>
       <c r="F14" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="G14" t="n">
         <v>0.02</v>
       </c>
       <c r="H14" t="n">
-        <v>840</v>
+        <v>782</v>
       </c>
       <c r="I14" t="n">
-        <v>668</v>
+        <v>836</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -924,28 +924,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.421</v>
+        <v>2.401</v>
       </c>
       <c r="C15" t="n">
-        <v>0.514</v>
+        <v>0.551</v>
       </c>
       <c r="D15" t="n">
-        <v>1.448</v>
+        <v>1.351</v>
       </c>
       <c r="E15" t="n">
-        <v>3.346</v>
+        <v>3.358</v>
       </c>
       <c r="F15" t="n">
-        <v>0.012</v>
+        <v>0.016</v>
       </c>
       <c r="G15" t="n">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="H15" t="n">
-        <v>1899</v>
+        <v>1176</v>
       </c>
       <c r="I15" t="n">
-        <v>555</v>
+        <v>715</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -958,28 +958,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.196</v>
+        <v>3.134</v>
       </c>
       <c r="C16" t="n">
-        <v>1.241</v>
+        <v>1.243</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5</v>
+        <v>1.516</v>
       </c>
       <c r="E16" t="n">
-        <v>5.438</v>
+        <v>5.505</v>
       </c>
       <c r="F16" t="n">
         <v>0.045</v>
       </c>
       <c r="G16" t="n">
-        <v>0.029</v>
+        <v>0.034</v>
       </c>
       <c r="H16" t="n">
-        <v>755</v>
+        <v>743</v>
       </c>
       <c r="I16" t="n">
-        <v>597</v>
+        <v>552</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -992,31 +992,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.681</v>
+        <v>0.603</v>
       </c>
       <c r="C17" t="n">
-        <v>0.349</v>
+        <v>0.333</v>
       </c>
       <c r="D17" t="n">
-        <v>0.107</v>
+        <v>0.058</v>
       </c>
       <c r="E17" t="n">
-        <v>1.293</v>
+        <v>1.175</v>
       </c>
       <c r="F17" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="G17" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="H17" t="n">
-        <v>722</v>
+        <v>757</v>
       </c>
       <c r="I17" t="n">
-        <v>675</v>
+        <v>602</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="18">
@@ -1026,28 +1026,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.602</v>
+        <v>0.6</v>
       </c>
       <c r="C18" t="n">
-        <v>0.271</v>
+        <v>0.289</v>
       </c>
       <c r="D18" t="n">
-        <v>0.146</v>
+        <v>0.123</v>
       </c>
       <c r="E18" t="n">
-        <v>1.084</v>
+        <v>1.113</v>
       </c>
       <c r="F18" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="G18" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="H18" t="n">
-        <v>1452</v>
+        <v>1178</v>
       </c>
       <c r="I18" t="n">
-        <v>821</v>
+        <v>672</v>
       </c>
       <c r="J18" t="n">
         <v>1.01</v>
@@ -1060,28 +1060,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22.624</v>
+        <v>22.666</v>
       </c>
       <c r="C19" t="n">
-        <v>1.665</v>
+        <v>1.699</v>
       </c>
       <c r="D19" t="n">
-        <v>20.014</v>
+        <v>20.033</v>
       </c>
       <c r="E19" t="n">
-        <v>25.381</v>
+        <v>25.451</v>
       </c>
       <c r="F19" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
       <c r="G19" t="n">
-        <v>0.04</v>
+        <v>0.038</v>
       </c>
       <c r="H19" t="n">
-        <v>963</v>
+        <v>1226</v>
       </c>
       <c r="I19" t="n">
-        <v>543</v>
+        <v>620</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.614</v>
+        <v>0.657</v>
       </c>
       <c r="C20" t="n">
-        <v>0.196</v>
+        <v>0.192</v>
       </c>
       <c r="D20" t="n">
-        <v>0.297</v>
+        <v>0.319</v>
       </c>
       <c r="E20" t="n">
-        <v>0.997</v>
+        <v>1.032</v>
       </c>
       <c r="F20" t="n">
         <v>0.005</v>
@@ -1112,10 +1112,10 @@
         <v>0.006</v>
       </c>
       <c r="H20" t="n">
-        <v>1319</v>
+        <v>1737</v>
       </c>
       <c r="I20" t="n">
-        <v>763</v>
+        <v>707</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.214</v>
+        <v>0.181</v>
       </c>
       <c r="C21" t="n">
-        <v>0.056</v>
+        <v>0.054</v>
       </c>
       <c r="D21" t="n">
-        <v>0.12</v>
+        <v>0.091</v>
       </c>
       <c r="E21" t="n">
-        <v>0.315</v>
+        <v>0.28</v>
       </c>
       <c r="F21" t="n">
         <v>0.002</v>
@@ -1146,10 +1146,10 @@
         <v>0.002</v>
       </c>
       <c r="H21" t="n">
-        <v>840</v>
+        <v>956</v>
       </c>
       <c r="I21" t="n">
-        <v>776</v>
+        <v>687</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -1168,10 +1168,10 @@
         <v>0.005</v>
       </c>
       <c r="D22" t="n">
-        <v>0.043</v>
+        <v>0.042</v>
       </c>
       <c r="E22" t="n">
-        <v>0.061</v>
+        <v>0.062</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1180,13 +1180,13 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>613</v>
+        <v>491</v>
       </c>
       <c r="I22" t="n">
-        <v>715</v>
+        <v>683</v>
       </c>
       <c r="J22" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.132</v>
+        <v>0.127</v>
       </c>
       <c r="D23" t="n">
         <v>0.446</v>
       </c>
       <c r="E23" t="n">
-        <v>0.91</v>
+        <v>0.909</v>
       </c>
       <c r="F23" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="G23" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H23" t="n">
-        <v>1162</v>
+        <v>1176</v>
       </c>
       <c r="I23" t="n">
-        <v>869</v>
+        <v>610</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -1233,13 +1233,13 @@
         <v>0.05</v>
       </c>
       <c r="C24" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="D24" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F24" t="n">
         <v>0.001</v>
@@ -1248,13 +1248,13 @@
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>1149</v>
+        <v>1263</v>
       </c>
       <c r="I24" t="n">
-        <v>476</v>
+        <v>511</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="25">
@@ -1264,16 +1264,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
       <c r="C25" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="E25" t="n">
-        <v>0.056</v>
+        <v>0.054</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1282,13 +1282,13 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1305</v>
+        <v>913</v>
       </c>
       <c r="I25" t="n">
-        <v>870</v>
+        <v>422</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="26">
@@ -1316,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1143</v>
+        <v>1523</v>
       </c>
       <c r="I26" t="n">
-        <v>676</v>
+        <v>616</v>
       </c>
       <c r="J26" t="n">
         <v>1.01</v>
@@ -1332,16 +1332,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.172</v>
+        <v>3.192</v>
       </c>
       <c r="C27" t="n">
-        <v>0.638</v>
+        <v>0.633</v>
       </c>
       <c r="D27" t="n">
-        <v>2.062</v>
+        <v>2.149</v>
       </c>
       <c r="E27" t="n">
-        <v>4.326</v>
+        <v>4.381</v>
       </c>
       <c r="F27" t="n">
         <v>0.017</v>
@@ -1350,10 +1350,10 @@
         <v>0.022</v>
       </c>
       <c r="H27" t="n">
-        <v>1341</v>
+        <v>1378</v>
       </c>
       <c r="I27" t="n">
-        <v>778</v>
+        <v>686</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -1369,25 +1369,25 @@
         <v>0.077</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="D28" t="n">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
       <c r="E28" t="n">
-        <v>0.118</v>
+        <v>0.115</v>
       </c>
       <c r="F28" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>1472</v>
+        <v>1801</v>
       </c>
       <c r="I28" t="n">
-        <v>650</v>
+        <v>791</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -1400,31 +1400,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.218</v>
+        <v>0.22</v>
       </c>
       <c r="C29" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="D29" t="n">
-        <v>0.11</v>
+        <v>0.111</v>
       </c>
       <c r="E29" t="n">
-        <v>0.335</v>
+        <v>0.331</v>
       </c>
       <c r="F29" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="G29" t="n">
         <v>0.002</v>
       </c>
       <c r="H29" t="n">
-        <v>1466</v>
+        <v>1652</v>
       </c>
       <c r="I29" t="n">
-        <v>685</v>
+        <v>723</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="30">
@@ -1434,28 +1434,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.059</v>
+        <v>1.063</v>
       </c>
       <c r="C30" t="n">
-        <v>0.218</v>
+        <v>0.219</v>
       </c>
       <c r="D30" t="n">
-        <v>0.622</v>
+        <v>0.656</v>
       </c>
       <c r="E30" t="n">
-        <v>1.43</v>
+        <v>1.442</v>
       </c>
       <c r="F30" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="G30" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="H30" t="n">
-        <v>1590</v>
+        <v>991</v>
       </c>
       <c r="I30" t="n">
-        <v>828</v>
+        <v>622</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -1486,10 +1486,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>869</v>
+        <v>1198</v>
       </c>
       <c r="I31" t="n">
-        <v>475</v>
+        <v>620</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -1502,31 +1502,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>41469.012</v>
+        <v>19494.232</v>
       </c>
       <c r="C32" t="n">
-        <v>210239.05</v>
+        <v>73120.234</v>
       </c>
       <c r="D32" t="n">
-        <v>588.725</v>
+        <v>586.919</v>
       </c>
       <c r="E32" t="n">
-        <v>72870.086</v>
+        <v>63424.866</v>
       </c>
       <c r="F32" t="n">
-        <v>10723.404</v>
+        <v>3503.085</v>
       </c>
       <c r="G32" t="n">
-        <v>59958.06</v>
+        <v>23506.159</v>
       </c>
       <c r="H32" t="n">
-        <v>869</v>
+        <v>1198</v>
       </c>
       <c r="I32" t="n">
-        <v>475</v>
+        <v>620</v>
       </c>
       <c r="J32" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/diagnostics/Bayesian_parameter(results).xlsx
+++ b/output/diagnostics/Bayesian_parameter(results).xlsx
@@ -482,28 +482,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.974</v>
+        <v>0.954</v>
       </c>
       <c r="C2" t="n">
-        <v>0.212</v>
+        <v>0.202</v>
       </c>
       <c r="D2" t="n">
-        <v>0.601</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>1.372</v>
+        <v>1.3</v>
       </c>
       <c r="F2" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.006</v>
       </c>
-      <c r="G2" t="n">
-        <v>0.007</v>
-      </c>
       <c r="H2" t="n">
-        <v>1172</v>
+        <v>894</v>
       </c>
       <c r="I2" t="n">
-        <v>776</v>
+        <v>739</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -516,31 +516,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.494</v>
+        <v>0.492</v>
       </c>
       <c r="C3" t="n">
-        <v>0.17</v>
+        <v>0.165</v>
       </c>
       <c r="D3" t="n">
-        <v>0.194</v>
+        <v>0.219</v>
       </c>
       <c r="E3" t="n">
         <v>0.8129999999999999</v>
       </c>
       <c r="F3" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.005</v>
       </c>
-      <c r="G3" t="n">
-        <v>0.007</v>
-      </c>
       <c r="H3" t="n">
-        <v>1157</v>
+        <v>1579</v>
       </c>
       <c r="I3" t="n">
-        <v>517</v>
+        <v>934</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -550,28 +550,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.52</v>
+        <v>0.509</v>
       </c>
       <c r="C4" t="n">
-        <v>0.171</v>
+        <v>0.157</v>
       </c>
       <c r="D4" t="n">
-        <v>0.26</v>
+        <v>0.276</v>
       </c>
       <c r="E4" t="n">
-        <v>0.849</v>
+        <v>0.823</v>
       </c>
       <c r="F4" t="n">
         <v>0.005</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="H4" t="n">
-        <v>1258</v>
+        <v>1156</v>
       </c>
       <c r="I4" t="n">
-        <v>881</v>
+        <v>867</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -584,16 +584,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.12</v>
+        <v>0.121</v>
       </c>
       <c r="C5" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="D5" t="n">
-        <v>0.093</v>
+        <v>0.092</v>
       </c>
       <c r="E5" t="n">
-        <v>0.149</v>
+        <v>0.146</v>
       </c>
       <c r="F5" t="n">
         <v>0.001</v>
@@ -602,13 +602,13 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>496</v>
+        <v>533</v>
       </c>
       <c r="I5" t="n">
-        <v>510</v>
+        <v>374</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="6">
@@ -618,16 +618,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.037</v>
+        <v>0.035</v>
       </c>
       <c r="D6" t="n">
-        <v>0.029</v>
+        <v>0.023</v>
       </c>
       <c r="E6" t="n">
-        <v>0.154</v>
+        <v>0.149</v>
       </c>
       <c r="F6" t="n">
         <v>0.001</v>
@@ -636,10 +636,10 @@
         <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>1253</v>
+        <v>1894</v>
       </c>
       <c r="I6" t="n">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -652,28 +652,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.271</v>
+        <v>1.29</v>
       </c>
       <c r="C7" t="n">
-        <v>0.429</v>
+        <v>0.46</v>
       </c>
       <c r="D7" t="n">
-        <v>0.627</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>2.094</v>
+        <v>2.228</v>
       </c>
       <c r="F7" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="G7" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="H7" t="n">
-        <v>1150</v>
+        <v>1767</v>
       </c>
       <c r="I7" t="n">
-        <v>911</v>
+        <v>830</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -692,10 +692,10 @@
         <v>0.01</v>
       </c>
       <c r="D8" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="E8" t="n">
-        <v>0.059</v>
+        <v>0.058</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>807</v>
+        <v>1177</v>
       </c>
       <c r="I8" t="n">
-        <v>523</v>
+        <v>705</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -723,25 +723,25 @@
         <v>0.256</v>
       </c>
       <c r="C9" t="n">
-        <v>0.055</v>
+        <v>0.062</v>
       </c>
       <c r="D9" t="n">
-        <v>0.166</v>
+        <v>0.146</v>
       </c>
       <c r="E9" t="n">
-        <v>0.364</v>
+        <v>0.368</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="G9" t="n">
         <v>0.002</v>
       </c>
       <c r="H9" t="n">
-        <v>1372</v>
+        <v>2441</v>
       </c>
       <c r="I9" t="n">
-        <v>762</v>
+        <v>699</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -754,16 +754,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.356</v>
+        <v>0.352</v>
       </c>
       <c r="C10" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.076</v>
       </c>
       <c r="D10" t="n">
-        <v>0.224</v>
+        <v>0.208</v>
       </c>
       <c r="E10" t="n">
-        <v>0.499</v>
+        <v>0.483</v>
       </c>
       <c r="F10" t="n">
         <v>0.002</v>
@@ -772,10 +772,10 @@
         <v>0.002</v>
       </c>
       <c r="H10" t="n">
-        <v>1343</v>
+        <v>2010</v>
       </c>
       <c r="I10" t="n">
-        <v>732</v>
+        <v>812</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -794,10 +794,10 @@
         <v>0.005</v>
       </c>
       <c r="D11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="E11" t="n">
-        <v>0.028</v>
+        <v>0.026</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -806,13 +806,13 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>492</v>
+        <v>593</v>
       </c>
       <c r="I11" t="n">
-        <v>715</v>
+        <v>684</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="12">
@@ -822,31 +822,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.744</v>
+        <v>0.765</v>
       </c>
       <c r="C12" t="n">
-        <v>0.243</v>
+        <v>0.245</v>
       </c>
       <c r="D12" t="n">
         <v>0.334</v>
       </c>
       <c r="E12" t="n">
-        <v>1.194</v>
+        <v>1.189</v>
       </c>
       <c r="F12" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="G12" t="n">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="H12" t="n">
-        <v>1040</v>
+        <v>2179</v>
       </c>
       <c r="I12" t="n">
-        <v>759</v>
+        <v>595</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="13">
@@ -856,16 +856,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.169</v>
+        <v>0.175</v>
       </c>
       <c r="C13" t="n">
         <v>0.08799999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="E13" t="n">
-        <v>0.328</v>
+        <v>0.335</v>
       </c>
       <c r="F13" t="n">
         <v>0.002</v>
@@ -874,10 +874,10 @@
         <v>0.003</v>
       </c>
       <c r="H13" t="n">
-        <v>1252</v>
+        <v>2078</v>
       </c>
       <c r="I13" t="n">
-        <v>622</v>
+        <v>649</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -890,28 +890,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.511</v>
+        <v>1.459</v>
       </c>
       <c r="C14" t="n">
-        <v>0.656</v>
+        <v>0.607</v>
       </c>
       <c r="D14" t="n">
-        <v>0.477</v>
+        <v>0.504</v>
       </c>
       <c r="E14" t="n">
-        <v>2.703</v>
+        <v>2.582</v>
       </c>
       <c r="F14" t="n">
-        <v>0.023</v>
+        <v>0.018</v>
       </c>
       <c r="G14" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="H14" t="n">
-        <v>782</v>
+        <v>1114</v>
       </c>
       <c r="I14" t="n">
-        <v>836</v>
+        <v>793</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -924,31 +924,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.401</v>
+        <v>2.432</v>
       </c>
       <c r="C15" t="n">
-        <v>0.551</v>
+        <v>0.527</v>
       </c>
       <c r="D15" t="n">
-        <v>1.351</v>
+        <v>1.517</v>
       </c>
       <c r="E15" t="n">
-        <v>3.358</v>
+        <v>3.408</v>
       </c>
       <c r="F15" t="n">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="G15" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="H15" t="n">
-        <v>1176</v>
+        <v>1660</v>
       </c>
       <c r="I15" t="n">
-        <v>715</v>
+        <v>700</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="16">
@@ -958,28 +958,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.134</v>
+        <v>3.254</v>
       </c>
       <c r="C16" t="n">
-        <v>1.243</v>
+        <v>1.249</v>
       </c>
       <c r="D16" t="n">
-        <v>1.516</v>
+        <v>1.503</v>
       </c>
       <c r="E16" t="n">
-        <v>5.505</v>
+        <v>5.432</v>
       </c>
       <c r="F16" t="n">
-        <v>0.045</v>
+        <v>0.039</v>
       </c>
       <c r="G16" t="n">
-        <v>0.034</v>
+        <v>0.028</v>
       </c>
       <c r="H16" t="n">
-        <v>743</v>
+        <v>837</v>
       </c>
       <c r="I16" t="n">
-        <v>552</v>
+        <v>483</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -992,31 +992,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.603</v>
+        <v>0.584</v>
       </c>
       <c r="C17" t="n">
-        <v>0.333</v>
+        <v>0.312</v>
       </c>
       <c r="D17" t="n">
-        <v>0.058</v>
+        <v>0.113</v>
       </c>
       <c r="E17" t="n">
-        <v>1.175</v>
+        <v>1.195</v>
       </c>
       <c r="F17" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="G17" t="n">
         <v>0.012</v>
       </c>
       <c r="H17" t="n">
-        <v>757</v>
+        <v>823</v>
       </c>
       <c r="I17" t="n">
-        <v>602</v>
+        <v>690</v>
       </c>
       <c r="J17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1026,31 +1026,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6</v>
+        <v>0.578</v>
       </c>
       <c r="C18" t="n">
-        <v>0.289</v>
+        <v>0.272</v>
       </c>
       <c r="D18" t="n">
-        <v>0.123</v>
+        <v>0.116</v>
       </c>
       <c r="E18" t="n">
-        <v>1.113</v>
+        <v>1.076</v>
       </c>
       <c r="F18" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="G18" t="n">
-        <v>0.012</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>1178</v>
+        <v>1149</v>
       </c>
       <c r="I18" t="n">
-        <v>672</v>
+        <v>590</v>
       </c>
       <c r="J18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1060,28 +1060,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22.666</v>
+        <v>22.612</v>
       </c>
       <c r="C19" t="n">
-        <v>1.699</v>
+        <v>1.739</v>
       </c>
       <c r="D19" t="n">
-        <v>20.033</v>
+        <v>20.007</v>
       </c>
       <c r="E19" t="n">
-        <v>25.451</v>
+        <v>25.552</v>
       </c>
       <c r="F19" t="n">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="G19" t="n">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
       <c r="H19" t="n">
-        <v>1226</v>
+        <v>1323</v>
       </c>
       <c r="I19" t="n">
-        <v>620</v>
+        <v>708</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.657</v>
+        <v>0.668</v>
       </c>
       <c r="C20" t="n">
-        <v>0.192</v>
+        <v>0.204</v>
       </c>
       <c r="D20" t="n">
-        <v>0.319</v>
+        <v>0.336</v>
       </c>
       <c r="E20" t="n">
-        <v>1.032</v>
+        <v>1.095</v>
       </c>
       <c r="F20" t="n">
         <v>0.005</v>
       </c>
       <c r="G20" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="H20" t="n">
-        <v>1737</v>
+        <v>1692</v>
       </c>
       <c r="I20" t="n">
-        <v>707</v>
+        <v>655</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.181</v>
+        <v>0.187</v>
       </c>
       <c r="C21" t="n">
-        <v>0.054</v>
+        <v>0.056</v>
       </c>
       <c r="D21" t="n">
-        <v>0.091</v>
+        <v>0.095</v>
       </c>
       <c r="E21" t="n">
-        <v>0.28</v>
+        <v>0.291</v>
       </c>
       <c r="F21" t="n">
         <v>0.002</v>
@@ -1146,10 +1146,10 @@
         <v>0.002</v>
       </c>
       <c r="H21" t="n">
-        <v>956</v>
+        <v>859</v>
       </c>
       <c r="I21" t="n">
-        <v>687</v>
+        <v>726</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -1171,7 +1171,7 @@
         <v>0.042</v>
       </c>
       <c r="E22" t="n">
-        <v>0.062</v>
+        <v>0.06</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1180,13 +1180,13 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>491</v>
+        <v>593</v>
       </c>
       <c r="I22" t="n">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="23">
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>0.127</v>
+        <v>0.13</v>
       </c>
       <c r="D23" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="E23" t="n">
-        <v>0.909</v>
+        <v>0.915</v>
       </c>
       <c r="F23" t="n">
         <v>0.003</v>
       </c>
       <c r="G23" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H23" t="n">
-        <v>1176</v>
+        <v>2086</v>
       </c>
       <c r="I23" t="n">
-        <v>610</v>
+        <v>639</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="24">
@@ -1239,7 +1239,7 @@
         <v>0.016</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F24" t="n">
         <v>0.001</v>
@@ -1248,13 +1248,13 @@
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>1263</v>
+        <v>1024</v>
       </c>
       <c r="I24" t="n">
-        <v>511</v>
+        <v>407</v>
       </c>
       <c r="J24" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.037</v>
+        <v>0.038</v>
       </c>
       <c r="C25" t="n">
         <v>0.008999999999999999</v>
@@ -1273,7 +1273,7 @@
         <v>0.022</v>
       </c>
       <c r="E25" t="n">
-        <v>0.054</v>
+        <v>0.055</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1282,10 +1282,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>913</v>
+        <v>1504</v>
       </c>
       <c r="I25" t="n">
-        <v>422</v>
+        <v>670</v>
       </c>
       <c r="J25" t="n">
         <v>1.01</v>
@@ -1301,13 +1301,13 @@
         <v>0.023</v>
       </c>
       <c r="C26" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="D26" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="E26" t="n">
-        <v>0.033</v>
+        <v>0.032</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1316,13 +1316,13 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1523</v>
+        <v>2076</v>
       </c>
       <c r="I26" t="n">
-        <v>616</v>
+        <v>561</v>
       </c>
       <c r="J26" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1332,28 +1332,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.192</v>
+        <v>3.214</v>
       </c>
       <c r="C27" t="n">
-        <v>0.633</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>2.149</v>
+        <v>2.106</v>
       </c>
       <c r="E27" t="n">
-        <v>4.381</v>
+        <v>4.515</v>
       </c>
       <c r="F27" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="G27" t="n">
-        <v>0.022</v>
+        <v>0.03</v>
       </c>
       <c r="H27" t="n">
-        <v>1378</v>
+        <v>2009</v>
       </c>
       <c r="I27" t="n">
-        <v>686</v>
+        <v>644</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -1366,31 +1366,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.077</v>
+        <v>0.076</v>
       </c>
       <c r="C28" t="n">
         <v>0.019</v>
       </c>
       <c r="D28" t="n">
-        <v>0.046</v>
+        <v>0.041</v>
       </c>
       <c r="E28" t="n">
-        <v>0.115</v>
+        <v>0.111</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>1801</v>
+        <v>1143</v>
       </c>
       <c r="I28" t="n">
-        <v>791</v>
+        <v>684</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="29">
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.22</v>
+        <v>0.219</v>
       </c>
       <c r="C29" t="n">
-        <v>0.061</v>
+        <v>0.059</v>
       </c>
       <c r="D29" t="n">
-        <v>0.111</v>
+        <v>0.119</v>
       </c>
       <c r="E29" t="n">
-        <v>0.331</v>
+        <v>0.332</v>
       </c>
       <c r="F29" t="n">
         <v>0.001</v>
@@ -1418,13 +1418,13 @@
         <v>0.002</v>
       </c>
       <c r="H29" t="n">
-        <v>1652</v>
+        <v>1544</v>
       </c>
       <c r="I29" t="n">
-        <v>723</v>
+        <v>866</v>
       </c>
       <c r="J29" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1434,28 +1434,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.063</v>
+        <v>1.069</v>
       </c>
       <c r="C30" t="n">
-        <v>0.219</v>
+        <v>0.221</v>
       </c>
       <c r="D30" t="n">
-        <v>0.656</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>1.442</v>
+        <v>1.46</v>
       </c>
       <c r="F30" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="G30" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="H30" t="n">
-        <v>991</v>
+        <v>1577</v>
       </c>
       <c r="I30" t="n">
-        <v>622</v>
+        <v>763</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -1486,10 +1486,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1198</v>
+        <v>1121</v>
       </c>
       <c r="I31" t="n">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -1502,31 +1502,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>19494.232</v>
+        <v>88205.322</v>
       </c>
       <c r="C32" t="n">
-        <v>73120.234</v>
+        <v>1092784.952</v>
       </c>
       <c r="D32" t="n">
-        <v>586.919</v>
+        <v>490.831</v>
       </c>
       <c r="E32" t="n">
-        <v>63424.866</v>
+        <v>69276.523</v>
       </c>
       <c r="F32" t="n">
-        <v>3503.085</v>
+        <v>42791.553</v>
       </c>
       <c r="G32" t="n">
-        <v>23506.159</v>
+        <v>407141.975</v>
       </c>
       <c r="H32" t="n">
-        <v>1198</v>
+        <v>1121</v>
       </c>
       <c r="I32" t="n">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
   </sheetData>

--- a/output/diagnostics/Bayesian_parameter(results).xlsx
+++ b/output/diagnostics/Bayesian_parameter(results).xlsx
@@ -482,28 +482,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.954</v>
+        <v>0.975</v>
       </c>
       <c r="C2" t="n">
-        <v>0.202</v>
+        <v>0.207</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.593</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3</v>
+        <v>1.327</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="G2" t="n">
         <v>0.006</v>
       </c>
       <c r="H2" t="n">
-        <v>894</v>
+        <v>1033</v>
       </c>
       <c r="I2" t="n">
-        <v>739</v>
+        <v>915</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -516,16 +516,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.492</v>
+        <v>0.486</v>
       </c>
       <c r="C3" t="n">
-        <v>0.165</v>
+        <v>0.163</v>
       </c>
       <c r="D3" t="n">
-        <v>0.219</v>
+        <v>0.2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.785</v>
       </c>
       <c r="F3" t="n">
         <v>0.004</v>
@@ -534,10 +534,10 @@
         <v>0.005</v>
       </c>
       <c r="H3" t="n">
-        <v>1579</v>
+        <v>1383</v>
       </c>
       <c r="I3" t="n">
-        <v>934</v>
+        <v>768</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -553,13 +553,13 @@
         <v>0.509</v>
       </c>
       <c r="C4" t="n">
-        <v>0.157</v>
+        <v>0.16</v>
       </c>
       <c r="D4" t="n">
-        <v>0.276</v>
+        <v>0.239</v>
       </c>
       <c r="E4" t="n">
-        <v>0.823</v>
+        <v>0.792</v>
       </c>
       <c r="F4" t="n">
         <v>0.005</v>
@@ -568,10 +568,10 @@
         <v>0.006</v>
       </c>
       <c r="H4" t="n">
-        <v>1156</v>
+        <v>913</v>
       </c>
       <c r="I4" t="n">
-        <v>867</v>
+        <v>822</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -602,10 +602,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="I5" t="n">
-        <v>374</v>
+        <v>583</v>
       </c>
       <c r="J5" t="n">
         <v>1.01</v>
@@ -621,13 +621,13 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.035</v>
+        <v>0.037</v>
       </c>
       <c r="D6" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="E6" t="n">
-        <v>0.149</v>
+        <v>0.151</v>
       </c>
       <c r="F6" t="n">
         <v>0.001</v>
@@ -636,13 +636,13 @@
         <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>1894</v>
+        <v>1329</v>
       </c>
       <c r="I6" t="n">
-        <v>797</v>
+        <v>777</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="7">
@@ -652,28 +652,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.29</v>
+        <v>1.271</v>
       </c>
       <c r="C7" t="n">
-        <v>0.46</v>
+        <v>0.448</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.581</v>
       </c>
       <c r="E7" t="n">
-        <v>2.228</v>
+        <v>2.135</v>
       </c>
       <c r="F7" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="G7" t="n">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="H7" t="n">
-        <v>1767</v>
+        <v>1193</v>
       </c>
       <c r="I7" t="n">
-        <v>830</v>
+        <v>915</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -695,7 +695,7 @@
         <v>0.024</v>
       </c>
       <c r="E8" t="n">
-        <v>0.058</v>
+        <v>0.059</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -704,13 +704,13 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1177</v>
+        <v>1132</v>
       </c>
       <c r="I8" t="n">
-        <v>705</v>
+        <v>782</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="9">
@@ -723,10 +723,10 @@
         <v>0.256</v>
       </c>
       <c r="C9" t="n">
-        <v>0.062</v>
+        <v>0.056</v>
       </c>
       <c r="D9" t="n">
-        <v>0.146</v>
+        <v>0.161</v>
       </c>
       <c r="E9" t="n">
         <v>0.368</v>
@@ -738,13 +738,13 @@
         <v>0.002</v>
       </c>
       <c r="H9" t="n">
-        <v>2441</v>
+        <v>1509</v>
       </c>
       <c r="I9" t="n">
-        <v>699</v>
+        <v>646</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="10">
@@ -754,16 +754,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="C10" t="n">
-        <v>0.076</v>
+        <v>0.074</v>
       </c>
       <c r="D10" t="n">
-        <v>0.208</v>
+        <v>0.218</v>
       </c>
       <c r="E10" t="n">
-        <v>0.483</v>
+        <v>0.487</v>
       </c>
       <c r="F10" t="n">
         <v>0.002</v>
@@ -772,10 +772,10 @@
         <v>0.002</v>
       </c>
       <c r="H10" t="n">
-        <v>2010</v>
+        <v>1755</v>
       </c>
       <c r="I10" t="n">
-        <v>812</v>
+        <v>784</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -797,7 +797,7 @@
         <v>0.008</v>
       </c>
       <c r="E11" t="n">
-        <v>0.026</v>
+        <v>0.025</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -806,10 +806,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>593</v>
+        <v>495</v>
       </c>
       <c r="I11" t="n">
-        <v>684</v>
+        <v>671</v>
       </c>
       <c r="J11" t="n">
         <v>1.01</v>
@@ -822,31 +822,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.765</v>
+        <v>0.759</v>
       </c>
       <c r="C12" t="n">
-        <v>0.245</v>
+        <v>0.258</v>
       </c>
       <c r="D12" t="n">
-        <v>0.334</v>
+        <v>0.322</v>
       </c>
       <c r="E12" t="n">
-        <v>1.189</v>
+        <v>1.238</v>
       </c>
       <c r="F12" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="G12" t="n">
         <v>0.01</v>
       </c>
       <c r="H12" t="n">
-        <v>2179</v>
+        <v>1752</v>
       </c>
       <c r="I12" t="n">
-        <v>595</v>
+        <v>714</v>
       </c>
       <c r="J12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -859,13 +859,13 @@
         <v>0.175</v>
       </c>
       <c r="C13" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="D13" t="n">
-        <v>0.024</v>
+        <v>0.035</v>
       </c>
       <c r="E13" t="n">
-        <v>0.335</v>
+        <v>0.354</v>
       </c>
       <c r="F13" t="n">
         <v>0.002</v>
@@ -874,10 +874,10 @@
         <v>0.003</v>
       </c>
       <c r="H13" t="n">
-        <v>2078</v>
+        <v>1941</v>
       </c>
       <c r="I13" t="n">
-        <v>649</v>
+        <v>753</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -890,28 +890,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.459</v>
+        <v>1.525</v>
       </c>
       <c r="C14" t="n">
-        <v>0.607</v>
+        <v>0.628</v>
       </c>
       <c r="D14" t="n">
-        <v>0.504</v>
+        <v>0.36</v>
       </c>
       <c r="E14" t="n">
-        <v>2.582</v>
+        <v>2.626</v>
       </c>
       <c r="F14" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="G14" t="n">
         <v>0.021</v>
       </c>
       <c r="H14" t="n">
-        <v>1114</v>
+        <v>1420</v>
       </c>
       <c r="I14" t="n">
-        <v>793</v>
+        <v>809</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -924,28 +924,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.432</v>
+        <v>2.435</v>
       </c>
       <c r="C15" t="n">
-        <v>0.527</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>1.517</v>
+        <v>1.372</v>
       </c>
       <c r="E15" t="n">
-        <v>3.408</v>
+        <v>3.39</v>
       </c>
       <c r="F15" t="n">
-        <v>0.012</v>
+        <v>0.014</v>
       </c>
       <c r="G15" t="n">
-        <v>0.017</v>
+        <v>0.022</v>
       </c>
       <c r="H15" t="n">
-        <v>1660</v>
+        <v>1578</v>
       </c>
       <c r="I15" t="n">
-        <v>700</v>
+        <v>428</v>
       </c>
       <c r="J15" t="n">
         <v>1.01</v>
@@ -958,28 +958,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.254</v>
+        <v>3.18</v>
       </c>
       <c r="C16" t="n">
-        <v>1.249</v>
+        <v>1.159</v>
       </c>
       <c r="D16" t="n">
-        <v>1.503</v>
+        <v>1.5</v>
       </c>
       <c r="E16" t="n">
-        <v>5.432</v>
+        <v>5.267</v>
       </c>
       <c r="F16" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="G16" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="H16" t="n">
-        <v>837</v>
+        <v>1532</v>
       </c>
       <c r="I16" t="n">
-        <v>483</v>
+        <v>553</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -992,28 +992,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.584</v>
+        <v>0.578</v>
       </c>
       <c r="C17" t="n">
-        <v>0.312</v>
+        <v>0.314</v>
       </c>
       <c r="D17" t="n">
-        <v>0.113</v>
+        <v>0.076</v>
       </c>
       <c r="E17" t="n">
-        <v>1.195</v>
+        <v>1.135</v>
       </c>
       <c r="F17" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="G17" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="H17" t="n">
-        <v>823</v>
+        <v>653</v>
       </c>
       <c r="I17" t="n">
-        <v>690</v>
+        <v>709</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -1026,28 +1026,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.578</v>
+        <v>0.587</v>
       </c>
       <c r="C18" t="n">
-        <v>0.272</v>
+        <v>0.273</v>
       </c>
       <c r="D18" t="n">
-        <v>0.116</v>
+        <v>0.16</v>
       </c>
       <c r="E18" t="n">
-        <v>1.076</v>
+        <v>1.13</v>
       </c>
       <c r="F18" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="G18" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>1149</v>
+        <v>1154</v>
       </c>
       <c r="I18" t="n">
-        <v>590</v>
+        <v>752</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -1060,16 +1060,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22.612</v>
+        <v>22.745</v>
       </c>
       <c r="C19" t="n">
-        <v>1.739</v>
+        <v>1.745</v>
       </c>
       <c r="D19" t="n">
-        <v>20.007</v>
+        <v>20.022</v>
       </c>
       <c r="E19" t="n">
-        <v>25.552</v>
+        <v>25.623</v>
       </c>
       <c r="F19" t="n">
         <v>0.045</v>
@@ -1078,10 +1078,10 @@
         <v>0.036</v>
       </c>
       <c r="H19" t="n">
-        <v>1323</v>
+        <v>1282</v>
       </c>
       <c r="I19" t="n">
-        <v>708</v>
+        <v>599</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.668</v>
+        <v>0.66</v>
       </c>
       <c r="C20" t="n">
-        <v>0.204</v>
+        <v>0.201</v>
       </c>
       <c r="D20" t="n">
-        <v>0.336</v>
+        <v>0.272</v>
       </c>
       <c r="E20" t="n">
-        <v>1.095</v>
+        <v>0.984</v>
       </c>
       <c r="F20" t="n">
         <v>0.005</v>
@@ -1112,13 +1112,13 @@
         <v>0.008</v>
       </c>
       <c r="H20" t="n">
-        <v>1692</v>
+        <v>1608</v>
       </c>
       <c r="I20" t="n">
-        <v>655</v>
+        <v>473</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="21">
@@ -1128,28 +1128,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.187</v>
+        <v>0.186</v>
       </c>
       <c r="C21" t="n">
-        <v>0.056</v>
+        <v>0.058</v>
       </c>
       <c r="D21" t="n">
-        <v>0.095</v>
+        <v>0.1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.291</v>
+        <v>0.284</v>
       </c>
       <c r="F21" t="n">
         <v>0.002</v>
       </c>
       <c r="G21" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H21" t="n">
-        <v>859</v>
+        <v>766</v>
       </c>
       <c r="I21" t="n">
-        <v>726</v>
+        <v>749</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>593</v>
+        <v>511</v>
       </c>
       <c r="I22" t="n">
-        <v>671</v>
+        <v>730</v>
       </c>
       <c r="J22" t="n">
         <v>1.01</v>
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.13</v>
+        <v>0.133</v>
       </c>
       <c r="D23" t="n">
-        <v>0.447</v>
+        <v>0.457</v>
       </c>
       <c r="E23" t="n">
-        <v>0.915</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="F23" t="n">
         <v>0.003</v>
@@ -1214,13 +1214,13 @@
         <v>0.004</v>
       </c>
       <c r="H23" t="n">
-        <v>2086</v>
+        <v>1541</v>
       </c>
       <c r="I23" t="n">
-        <v>639</v>
+        <v>621</v>
       </c>
       <c r="J23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="24">
@@ -1239,22 +1239,22 @@
         <v>0.016</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>1024</v>
+        <v>1674</v>
       </c>
       <c r="I24" t="n">
-        <v>407</v>
+        <v>603</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="25">
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
       <c r="C25" t="n">
         <v>0.008999999999999999</v>
@@ -1273,7 +1273,7 @@
         <v>0.022</v>
       </c>
       <c r="E25" t="n">
-        <v>0.055</v>
+        <v>0.053</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1282,10 +1282,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1504</v>
+        <v>1774</v>
       </c>
       <c r="I25" t="n">
-        <v>670</v>
+        <v>818</v>
       </c>
       <c r="J25" t="n">
         <v>1.01</v>
@@ -1301,13 +1301,13 @@
         <v>0.023</v>
       </c>
       <c r="C26" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="D26" t="n">
         <v>0.013</v>
       </c>
       <c r="E26" t="n">
-        <v>0.032</v>
+        <v>0.034</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1316,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2076</v>
+        <v>1947</v>
       </c>
       <c r="I26" t="n">
-        <v>561</v>
+        <v>824</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -1332,28 +1332,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.214</v>
+        <v>3.158</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.629</v>
       </c>
       <c r="D27" t="n">
-        <v>2.106</v>
+        <v>2.035</v>
       </c>
       <c r="E27" t="n">
-        <v>4.515</v>
+        <v>4.31</v>
       </c>
       <c r="F27" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="G27" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="H27" t="n">
-        <v>2009</v>
+        <v>1316</v>
       </c>
       <c r="I27" t="n">
-        <v>644</v>
+        <v>757</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -1366,31 +1366,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.076</v>
+        <v>0.077</v>
       </c>
       <c r="C28" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="D28" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="E28" t="n">
-        <v>0.111</v>
+        <v>0.115</v>
       </c>
       <c r="F28" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>1143</v>
+        <v>2528</v>
       </c>
       <c r="I28" t="n">
-        <v>684</v>
+        <v>898</v>
       </c>
       <c r="J28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="29">
@@ -1400,28 +1400,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.219</v>
+        <v>0.222</v>
       </c>
       <c r="C29" t="n">
-        <v>0.059</v>
+        <v>0.062</v>
       </c>
       <c r="D29" t="n">
-        <v>0.119</v>
+        <v>0.108</v>
       </c>
       <c r="E29" t="n">
-        <v>0.332</v>
+        <v>0.334</v>
       </c>
       <c r="F29" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="G29" t="n">
         <v>0.002</v>
       </c>
       <c r="H29" t="n">
-        <v>1544</v>
+        <v>1356</v>
       </c>
       <c r="I29" t="n">
-        <v>866</v>
+        <v>632</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -1434,28 +1434,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.069</v>
+        <v>1.07</v>
       </c>
       <c r="C30" t="n">
         <v>0.221</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.707</v>
       </c>
       <c r="E30" t="n">
-        <v>1.46</v>
+        <v>1.499</v>
       </c>
       <c r="F30" t="n">
         <v>0.006</v>
       </c>
       <c r="G30" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>1577</v>
+        <v>1511</v>
       </c>
       <c r="I30" t="n">
-        <v>763</v>
+        <v>587</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -1486,13 +1486,13 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1121</v>
+        <v>1319</v>
       </c>
       <c r="I31" t="n">
-        <v>619</v>
+        <v>486</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="32">
@@ -1502,31 +1502,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>88205.322</v>
+        <v>20939.622</v>
       </c>
       <c r="C32" t="n">
-        <v>1092784.952</v>
+        <v>80446.257</v>
       </c>
       <c r="D32" t="n">
-        <v>490.831</v>
+        <v>562.1799999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>69276.523</v>
+        <v>66283.069</v>
       </c>
       <c r="F32" t="n">
-        <v>42791.553</v>
+        <v>2836.893</v>
       </c>
       <c r="G32" t="n">
-        <v>407141.975</v>
+        <v>23284.58</v>
       </c>
       <c r="H32" t="n">
-        <v>1121</v>
+        <v>1319</v>
       </c>
       <c r="I32" t="n">
-        <v>619</v>
+        <v>486</v>
       </c>
       <c r="J32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
     </row>
   </sheetData>

--- a/output/diagnostics/Bayesian_parameter(results).xlsx
+++ b/output/diagnostics/Bayesian_parameter(results).xlsx
@@ -482,31 +482,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.975</v>
+        <v>0.878</v>
       </c>
       <c r="C2" t="n">
-        <v>0.207</v>
+        <v>0.18</v>
       </c>
       <c r="D2" t="n">
-        <v>0.593</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>1.327</v>
+        <v>1.206</v>
       </c>
       <c r="F2" t="n">
         <v>0.006</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="H2" t="n">
-        <v>1033</v>
+        <v>880</v>
       </c>
       <c r="I2" t="n">
-        <v>915</v>
+        <v>783</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="3">
@@ -516,16 +516,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.486</v>
+        <v>0.489</v>
       </c>
       <c r="C3" t="n">
-        <v>0.163</v>
+        <v>0.172</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2</v>
+        <v>0.208</v>
       </c>
       <c r="E3" t="n">
-        <v>0.785</v>
+        <v>0.831</v>
       </c>
       <c r="F3" t="n">
         <v>0.004</v>
@@ -534,10 +534,10 @@
         <v>0.005</v>
       </c>
       <c r="H3" t="n">
-        <v>1383</v>
+        <v>1400</v>
       </c>
       <c r="I3" t="n">
-        <v>768</v>
+        <v>629</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -550,28 +550,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.509</v>
+        <v>0.492</v>
       </c>
       <c r="C4" t="n">
-        <v>0.16</v>
+        <v>0.151</v>
       </c>
       <c r="D4" t="n">
-        <v>0.239</v>
+        <v>0.246</v>
       </c>
       <c r="E4" t="n">
-        <v>0.792</v>
+        <v>0.772</v>
       </c>
       <c r="F4" t="n">
         <v>0.005</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="H4" t="n">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="I4" t="n">
-        <v>822</v>
+        <v>635</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -590,7 +590,7 @@
         <v>0.014</v>
       </c>
       <c r="D5" t="n">
-        <v>0.092</v>
+        <v>0.094</v>
       </c>
       <c r="E5" t="n">
         <v>0.146</v>
@@ -602,10 +602,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>540</v>
+        <v>503</v>
       </c>
       <c r="I5" t="n">
-        <v>583</v>
+        <v>699</v>
       </c>
       <c r="J5" t="n">
         <v>1.01</v>
@@ -618,13 +618,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.037</v>
+        <v>0.036</v>
       </c>
       <c r="D6" t="n">
-        <v>0.022</v>
+        <v>0.03</v>
       </c>
       <c r="E6" t="n">
         <v>0.151</v>
@@ -636,13 +636,13 @@
         <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>1329</v>
+        <v>1463</v>
       </c>
       <c r="I6" t="n">
-        <v>777</v>
+        <v>821</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -652,28 +652,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.271</v>
+        <v>1.12</v>
       </c>
       <c r="C7" t="n">
-        <v>0.448</v>
+        <v>0.401</v>
       </c>
       <c r="D7" t="n">
-        <v>0.581</v>
+        <v>0.445</v>
       </c>
       <c r="E7" t="n">
-        <v>2.135</v>
+        <v>1.804</v>
       </c>
       <c r="F7" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="G7" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="H7" t="n">
-        <v>1193</v>
+        <v>1247</v>
       </c>
       <c r="I7" t="n">
-        <v>915</v>
+        <v>850</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.041</v>
+        <v>0.04</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="E8" t="n">
-        <v>0.059</v>
+        <v>0.058</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -704,13 +704,13 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1132</v>
+        <v>1006</v>
       </c>
       <c r="I8" t="n">
-        <v>782</v>
+        <v>876</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.256</v>
+        <v>0.253</v>
       </c>
       <c r="C9" t="n">
-        <v>0.056</v>
+        <v>0.055</v>
       </c>
       <c r="D9" t="n">
-        <v>0.161</v>
+        <v>0.151</v>
       </c>
       <c r="E9" t="n">
-        <v>0.368</v>
+        <v>0.354</v>
       </c>
       <c r="F9" t="n">
         <v>0.001</v>
@@ -738,13 +738,13 @@
         <v>0.002</v>
       </c>
       <c r="H9" t="n">
-        <v>1509</v>
+        <v>1379</v>
       </c>
       <c r="I9" t="n">
-        <v>646</v>
+        <v>788</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -760,22 +760,22 @@
         <v>0.074</v>
       </c>
       <c r="D10" t="n">
-        <v>0.218</v>
+        <v>0.227</v>
       </c>
       <c r="E10" t="n">
-        <v>0.487</v>
+        <v>0.507</v>
       </c>
       <c r="F10" t="n">
         <v>0.002</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H10" t="n">
-        <v>1755</v>
+        <v>1600</v>
       </c>
       <c r="I10" t="n">
-        <v>784</v>
+        <v>760</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -794,7 +794,7 @@
         <v>0.005</v>
       </c>
       <c r="D11" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E11" t="n">
         <v>0.025</v>
@@ -806,13 +806,13 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="I11" t="n">
-        <v>671</v>
+        <v>611</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -822,28 +822,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.759</v>
+        <v>0.742</v>
       </c>
       <c r="C12" t="n">
-        <v>0.258</v>
+        <v>0.262</v>
       </c>
       <c r="D12" t="n">
-        <v>0.322</v>
+        <v>0.31</v>
       </c>
       <c r="E12" t="n">
-        <v>1.238</v>
+        <v>1.215</v>
       </c>
       <c r="F12" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>1752</v>
+        <v>1279</v>
       </c>
       <c r="I12" t="n">
-        <v>714</v>
+        <v>726</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -856,28 +856,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.175</v>
+        <v>0.176</v>
       </c>
       <c r="C13" t="n">
-        <v>0.093</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
       <c r="E13" t="n">
-        <v>0.354</v>
+        <v>0.332</v>
       </c>
       <c r="F13" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="G13" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H13" t="n">
-        <v>1941</v>
+        <v>1211</v>
       </c>
       <c r="I13" t="n">
-        <v>753</v>
+        <v>651</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -890,28 +890,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.525</v>
+        <v>1.48</v>
       </c>
       <c r="C14" t="n">
-        <v>0.628</v>
+        <v>0.636</v>
       </c>
       <c r="D14" t="n">
-        <v>0.36</v>
+        <v>0.431</v>
       </c>
       <c r="E14" t="n">
-        <v>2.626</v>
+        <v>2.65</v>
       </c>
       <c r="F14" t="n">
-        <v>0.017</v>
+        <v>0.021</v>
       </c>
       <c r="G14" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="H14" t="n">
-        <v>1420</v>
+        <v>773</v>
       </c>
       <c r="I14" t="n">
-        <v>809</v>
+        <v>537</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -927,28 +927,28 @@
         <v>2.435</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.545</v>
       </c>
       <c r="D15" t="n">
-        <v>1.372</v>
+        <v>1.537</v>
       </c>
       <c r="E15" t="n">
-        <v>3.39</v>
+        <v>3.487</v>
       </c>
       <c r="F15" t="n">
         <v>0.014</v>
       </c>
       <c r="G15" t="n">
-        <v>0.022</v>
+        <v>0.018</v>
       </c>
       <c r="H15" t="n">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="I15" t="n">
-        <v>428</v>
+        <v>605</v>
       </c>
       <c r="J15" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -958,28 +958,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.18</v>
+        <v>3.31</v>
       </c>
       <c r="C16" t="n">
-        <v>1.159</v>
+        <v>1.25</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5</v>
+        <v>1.518</v>
       </c>
       <c r="E16" t="n">
-        <v>5.267</v>
+        <v>5.531</v>
       </c>
       <c r="F16" t="n">
-        <v>0.03</v>
+        <v>0.047</v>
       </c>
       <c r="G16" t="n">
-        <v>0.03</v>
+        <v>0.031</v>
       </c>
       <c r="H16" t="n">
-        <v>1532</v>
+        <v>803</v>
       </c>
       <c r="I16" t="n">
-        <v>553</v>
+        <v>412</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -992,31 +992,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.578</v>
+        <v>0.572</v>
       </c>
       <c r="C17" t="n">
-        <v>0.314</v>
+        <v>0.318</v>
       </c>
       <c r="D17" t="n">
-        <v>0.076</v>
+        <v>0.043</v>
       </c>
       <c r="E17" t="n">
-        <v>1.135</v>
+        <v>1.099</v>
       </c>
       <c r="F17" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="G17" t="n">
         <v>0.012</v>
       </c>
-      <c r="G17" t="n">
-        <v>0.01</v>
-      </c>
       <c r="H17" t="n">
-        <v>653</v>
+        <v>493</v>
       </c>
       <c r="I17" t="n">
-        <v>709</v>
+        <v>555</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="18">
@@ -1029,25 +1029,25 @@
         <v>0.587</v>
       </c>
       <c r="C18" t="n">
-        <v>0.273</v>
+        <v>0.311</v>
       </c>
       <c r="D18" t="n">
-        <v>0.16</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>1.13</v>
+        <v>1.158</v>
       </c>
       <c r="F18" t="n">
         <v>0.008</v>
       </c>
       <c r="G18" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="H18" t="n">
-        <v>1154</v>
+        <v>1253</v>
       </c>
       <c r="I18" t="n">
-        <v>752</v>
+        <v>533</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -1060,28 +1060,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22.745</v>
+        <v>22.737</v>
       </c>
       <c r="C19" t="n">
         <v>1.745</v>
       </c>
       <c r="D19" t="n">
-        <v>20.022</v>
+        <v>20.031</v>
       </c>
       <c r="E19" t="n">
-        <v>25.623</v>
+        <v>25.514</v>
       </c>
       <c r="F19" t="n">
-        <v>0.045</v>
+        <v>0.043</v>
       </c>
       <c r="G19" t="n">
-        <v>0.036</v>
+        <v>0.039</v>
       </c>
       <c r="H19" t="n">
-        <v>1282</v>
+        <v>1445</v>
       </c>
       <c r="I19" t="n">
-        <v>599</v>
+        <v>652</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.66</v>
+        <v>0.672</v>
       </c>
       <c r="C20" t="n">
-        <v>0.201</v>
+        <v>0.196</v>
       </c>
       <c r="D20" t="n">
-        <v>0.272</v>
+        <v>0.315</v>
       </c>
       <c r="E20" t="n">
-        <v>0.984</v>
+        <v>1.005</v>
       </c>
       <c r="F20" t="n">
         <v>0.005</v>
       </c>
       <c r="G20" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="H20" t="n">
-        <v>1608</v>
+        <v>1342</v>
       </c>
       <c r="I20" t="n">
-        <v>473</v>
+        <v>651</v>
       </c>
       <c r="J20" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1128,31 +1128,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.186</v>
+        <v>0.174</v>
       </c>
       <c r="C21" t="n">
-        <v>0.058</v>
+        <v>0.049</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1</v>
+        <v>0.096</v>
       </c>
       <c r="E21" t="n">
-        <v>0.284</v>
+        <v>0.257</v>
       </c>
       <c r="F21" t="n">
         <v>0.002</v>
       </c>
       <c r="G21" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H21" t="n">
-        <v>766</v>
+        <v>783</v>
       </c>
       <c r="I21" t="n">
-        <v>749</v>
+        <v>655</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="22">
@@ -1171,7 +1171,7 @@
         <v>0.042</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1180,13 +1180,13 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>511</v>
+        <v>446</v>
       </c>
       <c r="I22" t="n">
-        <v>730</v>
+        <v>641</v>
       </c>
       <c r="J22" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.133</v>
+        <v>0.127</v>
       </c>
       <c r="D23" t="n">
-        <v>0.457</v>
+        <v>0.454</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="F23" t="n">
         <v>0.003</v>
       </c>
       <c r="G23" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H23" t="n">
-        <v>1541</v>
+        <v>1242</v>
       </c>
       <c r="I23" t="n">
-        <v>621</v>
+        <v>631</v>
       </c>
       <c r="J23" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1233,13 +1233,13 @@
         <v>0.05</v>
       </c>
       <c r="C24" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="D24" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.082</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1248,13 +1248,13 @@
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>1674</v>
+        <v>1512</v>
       </c>
       <c r="I24" t="n">
-        <v>603</v>
+        <v>366</v>
       </c>
       <c r="J24" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1264,16 +1264,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.037</v>
+        <v>0.036</v>
       </c>
       <c r="C25" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="D25" t="n">
         <v>0.022</v>
       </c>
       <c r="E25" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1282,13 +1282,13 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1774</v>
+        <v>1154</v>
       </c>
       <c r="I25" t="n">
-        <v>818</v>
+        <v>652</v>
       </c>
       <c r="J25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1304,7 +1304,7 @@
         <v>0.006</v>
       </c>
       <c r="D26" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="E26" t="n">
         <v>0.034</v>
@@ -1316,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1947</v>
+        <v>1862</v>
       </c>
       <c r="I26" t="n">
-        <v>824</v>
+        <v>780</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -1332,31 +1332,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.158</v>
+        <v>3.201</v>
       </c>
       <c r="C27" t="n">
-        <v>0.629</v>
+        <v>0.67</v>
       </c>
       <c r="D27" t="n">
-        <v>2.035</v>
+        <v>2.132</v>
       </c>
       <c r="E27" t="n">
-        <v>4.31</v>
+        <v>4.607</v>
       </c>
       <c r="F27" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="G27" t="n">
         <v>0.025</v>
       </c>
       <c r="H27" t="n">
-        <v>1316</v>
+        <v>1715</v>
       </c>
       <c r="I27" t="n">
-        <v>757</v>
+        <v>665</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="28">
@@ -1366,16 +1366,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.077</v>
+        <v>0.076</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="D28" t="n">
         <v>0.042</v>
       </c>
       <c r="E28" t="n">
-        <v>0.115</v>
+        <v>0.112</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1384,10 +1384,10 @@
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>2528</v>
+        <v>1455</v>
       </c>
       <c r="I28" t="n">
-        <v>898</v>
+        <v>651</v>
       </c>
       <c r="J28" t="n">
         <v>1.01</v>
@@ -1400,28 +1400,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.222</v>
+        <v>0.22</v>
       </c>
       <c r="C29" t="n">
-        <v>0.062</v>
+        <v>0.06</v>
       </c>
       <c r="D29" t="n">
-        <v>0.108</v>
+        <v>0.115</v>
       </c>
       <c r="E29" t="n">
-        <v>0.334</v>
+        <v>0.328</v>
       </c>
       <c r="F29" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="G29" t="n">
         <v>0.002</v>
       </c>
       <c r="H29" t="n">
-        <v>1356</v>
+        <v>1823</v>
       </c>
       <c r="I29" t="n">
-        <v>632</v>
+        <v>906</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -1434,28 +1434,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.07</v>
+        <v>1.064</v>
       </c>
       <c r="C30" t="n">
-        <v>0.221</v>
+        <v>0.206</v>
       </c>
       <c r="D30" t="n">
-        <v>0.707</v>
+        <v>0.709</v>
       </c>
       <c r="E30" t="n">
-        <v>1.499</v>
+        <v>1.461</v>
       </c>
       <c r="F30" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="G30" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="H30" t="n">
-        <v>1511</v>
+        <v>1678</v>
       </c>
       <c r="I30" t="n">
-        <v>587</v>
+        <v>731</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -1486,13 +1486,13 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1319</v>
+        <v>907</v>
       </c>
       <c r="I31" t="n">
-        <v>486</v>
+        <v>524</v>
       </c>
       <c r="J31" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1502,31 +1502,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>20939.622</v>
+        <v>27117.895</v>
       </c>
       <c r="C32" t="n">
-        <v>80446.257</v>
+        <v>97345.39999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>562.1799999999999</v>
+        <v>650.027</v>
       </c>
       <c r="E32" t="n">
-        <v>66283.069</v>
+        <v>80828.74400000001</v>
       </c>
       <c r="F32" t="n">
-        <v>2836.893</v>
+        <v>4210.557</v>
       </c>
       <c r="G32" t="n">
-        <v>23284.58</v>
+        <v>19440.509</v>
       </c>
       <c r="H32" t="n">
-        <v>1319</v>
+        <v>907</v>
       </c>
       <c r="I32" t="n">
-        <v>486</v>
+        <v>524</v>
       </c>
       <c r="J32" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
